--- a/ThinktankWebCC_KeyBindings.xlsx
+++ b/ThinktankWebCC_KeyBindings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gogow\Documents\ThinktankWebCC\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CBE1B04-C2DB-4DEC-80FF-252828813C55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A3BCED6-D821-4A28-A92D-95E38A45FA42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1274,526 +1274,527 @@
     <t>Global &amp; ExMode キーバインディング詳細</t>
   </si>
   <si>
+    <t>Global: パネル切替</t>
+  </si>
+  <si>
+    <t>Global</t>
+  </si>
+  <si>
+    <t>*-*-*-*</t>
+  </si>
+  <si>
+    <t>▶ Global: モード切替</t>
+  </si>
+  <si>
+    <t>Global: モード切替</t>
+  </si>
+  <si>
+    <t>▶ Global: ExMode起動</t>
+  </si>
+  <si>
+    <t>Global: ExMode起動</t>
+  </si>
+  <si>
+    <t>▶ Global: 検索/その他</t>
+  </si>
+  <si>
+    <t>Global: 検索/その他</t>
+  </si>
+  <si>
+    <t>▶ ExApp (Global)</t>
+  </si>
+  <si>
+    <t>ExApp (Global)</t>
+  </si>
+  <si>
+    <t>Font.Size:up</t>
+  </si>
+  <si>
+    <t>*-*-*-ExApp</t>
+  </si>
+  <si>
+    <t>Font.Size:down</t>
+  </si>
+  <si>
+    <t>Style:zen</t>
+  </si>
+  <si>
+    <t>Zenレイアウト</t>
+  </si>
+  <si>
+    <t>Style:standard</t>
+  </si>
+  <si>
+    <t>Standardレイアウト</t>
+  </si>
+  <si>
+    <t>Style:reset</t>
+  </si>
+  <si>
+    <t>レイアウトリセット</t>
+  </si>
+  <si>
+    <t>Voice.Input:next</t>
+  </si>
+  <si>
+    <t>音声入力切替</t>
+  </si>
+  <si>
+    <t>Shift+Alt</t>
+  </si>
+  <si>
+    <t>Memo.Renew</t>
+  </si>
+  <si>
+    <t>メモ更新</t>
+  </si>
+  <si>
+    <t>Shift+Control+Alt</t>
+  </si>
+  <si>
+    <t>AllCollection.Save</t>
+  </si>
+  <si>
+    <t>全コレクション保存</t>
+  </si>
+  <si>
+    <t>▶ ExFold</t>
+  </si>
+  <si>
+    <t>ExFold</t>
+  </si>
+  <si>
+    <t>Folding.Open</t>
+  </si>
+  <si>
+    <t>展開</t>
+  </si>
+  <si>
+    <t>*-*-*-ExFold</t>
+  </si>
+  <si>
+    <t>Folding.Close</t>
+  </si>
+  <si>
+    <t>閉じる</t>
+  </si>
+  <si>
+    <t>O</t>
+  </si>
+  <si>
+    <t>Folding.OpenAll</t>
+  </si>
+  <si>
+    <t>全展開</t>
+  </si>
+  <si>
+    <t>Folding.CloseAll</t>
+  </si>
+  <si>
+    <t>全閉じる</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>全閉じる(1)</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>Folding.OpenLevel2</t>
+  </si>
+  <si>
+    <t>Lv2まで展開</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>Folding.OpenLevel3</t>
+  </si>
+  <si>
+    <t>Lv3まで展開</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>Folding.OpenLevel4</t>
+  </si>
+  <si>
+    <t>Lv4まで展開</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>Folding.OpenLevel5</t>
+  </si>
+  <si>
+    <t>Lv5まで展開</t>
+  </si>
+  <si>
+    <t>Editor.CurPos:prevfolding</t>
+  </si>
+  <si>
+    <t>前の折りたたみ</t>
+  </si>
+  <si>
+    <t>Editor.CurPos:nextfolding</t>
+  </si>
+  <si>
+    <t>次の折りたたみ</t>
+  </si>
+  <si>
+    <t>Folding.OpenAllSibling</t>
+  </si>
+  <si>
+    <t>Folding.CloseAllSibling</t>
+  </si>
+  <si>
+    <t>▶ ExDateTime</t>
+  </si>
+  <si>
+    <t>ExDateTime</t>
+  </si>
+  <si>
+    <t>DateTime.Next1y</t>
+  </si>
+  <si>
+    <t>1年後</t>
+  </si>
+  <si>
+    <t>*-*-*-ExDateTime</t>
+  </si>
+  <si>
+    <t>DateTime.Prev1y</t>
+  </si>
+  <si>
+    <t>1年前</t>
+  </si>
+  <si>
+    <t>DateTime.Next1m</t>
+  </si>
+  <si>
+    <t>1ヶ月後</t>
+  </si>
+  <si>
+    <t>DateTime.Prev1m</t>
+  </si>
+  <si>
+    <t>1ヶ月前</t>
+  </si>
+  <si>
+    <t>DateTime.Next1d</t>
+  </si>
+  <si>
+    <t>1日後</t>
+  </si>
+  <si>
+    <t>DateTime.Prev1d</t>
+  </si>
+  <si>
+    <t>1日前</t>
+  </si>
+  <si>
+    <t>DateTime.Next1w</t>
+  </si>
+  <si>
+    <t>1週間後</t>
+  </si>
+  <si>
+    <t>DateTime.Prev1w</t>
+  </si>
+  <si>
+    <t>1週間前</t>
+  </si>
+  <si>
+    <t>DateTime.Format:next</t>
+  </si>
+  <si>
+    <t>次のフォーマット</t>
+  </si>
+  <si>
+    <t>DateTime.Format:prev</t>
+  </si>
+  <si>
+    <t>前のフォーマット</t>
+  </si>
+  <si>
+    <t>DateTime.Weekday</t>
+  </si>
+  <si>
+    <t>曜日トグル</t>
+  </si>
+  <si>
+    <t>J</t>
+  </si>
+  <si>
+    <t>DateTime.Time</t>
+  </si>
+  <si>
+    <t>時刻トグル</t>
+  </si>
+  <si>
+    <t>▶ ExPanel (Global)</t>
+  </si>
+  <si>
+    <t>ExPanel (Global)</t>
+  </si>
+  <si>
+    <t>(ExPanel).Mode:Table</t>
+  </si>
+  <si>
+    <t>ExPanel Tableモード</t>
+  </si>
+  <si>
+    <t>*-*-*-ExPanel</t>
+  </si>
+  <si>
+    <t>(ExPanel).Mode:WebView</t>
+  </si>
+  <si>
+    <t>ExPanel WebViewモード</t>
+  </si>
+  <si>
+    <t>(ExPanel).Mode:Editor</t>
+  </si>
+  <si>
+    <t>ExPanel Editorモード</t>
+  </si>
+  <si>
+    <t>(ExPanel).Mode:next</t>
+  </si>
+  <si>
+    <t>ExPanel 次モード</t>
+  </si>
+  <si>
+    <t>(ExPanel).Mode:prev</t>
+  </si>
+  <si>
+    <t>ExPanel 前モード</t>
+  </si>
+  <si>
+    <t>(ExPanel).Font.Size:up</t>
+  </si>
+  <si>
+    <t>ExPanelフォント拡大</t>
+  </si>
+  <si>
+    <t>(ExPanel).Font.Size:down</t>
+  </si>
+  <si>
+    <t>ExPanelフォント縮小</t>
+  </si>
+  <si>
+    <t>空きキー分析 - モード別未割当キー一覧（新規アサイン候補）</t>
+  </si>
+  <si>
+    <t>※ GlobalキーはすべてのモードでBLOCK。MASKキーは明示的に無効化済み。空きキーはモード固有のアクション割当候補。</t>
+  </si>
+  <si>
+    <t>Editor現状</t>
+  </si>
+  <si>
+    <t>Table現状</t>
+  </si>
+  <si>
+    <t>WebView現状</t>
+  </si>
+  <si>
+    <t>空き(Editor)</t>
+  </si>
+  <si>
+    <t>空き(Table)</t>
+  </si>
+  <si>
+    <t>空き(WebView)</t>
+  </si>
+  <si>
+    <t>── 修飾キー: (なし) ──</t>
+  </si>
+  <si>
+    <t>★ 空き</t>
+  </si>
+  <si>
+    <t>U</t>
+  </si>
+  <si>
+    <t>Delegate</t>
+  </si>
+  <si>
+    <t>Rev</t>
+  </si>
+  <si>
+    <t>F6</t>
+  </si>
+  <si>
+    <t>F7</t>
+  </si>
+  <si>
+    <t>F8</t>
+  </si>
+  <si>
+    <t>F9</t>
+  </si>
+  <si>
+    <t>F10</t>
+  </si>
+  <si>
+    <t>Default</t>
+  </si>
+  <si>
+    <t>Query</t>
+  </si>
+  <si>
+    <t>CurPos:prevchar</t>
+  </si>
+  <si>
+    <t>CurPos:nextchar</t>
+  </si>
+  <si>
+    <t>TAB</t>
+  </si>
+  <si>
+    <t>ESC</t>
+  </si>
+  <si>
+    <t>── 修飾キー: Shift ──</t>
+  </si>
+  <si>
+    <t>ContextMenu</t>
+  </si>
+  <si>
+    <t>SelPos:prevline</t>
+  </si>
+  <si>
+    <t>CurPos:-10</t>
+  </si>
+  <si>
+    <t>SelPos:nextline</t>
+  </si>
+  <si>
+    <t>CurPos:+10</t>
+  </si>
+  <si>
+    <t>SelPos:prevchar</t>
+  </si>
+  <si>
+    <t>SelPos:nextchar</t>
+  </si>
+  <si>
+    <t>── 修飾キー: Control ──</t>
+  </si>
+  <si>
+    <t>CurPos:linestart+</t>
+  </si>
+  <si>
+    <t>CurPos:first</t>
+  </si>
+  <si>
+    <t>CurPos:lineend+</t>
+  </si>
+  <si>
+    <t>CurPos:last</t>
+  </si>
+  <si>
+    <t>FoldingDown</t>
+  </si>
+  <si>
+    <t>CurPos:nextline</t>
+  </si>
+  <si>
+    <t>CurPos:next</t>
+  </si>
+  <si>
+    <t>CurPos:prevline</t>
+  </si>
+  <si>
+    <t>CurPos:prev</t>
+  </si>
+  <si>
+    <t>Save</t>
+  </si>
+  <si>
+    <t>Suggest</t>
+  </si>
+  <si>
+    <t>── 修飾キー: Alt ──</t>
+  </si>
+  <si>
+    <t>Close</t>
+  </si>
+  <si>
+    <t>SearchMode:next</t>
+  </si>
+  <si>
+    <t>CurPos:prevvisfoldin</t>
+  </si>
+  <si>
+    <t>CurPos:nextvisfoldin</t>
+  </si>
+  <si>
+    <t>Open</t>
+  </si>
+  <si>
+    <t>── 修飾キー: Control+Shift ──</t>
+  </si>
+  <si>
+    <t>SelPos:linestart</t>
+  </si>
+  <si>
+    <t>SelPos:lineend</t>
+  </si>
+  <si>
+    <t>FoldingUp</t>
+  </si>
+  <si>
+    <t>── 修飾キー: Alt+Shift ──</t>
+  </si>
+  <si>
+    <t>CurPos:lastsibfoldin</t>
+  </si>
+  <si>
+    <t>CurPos:firstsibfoldi</t>
+  </si>
+  <si>
+    <t>CurPos:prevsibfoldin</t>
+  </si>
+  <si>
+    <t>CurPos:nextsibfoldin</t>
+  </si>
+  <si>
+    <t>CloseAllSibling</t>
+  </si>
+  <si>
+    <t>OpenAllSibling</t>
+  </si>
+  <si>
+    <t>── 修飾キー: Control+Alt ──</t>
+  </si>
+  <si>
+    <t>CurPos:lastline</t>
+  </si>
+  <si>
+    <t>CurPos:firstline</t>
+  </si>
+  <si>
+    <t>── 修飾キー: Control+Shift+Alt ──</t>
+  </si>
+  <si>
+    <t>FoldingInit</t>
+  </si>
+  <si>
+    <t>SelPos:lastline</t>
+  </si>
+  <si>
+    <t>SelPos:firstline</t>
+  </si>
+  <si>
     <t>▶ Global: パネル切替</t>
-  </si>
-  <si>
-    <t>Global: パネル切替</t>
-  </si>
-  <si>
-    <t>Global</t>
-  </si>
-  <si>
-    <t>*-*-*-*</t>
-  </si>
-  <si>
-    <t>▶ Global: モード切替</t>
-  </si>
-  <si>
-    <t>Global: モード切替</t>
-  </si>
-  <si>
-    <t>▶ Global: ExMode起動</t>
-  </si>
-  <si>
-    <t>Global: ExMode起動</t>
-  </si>
-  <si>
-    <t>▶ Global: 検索/その他</t>
-  </si>
-  <si>
-    <t>Global: 検索/その他</t>
-  </si>
-  <si>
-    <t>▶ ExApp (Global)</t>
-  </si>
-  <si>
-    <t>ExApp (Global)</t>
-  </si>
-  <si>
-    <t>Font.Size:up</t>
-  </si>
-  <si>
-    <t>*-*-*-ExApp</t>
-  </si>
-  <si>
-    <t>Font.Size:down</t>
-  </si>
-  <si>
-    <t>Style:zen</t>
-  </si>
-  <si>
-    <t>Zenレイアウト</t>
-  </si>
-  <si>
-    <t>Style:standard</t>
-  </si>
-  <si>
-    <t>Standardレイアウト</t>
-  </si>
-  <si>
-    <t>Style:reset</t>
-  </si>
-  <si>
-    <t>レイアウトリセット</t>
-  </si>
-  <si>
-    <t>Voice.Input:next</t>
-  </si>
-  <si>
-    <t>音声入力切替</t>
-  </si>
-  <si>
-    <t>Shift+Alt</t>
-  </si>
-  <si>
-    <t>Memo.Renew</t>
-  </si>
-  <si>
-    <t>メモ更新</t>
-  </si>
-  <si>
-    <t>Shift+Control+Alt</t>
-  </si>
-  <si>
-    <t>AllCollection.Save</t>
-  </si>
-  <si>
-    <t>全コレクション保存</t>
-  </si>
-  <si>
-    <t>▶ ExFold</t>
-  </si>
-  <si>
-    <t>ExFold</t>
-  </si>
-  <si>
-    <t>Folding.Open</t>
-  </si>
-  <si>
-    <t>展開</t>
-  </si>
-  <si>
-    <t>*-*-*-ExFold</t>
-  </si>
-  <si>
-    <t>Folding.Close</t>
-  </si>
-  <si>
-    <t>閉じる</t>
-  </si>
-  <si>
-    <t>O</t>
-  </si>
-  <si>
-    <t>Folding.OpenAll</t>
-  </si>
-  <si>
-    <t>全展開</t>
-  </si>
-  <si>
-    <t>Folding.CloseAll</t>
-  </si>
-  <si>
-    <t>全閉じる</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>全閉じる(1)</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>Folding.OpenLevel2</t>
-  </si>
-  <si>
-    <t>Lv2まで展開</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>Folding.OpenLevel3</t>
-  </si>
-  <si>
-    <t>Lv3まで展開</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>Folding.OpenLevel4</t>
-  </si>
-  <si>
-    <t>Lv4まで展開</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>Folding.OpenLevel5</t>
-  </si>
-  <si>
-    <t>Lv5まで展開</t>
-  </si>
-  <si>
-    <t>Editor.CurPos:prevfolding</t>
-  </si>
-  <si>
-    <t>前の折りたたみ</t>
-  </si>
-  <si>
-    <t>Editor.CurPos:nextfolding</t>
-  </si>
-  <si>
-    <t>次の折りたたみ</t>
-  </si>
-  <si>
-    <t>Folding.OpenAllSibling</t>
-  </si>
-  <si>
-    <t>Folding.CloseAllSibling</t>
-  </si>
-  <si>
-    <t>▶ ExDateTime</t>
-  </si>
-  <si>
-    <t>ExDateTime</t>
-  </si>
-  <si>
-    <t>DateTime.Next1y</t>
-  </si>
-  <si>
-    <t>1年後</t>
-  </si>
-  <si>
-    <t>*-*-*-ExDateTime</t>
-  </si>
-  <si>
-    <t>DateTime.Prev1y</t>
-  </si>
-  <si>
-    <t>1年前</t>
-  </si>
-  <si>
-    <t>DateTime.Next1m</t>
-  </si>
-  <si>
-    <t>1ヶ月後</t>
-  </si>
-  <si>
-    <t>DateTime.Prev1m</t>
-  </si>
-  <si>
-    <t>1ヶ月前</t>
-  </si>
-  <si>
-    <t>DateTime.Next1d</t>
-  </si>
-  <si>
-    <t>1日後</t>
-  </si>
-  <si>
-    <t>DateTime.Prev1d</t>
-  </si>
-  <si>
-    <t>1日前</t>
-  </si>
-  <si>
-    <t>DateTime.Next1w</t>
-  </si>
-  <si>
-    <t>1週間後</t>
-  </si>
-  <si>
-    <t>DateTime.Prev1w</t>
-  </si>
-  <si>
-    <t>1週間前</t>
-  </si>
-  <si>
-    <t>DateTime.Format:next</t>
-  </si>
-  <si>
-    <t>次のフォーマット</t>
-  </si>
-  <si>
-    <t>DateTime.Format:prev</t>
-  </si>
-  <si>
-    <t>前のフォーマット</t>
-  </si>
-  <si>
-    <t>DateTime.Weekday</t>
-  </si>
-  <si>
-    <t>曜日トグル</t>
-  </si>
-  <si>
-    <t>J</t>
-  </si>
-  <si>
-    <t>DateTime.Time</t>
-  </si>
-  <si>
-    <t>時刻トグル</t>
-  </si>
-  <si>
-    <t>▶ ExPanel (Global)</t>
-  </si>
-  <si>
-    <t>ExPanel (Global)</t>
-  </si>
-  <si>
-    <t>(ExPanel).Mode:Table</t>
-  </si>
-  <si>
-    <t>ExPanel Tableモード</t>
-  </si>
-  <si>
-    <t>*-*-*-ExPanel</t>
-  </si>
-  <si>
-    <t>(ExPanel).Mode:WebView</t>
-  </si>
-  <si>
-    <t>ExPanel WebViewモード</t>
-  </si>
-  <si>
-    <t>(ExPanel).Mode:Editor</t>
-  </si>
-  <si>
-    <t>ExPanel Editorモード</t>
-  </si>
-  <si>
-    <t>(ExPanel).Mode:next</t>
-  </si>
-  <si>
-    <t>ExPanel 次モード</t>
-  </si>
-  <si>
-    <t>(ExPanel).Mode:prev</t>
-  </si>
-  <si>
-    <t>ExPanel 前モード</t>
-  </si>
-  <si>
-    <t>(ExPanel).Font.Size:up</t>
-  </si>
-  <si>
-    <t>ExPanelフォント拡大</t>
-  </si>
-  <si>
-    <t>(ExPanel).Font.Size:down</t>
-  </si>
-  <si>
-    <t>ExPanelフォント縮小</t>
-  </si>
-  <si>
-    <t>空きキー分析 - モード別未割当キー一覧（新規アサイン候補）</t>
-  </si>
-  <si>
-    <t>※ GlobalキーはすべてのモードでBLOCK。MASKキーは明示的に無効化済み。空きキーはモード固有のアクション割当候補。</t>
-  </si>
-  <si>
-    <t>Editor現状</t>
-  </si>
-  <si>
-    <t>Table現状</t>
-  </si>
-  <si>
-    <t>WebView現状</t>
-  </si>
-  <si>
-    <t>空き(Editor)</t>
-  </si>
-  <si>
-    <t>空き(Table)</t>
-  </si>
-  <si>
-    <t>空き(WebView)</t>
-  </si>
-  <si>
-    <t>── 修飾キー: (なし) ──</t>
-  </si>
-  <si>
-    <t>★ 空き</t>
-  </si>
-  <si>
-    <t>U</t>
-  </si>
-  <si>
-    <t>Delegate</t>
-  </si>
-  <si>
-    <t>Rev</t>
-  </si>
-  <si>
-    <t>F6</t>
-  </si>
-  <si>
-    <t>F7</t>
-  </si>
-  <si>
-    <t>F8</t>
-  </si>
-  <si>
-    <t>F9</t>
-  </si>
-  <si>
-    <t>F10</t>
-  </si>
-  <si>
-    <t>Default</t>
-  </si>
-  <si>
-    <t>Query</t>
-  </si>
-  <si>
-    <t>CurPos:prevchar</t>
-  </si>
-  <si>
-    <t>CurPos:nextchar</t>
-  </si>
-  <si>
-    <t>TAB</t>
-  </si>
-  <si>
-    <t>ESC</t>
-  </si>
-  <si>
-    <t>── 修飾キー: Shift ──</t>
-  </si>
-  <si>
-    <t>ContextMenu</t>
-  </si>
-  <si>
-    <t>SelPos:prevline</t>
-  </si>
-  <si>
-    <t>CurPos:-10</t>
-  </si>
-  <si>
-    <t>SelPos:nextline</t>
-  </si>
-  <si>
-    <t>CurPos:+10</t>
-  </si>
-  <si>
-    <t>SelPos:prevchar</t>
-  </si>
-  <si>
-    <t>SelPos:nextchar</t>
-  </si>
-  <si>
-    <t>── 修飾キー: Control ──</t>
-  </si>
-  <si>
-    <t>CurPos:linestart+</t>
-  </si>
-  <si>
-    <t>CurPos:first</t>
-  </si>
-  <si>
-    <t>CurPos:lineend+</t>
-  </si>
-  <si>
-    <t>CurPos:last</t>
-  </si>
-  <si>
-    <t>FoldingDown</t>
-  </si>
-  <si>
-    <t>CurPos:nextline</t>
-  </si>
-  <si>
-    <t>CurPos:next</t>
-  </si>
-  <si>
-    <t>CurPos:prevline</t>
-  </si>
-  <si>
-    <t>CurPos:prev</t>
-  </si>
-  <si>
-    <t>Save</t>
-  </si>
-  <si>
-    <t>Suggest</t>
-  </si>
-  <si>
-    <t>── 修飾キー: Alt ──</t>
-  </si>
-  <si>
-    <t>Close</t>
-  </si>
-  <si>
-    <t>SearchMode:next</t>
-  </si>
-  <si>
-    <t>CurPos:prevvisfoldin</t>
-  </si>
-  <si>
-    <t>CurPos:nextvisfoldin</t>
-  </si>
-  <si>
-    <t>Open</t>
-  </si>
-  <si>
-    <t>── 修飾キー: Control+Shift ──</t>
-  </si>
-  <si>
-    <t>SelPos:linestart</t>
-  </si>
-  <si>
-    <t>SelPos:lineend</t>
-  </si>
-  <si>
-    <t>FoldingUp</t>
-  </si>
-  <si>
-    <t>── 修飾キー: Alt+Shift ──</t>
-  </si>
-  <si>
-    <t>CurPos:lastsibfoldin</t>
-  </si>
-  <si>
-    <t>CurPos:firstsibfoldi</t>
-  </si>
-  <si>
-    <t>CurPos:prevsibfoldin</t>
-  </si>
-  <si>
-    <t>CurPos:nextsibfoldin</t>
-  </si>
-  <si>
-    <t>CloseAllSibling</t>
-  </si>
-  <si>
-    <t>OpenAllSibling</t>
-  </si>
-  <si>
-    <t>── 修飾キー: Control+Alt ──</t>
-  </si>
-  <si>
-    <t>CurPos:lastline</t>
-  </si>
-  <si>
-    <t>CurPos:firstline</t>
-  </si>
-  <si>
-    <t>── 修飾キー: Control+Shift+Alt ──</t>
-  </si>
-  <si>
-    <t>FoldingInit</t>
-  </si>
-  <si>
-    <t>SelPos:lastline</t>
-  </si>
-  <si>
-    <t>SelPos:firstline</t>
+    <phoneticPr fontId="13"/>
   </si>
 </sst>
 </file>
@@ -7681,17 +7682,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="A95:G95"/>
-    <mergeCell ref="A86:G86"/>
-    <mergeCell ref="A60:G60"/>
-    <mergeCell ref="A49:G49"/>
-    <mergeCell ref="A75:G75"/>
     <mergeCell ref="A13:G13"/>
     <mergeCell ref="A36:G36"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A80:G80"/>
     <mergeCell ref="A3:G3"/>
     <mergeCell ref="A77:G77"/>
+    <mergeCell ref="A95:G95"/>
+    <mergeCell ref="A86:G86"/>
+    <mergeCell ref="A60:G60"/>
+    <mergeCell ref="A49:G49"/>
+    <mergeCell ref="A75:G75"/>
   </mergeCells>
   <phoneticPr fontId="13"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -9476,7 +9477,7 @@
     </row>
     <row r="3" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="42" t="s">
-        <v>413</v>
+        <v>586</v>
       </c>
       <c r="B3" s="39"/>
       <c r="C3" s="39"/>
@@ -9487,7 +9488,7 @@
     </row>
     <row r="4" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="18" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B4" s="19" t="s">
         <v>166</v>
@@ -9502,15 +9503,15 @@
         <v>231</v>
       </c>
       <c r="F4" s="19" t="s">
+        <v>414</v>
+      </c>
+      <c r="G4" s="22" t="s">
         <v>415</v>
-      </c>
-      <c r="G4" s="22" t="s">
-        <v>416</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="18" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B5" s="19" t="s">
         <v>268</v>
@@ -9525,15 +9526,15 @@
         <v>291</v>
       </c>
       <c r="F5" s="19" t="s">
+        <v>414</v>
+      </c>
+      <c r="G5" s="22" t="s">
         <v>415</v>
-      </c>
-      <c r="G5" s="22" t="s">
-        <v>416</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="18" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B6" s="19" t="s">
         <v>166</v>
@@ -9548,15 +9549,15 @@
         <v>192</v>
       </c>
       <c r="F6" s="19" t="s">
+        <v>414</v>
+      </c>
+      <c r="G6" s="22" t="s">
         <v>415</v>
-      </c>
-      <c r="G6" s="22" t="s">
-        <v>416</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="18" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B7" s="19" t="s">
         <v>166</v>
@@ -9571,15 +9572,15 @@
         <v>189</v>
       </c>
       <c r="F7" s="19" t="s">
+        <v>414</v>
+      </c>
+      <c r="G7" s="22" t="s">
         <v>415</v>
-      </c>
-      <c r="G7" s="22" t="s">
-        <v>416</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="18" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B8" s="19" t="s">
         <v>166</v>
@@ -9594,15 +9595,15 @@
         <v>214</v>
       </c>
       <c r="F8" s="19" t="s">
+        <v>414</v>
+      </c>
+      <c r="G8" s="22" t="s">
         <v>415</v>
-      </c>
-      <c r="G8" s="22" t="s">
-        <v>416</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="18" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B9" s="19" t="s">
         <v>166</v>
@@ -9617,15 +9618,15 @@
         <v>179</v>
       </c>
       <c r="F9" s="19" t="s">
+        <v>414</v>
+      </c>
+      <c r="G9" s="22" t="s">
         <v>415</v>
-      </c>
-      <c r="G9" s="22" t="s">
-        <v>416</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="18" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B10" s="19" t="s">
         <v>166</v>
@@ -9640,15 +9641,15 @@
         <v>222</v>
       </c>
       <c r="F10" s="19" t="s">
+        <v>414</v>
+      </c>
+      <c r="G10" s="22" t="s">
         <v>415</v>
-      </c>
-      <c r="G10" s="22" t="s">
-        <v>416</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="18" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B11" s="19" t="s">
         <v>166</v>
@@ -9663,15 +9664,15 @@
         <v>225</v>
       </c>
       <c r="F11" s="19" t="s">
+        <v>414</v>
+      </c>
+      <c r="G11" s="22" t="s">
         <v>415</v>
-      </c>
-      <c r="G11" s="22" t="s">
-        <v>416</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="18" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B12" s="19" t="s">
         <v>166</v>
@@ -9686,15 +9687,15 @@
         <v>228</v>
       </c>
       <c r="F12" s="19" t="s">
+        <v>414</v>
+      </c>
+      <c r="G12" s="22" t="s">
         <v>415</v>
-      </c>
-      <c r="G12" s="22" t="s">
-        <v>416</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="42" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="B13" s="39"/>
       <c r="C13" s="39"/>
@@ -9705,7 +9706,7 @@
     </row>
     <row r="14" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A14" s="18" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="B14" s="19" t="s">
         <v>166</v>
@@ -9720,15 +9721,15 @@
         <v>207</v>
       </c>
       <c r="F14" s="19" t="s">
+        <v>414</v>
+      </c>
+      <c r="G14" s="22" t="s">
         <v>415</v>
-      </c>
-      <c r="G14" s="22" t="s">
-        <v>416</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A15" s="18" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="B15" s="19" t="s">
         <v>166</v>
@@ -9743,15 +9744,15 @@
         <v>220</v>
       </c>
       <c r="F15" s="19" t="s">
+        <v>414</v>
+      </c>
+      <c r="G15" s="22" t="s">
         <v>415</v>
-      </c>
-      <c r="G15" s="22" t="s">
-        <v>416</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A16" s="18" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="B16" s="19" t="s">
         <v>166</v>
@@ -9766,15 +9767,15 @@
         <v>181</v>
       </c>
       <c r="F16" s="19" t="s">
+        <v>414</v>
+      </c>
+      <c r="G16" s="22" t="s">
         <v>415</v>
-      </c>
-      <c r="G16" s="22" t="s">
-        <v>416</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A17" s="18" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="B17" s="19" t="s">
         <v>166</v>
@@ -9789,15 +9790,15 @@
         <v>195</v>
       </c>
       <c r="F17" s="19" t="s">
+        <v>414</v>
+      </c>
+      <c r="G17" s="22" t="s">
         <v>415</v>
-      </c>
-      <c r="G17" s="22" t="s">
-        <v>416</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A18" s="18" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="B18" s="19" t="s">
         <v>268</v>
@@ -9812,15 +9813,15 @@
         <v>282</v>
       </c>
       <c r="F18" s="19" t="s">
+        <v>414</v>
+      </c>
+      <c r="G18" s="22" t="s">
         <v>415</v>
-      </c>
-      <c r="G18" s="22" t="s">
-        <v>416</v>
       </c>
     </row>
     <row r="19" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A19" s="18" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="B19" s="19" t="s">
         <v>311</v>
@@ -9835,15 +9836,15 @@
         <v>314</v>
       </c>
       <c r="F19" s="19" t="s">
+        <v>414</v>
+      </c>
+      <c r="G19" s="22" t="s">
         <v>415</v>
-      </c>
-      <c r="G19" s="22" t="s">
-        <v>416</v>
       </c>
     </row>
     <row r="20" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A20" s="18" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="B20" s="19" t="s">
         <v>311</v>
@@ -9858,15 +9859,15 @@
         <v>320</v>
       </c>
       <c r="F20" s="19" t="s">
+        <v>414</v>
+      </c>
+      <c r="G20" s="22" t="s">
         <v>415</v>
-      </c>
-      <c r="G20" s="22" t="s">
-        <v>416</v>
       </c>
     </row>
     <row r="21" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A21" s="18" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="B21" s="19" t="s">
         <v>311</v>
@@ -9881,15 +9882,15 @@
         <v>318</v>
       </c>
       <c r="F21" s="19" t="s">
+        <v>414</v>
+      </c>
+      <c r="G21" s="22" t="s">
         <v>415</v>
-      </c>
-      <c r="G21" s="22" t="s">
-        <v>416</v>
       </c>
     </row>
     <row r="22" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A22" s="18" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="B22" s="19" t="s">
         <v>311</v>
@@ -9904,15 +9905,15 @@
         <v>322</v>
       </c>
       <c r="F22" s="19" t="s">
+        <v>414</v>
+      </c>
+      <c r="G22" s="22" t="s">
         <v>415</v>
-      </c>
-      <c r="G22" s="22" t="s">
-        <v>416</v>
       </c>
     </row>
     <row r="23" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A23" s="18" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="B23" s="19" t="s">
         <v>311</v>
@@ -9927,15 +9928,15 @@
         <v>316</v>
       </c>
       <c r="F23" s="19" t="s">
+        <v>414</v>
+      </c>
+      <c r="G23" s="22" t="s">
         <v>415</v>
-      </c>
-      <c r="G23" s="22" t="s">
-        <v>416</v>
       </c>
     </row>
     <row r="24" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A24" s="18" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="B24" s="19" t="s">
         <v>311</v>
@@ -9950,15 +9951,15 @@
         <v>324</v>
       </c>
       <c r="F24" s="19" t="s">
+        <v>414</v>
+      </c>
+      <c r="G24" s="22" t="s">
         <v>415</v>
-      </c>
-      <c r="G24" s="22" t="s">
-        <v>416</v>
       </c>
     </row>
     <row r="25" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A25" s="18" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="B25" s="19" t="s">
         <v>311</v>
@@ -9973,15 +9974,15 @@
         <v>326</v>
       </c>
       <c r="F25" s="19" t="s">
+        <v>414</v>
+      </c>
+      <c r="G25" s="22" t="s">
         <v>415</v>
-      </c>
-      <c r="G25" s="22" t="s">
-        <v>416</v>
       </c>
     </row>
     <row r="26" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A26" s="18" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="B26" s="19" t="s">
         <v>311</v>
@@ -9996,15 +9997,15 @@
         <v>328</v>
       </c>
       <c r="F26" s="19" t="s">
+        <v>414</v>
+      </c>
+      <c r="G26" s="22" t="s">
         <v>415</v>
-      </c>
-      <c r="G26" s="22" t="s">
-        <v>416</v>
       </c>
     </row>
     <row r="27" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="42" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B27" s="39"/>
       <c r="C27" s="39"/>
@@ -10015,7 +10016,7 @@
     </row>
     <row r="28" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A28" s="18" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B28" s="19" t="s">
         <v>311</v>
@@ -10030,15 +10031,15 @@
         <v>314</v>
       </c>
       <c r="F28" s="19" t="s">
+        <v>414</v>
+      </c>
+      <c r="G28" s="22" t="s">
         <v>415</v>
-      </c>
-      <c r="G28" s="22" t="s">
-        <v>416</v>
       </c>
     </row>
     <row r="29" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A29" s="18" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B29" s="19" t="s">
         <v>311</v>
@@ -10053,15 +10054,15 @@
         <v>320</v>
       </c>
       <c r="F29" s="19" t="s">
+        <v>414</v>
+      </c>
+      <c r="G29" s="22" t="s">
         <v>415</v>
-      </c>
-      <c r="G29" s="22" t="s">
-        <v>416</v>
       </c>
     </row>
     <row r="30" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A30" s="18" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B30" s="19" t="s">
         <v>311</v>
@@ -10076,15 +10077,15 @@
         <v>318</v>
       </c>
       <c r="F30" s="19" t="s">
+        <v>414</v>
+      </c>
+      <c r="G30" s="22" t="s">
         <v>415</v>
-      </c>
-      <c r="G30" s="22" t="s">
-        <v>416</v>
       </c>
     </row>
     <row r="31" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A31" s="18" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B31" s="19" t="s">
         <v>311</v>
@@ -10099,15 +10100,15 @@
         <v>322</v>
       </c>
       <c r="F31" s="19" t="s">
+        <v>414</v>
+      </c>
+      <c r="G31" s="22" t="s">
         <v>415</v>
-      </c>
-      <c r="G31" s="22" t="s">
-        <v>416</v>
       </c>
     </row>
     <row r="32" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A32" s="18" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B32" s="19" t="s">
         <v>311</v>
@@ -10122,15 +10123,15 @@
         <v>316</v>
       </c>
       <c r="F32" s="19" t="s">
+        <v>414</v>
+      </c>
+      <c r="G32" s="22" t="s">
         <v>415</v>
-      </c>
-      <c r="G32" s="22" t="s">
-        <v>416</v>
       </c>
     </row>
     <row r="33" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A33" s="18" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B33" s="19" t="s">
         <v>311</v>
@@ -10145,15 +10146,15 @@
         <v>324</v>
       </c>
       <c r="F33" s="19" t="s">
+        <v>414</v>
+      </c>
+      <c r="G33" s="22" t="s">
         <v>415</v>
-      </c>
-      <c r="G33" s="22" t="s">
-        <v>416</v>
       </c>
     </row>
     <row r="34" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A34" s="18" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B34" s="19" t="s">
         <v>311</v>
@@ -10168,15 +10169,15 @@
         <v>326</v>
       </c>
       <c r="F34" s="19" t="s">
+        <v>414</v>
+      </c>
+      <c r="G34" s="22" t="s">
         <v>415</v>
-      </c>
-      <c r="G34" s="22" t="s">
-        <v>416</v>
       </c>
     </row>
     <row r="35" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A35" s="18" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B35" s="19" t="s">
         <v>311</v>
@@ -10191,15 +10192,15 @@
         <v>328</v>
       </c>
       <c r="F35" s="19" t="s">
+        <v>414</v>
+      </c>
+      <c r="G35" s="22" t="s">
         <v>415</v>
-      </c>
-      <c r="G35" s="22" t="s">
-        <v>416</v>
       </c>
     </row>
     <row r="36" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="42" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B36" s="39"/>
       <c r="C36" s="39"/>
@@ -10210,7 +10211,7 @@
     </row>
     <row r="37" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A37" s="18" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="B37" s="19" t="s">
         <v>99</v>
@@ -10225,7 +10226,7 @@
         <v>124</v>
       </c>
       <c r="F37" s="19" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="G37" s="22" t="s">
         <v>339</v>
@@ -10233,7 +10234,7 @@
     </row>
     <row r="38" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A38" s="18" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="B38" s="19" t="s">
         <v>166</v>
@@ -10248,7 +10249,7 @@
         <v>212</v>
       </c>
       <c r="F38" s="19" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="G38" s="22" t="s">
         <v>339</v>
@@ -10256,7 +10257,7 @@
     </row>
     <row r="39" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A39" s="18" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="B39" s="19" t="s">
         <v>166</v>
@@ -10271,7 +10272,7 @@
         <v>177</v>
       </c>
       <c r="F39" s="19" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="G39" s="22" t="s">
         <v>339</v>
@@ -10279,7 +10280,7 @@
     </row>
     <row r="40" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A40" s="18" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="B40" s="19" t="s">
         <v>99</v>
@@ -10294,7 +10295,7 @@
         <v>133</v>
       </c>
       <c r="F40" s="19" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="G40" s="22" t="s">
         <v>339</v>
@@ -10302,7 +10303,7 @@
     </row>
     <row r="41" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A41" s="18" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="B41" s="19" t="s">
         <v>166</v>
@@ -10317,7 +10318,7 @@
         <v>338</v>
       </c>
       <c r="F41" s="19" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="G41" s="22" t="s">
         <v>339</v>
@@ -10325,7 +10326,7 @@
     </row>
     <row r="42" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A42" s="18" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="B42" s="19" t="s">
         <v>13</v>
@@ -10340,15 +10341,15 @@
         <v>50</v>
       </c>
       <c r="F42" s="19" t="s">
+        <v>414</v>
+      </c>
+      <c r="G42" s="22" t="s">
         <v>415</v>
-      </c>
-      <c r="G42" s="22" t="s">
-        <v>416</v>
       </c>
     </row>
     <row r="43" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A43" s="18" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="B43" s="19" t="s">
         <v>242</v>
@@ -10363,15 +10364,15 @@
         <v>50</v>
       </c>
       <c r="F43" s="19" t="s">
+        <v>414</v>
+      </c>
+      <c r="G43" s="22" t="s">
         <v>415</v>
-      </c>
-      <c r="G43" s="22" t="s">
-        <v>416</v>
       </c>
     </row>
     <row r="44" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A44" s="18" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="B44" s="19" t="s">
         <v>13</v>
@@ -10386,15 +10387,15 @@
         <v>55</v>
       </c>
       <c r="F44" s="19" t="s">
+        <v>414</v>
+      </c>
+      <c r="G44" s="22" t="s">
         <v>415</v>
-      </c>
-      <c r="G44" s="22" t="s">
-        <v>416</v>
       </c>
     </row>
     <row r="45" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A45" s="18" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="B45" s="19" t="s">
         <v>13</v>
@@ -10409,15 +10410,15 @@
         <v>53</v>
       </c>
       <c r="F45" s="19" t="s">
+        <v>414</v>
+      </c>
+      <c r="G45" s="22" t="s">
         <v>415</v>
-      </c>
-      <c r="G45" s="22" t="s">
-        <v>416</v>
       </c>
     </row>
     <row r="46" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A46" s="18" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="B46" s="19" t="s">
         <v>242</v>
@@ -10432,15 +10433,15 @@
         <v>156</v>
       </c>
       <c r="F46" s="19" t="s">
+        <v>414</v>
+      </c>
+      <c r="G46" s="22" t="s">
         <v>415</v>
-      </c>
-      <c r="G46" s="22" t="s">
-        <v>416</v>
       </c>
     </row>
     <row r="47" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A47" s="18" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="B47" s="19" t="s">
         <v>242</v>
@@ -10455,15 +10456,15 @@
         <v>158</v>
       </c>
       <c r="F47" s="19" t="s">
+        <v>414</v>
+      </c>
+      <c r="G47" s="22" t="s">
         <v>415</v>
-      </c>
-      <c r="G47" s="22" t="s">
-        <v>416</v>
       </c>
     </row>
     <row r="48" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A48" s="18" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="B48" s="19" t="s">
         <v>99</v>
@@ -10478,15 +10479,15 @@
         <v>156</v>
       </c>
       <c r="F48" s="19" t="s">
+        <v>414</v>
+      </c>
+      <c r="G48" s="22" t="s">
         <v>415</v>
-      </c>
-      <c r="G48" s="22" t="s">
-        <v>416</v>
       </c>
     </row>
     <row r="49" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A49" s="18" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="B49" s="19" t="s">
         <v>99</v>
@@ -10501,15 +10502,15 @@
         <v>158</v>
       </c>
       <c r="F49" s="19" t="s">
+        <v>414</v>
+      </c>
+      <c r="G49" s="22" t="s">
         <v>415</v>
-      </c>
-      <c r="G49" s="22" t="s">
-        <v>416</v>
       </c>
     </row>
     <row r="50" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A50" s="18" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="B50" s="19" t="s">
         <v>293</v>
@@ -10524,15 +10525,15 @@
         <v>297</v>
       </c>
       <c r="F50" s="19" t="s">
+        <v>414</v>
+      </c>
+      <c r="G50" s="22" t="s">
         <v>415</v>
-      </c>
-      <c r="G50" s="22" t="s">
-        <v>416</v>
       </c>
     </row>
     <row r="51" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A51" s="18" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="B51" s="19" t="s">
         <v>99</v>
@@ -10547,15 +10548,15 @@
         <v>129</v>
       </c>
       <c r="F51" s="19" t="s">
+        <v>414</v>
+      </c>
+      <c r="G51" s="22" t="s">
         <v>415</v>
-      </c>
-      <c r="G51" s="22" t="s">
-        <v>416</v>
       </c>
     </row>
     <row r="52" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A52" s="18" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="B52" s="19" t="s">
         <v>166</v>
@@ -10570,15 +10571,15 @@
         <v>217</v>
       </c>
       <c r="F52" s="19" t="s">
+        <v>414</v>
+      </c>
+      <c r="G52" s="22" t="s">
         <v>415</v>
-      </c>
-      <c r="G52" s="22" t="s">
-        <v>416</v>
       </c>
     </row>
     <row r="53" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="42" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="B53" s="39"/>
       <c r="C53" s="39"/>
@@ -10589,7 +10590,7 @@
     </row>
     <row r="54" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A54" s="18" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="B54" s="19" t="s">
         <v>13</v>
@@ -10598,7 +10599,7 @@
         <v>155</v>
       </c>
       <c r="D54" s="24" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="E54" s="19" t="s">
         <v>156</v>
@@ -10607,12 +10608,12 @@
         <v>360</v>
       </c>
       <c r="G54" s="22" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="55" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A55" s="18" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="B55" s="19" t="s">
         <v>13</v>
@@ -10621,7 +10622,7 @@
         <v>157</v>
       </c>
       <c r="D55" s="24" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="E55" s="19" t="s">
         <v>158</v>
@@ -10630,12 +10631,12 @@
         <v>360</v>
       </c>
       <c r="G55" s="22" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="56" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A56" s="18" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="B56" s="19" t="s">
         <v>13</v>
@@ -10644,21 +10645,21 @@
         <v>153</v>
       </c>
       <c r="D56" s="24" t="s">
+        <v>427</v>
+      </c>
+      <c r="E56" s="19" t="s">
         <v>428</v>
-      </c>
-      <c r="E56" s="19" t="s">
-        <v>429</v>
       </c>
       <c r="F56" s="19" t="s">
         <v>360</v>
       </c>
       <c r="G56" s="22" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="57" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A57" s="18" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="B57" s="19" t="s">
         <v>13</v>
@@ -10667,21 +10668,21 @@
         <v>144</v>
       </c>
       <c r="D57" s="24" t="s">
+        <v>429</v>
+      </c>
+      <c r="E57" s="19" t="s">
         <v>430</v>
-      </c>
-      <c r="E57" s="19" t="s">
-        <v>431</v>
       </c>
       <c r="F57" s="19" t="s">
         <v>360</v>
       </c>
       <c r="G57" s="22" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="58" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A58" s="18" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="B58" s="19" t="s">
         <v>13</v>
@@ -10690,21 +10691,21 @@
         <v>208</v>
       </c>
       <c r="D58" s="24" t="s">
+        <v>431</v>
+      </c>
+      <c r="E58" s="19" t="s">
         <v>432</v>
-      </c>
-      <c r="E58" s="19" t="s">
-        <v>433</v>
       </c>
       <c r="F58" s="19" t="s">
         <v>360</v>
       </c>
       <c r="G58" s="22" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="59" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A59" s="18" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="B59" s="19" t="s">
         <v>13</v>
@@ -10713,67 +10714,67 @@
         <v>147</v>
       </c>
       <c r="D59" s="24" t="s">
+        <v>433</v>
+      </c>
+      <c r="E59" s="19" t="s">
         <v>434</v>
-      </c>
-      <c r="E59" s="19" t="s">
-        <v>435</v>
       </c>
       <c r="F59" s="19" t="s">
         <v>360</v>
       </c>
       <c r="G59" s="22" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="60" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A60" s="18" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="B60" s="19" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="C60" s="20" t="s">
         <v>208</v>
       </c>
       <c r="D60" s="24" t="s">
+        <v>436</v>
+      </c>
+      <c r="E60" s="19" t="s">
         <v>437</v>
-      </c>
-      <c r="E60" s="19" t="s">
-        <v>438</v>
       </c>
       <c r="F60" s="19" t="s">
         <v>360</v>
       </c>
       <c r="G60" s="22" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="61" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A61" s="18" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="B61" s="19" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="C61" s="20" t="s">
         <v>208</v>
       </c>
       <c r="D61" s="24" t="s">
+        <v>439</v>
+      </c>
+      <c r="E61" s="19" t="s">
         <v>440</v>
-      </c>
-      <c r="E61" s="19" t="s">
-        <v>441</v>
       </c>
       <c r="F61" s="19" t="s">
         <v>360</v>
       </c>
       <c r="G61" s="22" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="62" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="42" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="B62" s="39"/>
       <c r="C62" s="39"/>
@@ -10784,7 +10785,7 @@
     </row>
     <row r="63" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A63" s="18" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="B63" s="19" t="s">
         <v>13</v>
@@ -10793,21 +10794,21 @@
         <v>30</v>
       </c>
       <c r="D63" s="28" t="s">
+        <v>443</v>
+      </c>
+      <c r="E63" s="19" t="s">
         <v>444</v>
       </c>
-      <c r="E63" s="19" t="s">
+      <c r="F63" s="19" t="s">
+        <v>442</v>
+      </c>
+      <c r="G63" s="22" t="s">
         <v>445</v>
-      </c>
-      <c r="F63" s="19" t="s">
-        <v>443</v>
-      </c>
-      <c r="G63" s="22" t="s">
-        <v>446</v>
       </c>
     </row>
     <row r="64" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A64" s="18" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="B64" s="19" t="s">
         <v>13</v>
@@ -10816,44 +10817,44 @@
         <v>27</v>
       </c>
       <c r="D64" s="28" t="s">
+        <v>446</v>
+      </c>
+      <c r="E64" s="19" t="s">
         <v>447</v>
       </c>
-      <c r="E64" s="19" t="s">
-        <v>448</v>
-      </c>
       <c r="F64" s="19" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="G64" s="22" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
     </row>
     <row r="65" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A65" s="18" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="B65" s="19" t="s">
         <v>13</v>
       </c>
       <c r="C65" s="20" t="s">
+        <v>448</v>
+      </c>
+      <c r="D65" s="28" t="s">
         <v>449</v>
       </c>
-      <c r="D65" s="28" t="s">
+      <c r="E65" s="19" t="s">
         <v>450</v>
       </c>
-      <c r="E65" s="19" t="s">
-        <v>451</v>
-      </c>
       <c r="F65" s="19" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="G65" s="22" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
     </row>
     <row r="66" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A66" s="18" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="B66" s="19" t="s">
         <v>13</v>
@@ -10862,136 +10863,136 @@
         <v>110</v>
       </c>
       <c r="D66" s="28" t="s">
+        <v>451</v>
+      </c>
+      <c r="E66" s="19" t="s">
         <v>452</v>
       </c>
-      <c r="E66" s="19" t="s">
-        <v>453</v>
-      </c>
       <c r="F66" s="19" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="G66" s="22" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
     </row>
     <row r="67" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A67" s="18" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="B67" s="19" t="s">
         <v>13</v>
       </c>
       <c r="C67" s="20" t="s">
+        <v>453</v>
+      </c>
+      <c r="D67" s="28" t="s">
+        <v>451</v>
+      </c>
+      <c r="E67" s="19" t="s">
         <v>454</v>
       </c>
-      <c r="D67" s="28" t="s">
-        <v>452</v>
-      </c>
-      <c r="E67" s="19" t="s">
-        <v>455</v>
-      </c>
       <c r="F67" s="19" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="G67" s="22" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
     </row>
     <row r="68" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A68" s="18" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="B68" s="19" t="s">
         <v>13</v>
       </c>
       <c r="C68" s="20" t="s">
+        <v>455</v>
+      </c>
+      <c r="D68" s="28" t="s">
         <v>456</v>
       </c>
-      <c r="D68" s="28" t="s">
+      <c r="E68" s="19" t="s">
         <v>457</v>
       </c>
-      <c r="E68" s="19" t="s">
-        <v>458</v>
-      </c>
       <c r="F68" s="19" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="G68" s="22" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
     </row>
     <row r="69" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A69" s="18" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="B69" s="19" t="s">
         <v>13</v>
       </c>
       <c r="C69" s="20" t="s">
+        <v>458</v>
+      </c>
+      <c r="D69" s="28" t="s">
         <v>459</v>
       </c>
-      <c r="D69" s="28" t="s">
+      <c r="E69" s="19" t="s">
         <v>460</v>
       </c>
-      <c r="E69" s="19" t="s">
-        <v>461</v>
-      </c>
       <c r="F69" s="19" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="G69" s="22" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
     </row>
     <row r="70" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A70" s="18" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="B70" s="19" t="s">
         <v>13</v>
       </c>
       <c r="C70" s="20" t="s">
+        <v>461</v>
+      </c>
+      <c r="D70" s="28" t="s">
         <v>462</v>
       </c>
-      <c r="D70" s="28" t="s">
+      <c r="E70" s="19" t="s">
         <v>463</v>
       </c>
-      <c r="E70" s="19" t="s">
-        <v>464</v>
-      </c>
       <c r="F70" s="19" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="G70" s="22" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
     </row>
     <row r="71" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A71" s="18" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="B71" s="19" t="s">
         <v>13</v>
       </c>
       <c r="C71" s="20" t="s">
+        <v>464</v>
+      </c>
+      <c r="D71" s="28" t="s">
         <v>465</v>
       </c>
-      <c r="D71" s="28" t="s">
+      <c r="E71" s="19" t="s">
         <v>466</v>
       </c>
-      <c r="E71" s="19" t="s">
-        <v>467</v>
-      </c>
       <c r="F71" s="19" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="G71" s="22" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
     </row>
     <row r="72" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A72" s="18" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="B72" s="19" t="s">
         <v>13</v>
@@ -11000,21 +11001,21 @@
         <v>142</v>
       </c>
       <c r="D72" s="28" t="s">
+        <v>467</v>
+      </c>
+      <c r="E72" s="19" t="s">
         <v>468</v>
       </c>
-      <c r="E72" s="19" t="s">
-        <v>469</v>
-      </c>
       <c r="F72" s="19" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="G72" s="22" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
     </row>
     <row r="73" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A73" s="18" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="B73" s="19" t="s">
         <v>13</v>
@@ -11023,21 +11024,21 @@
         <v>140</v>
       </c>
       <c r="D73" s="28" t="s">
+        <v>469</v>
+      </c>
+      <c r="E73" s="19" t="s">
         <v>470</v>
       </c>
-      <c r="E73" s="19" t="s">
-        <v>471</v>
-      </c>
       <c r="F73" s="19" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="G73" s="22" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
     </row>
     <row r="74" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A74" s="18" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="B74" s="19" t="s">
         <v>74</v>
@@ -11046,21 +11047,21 @@
         <v>30</v>
       </c>
       <c r="D74" s="28" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="E74" s="19" t="s">
         <v>276</v>
       </c>
       <c r="F74" s="19" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="G74" s="22" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
     </row>
     <row r="75" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A75" s="18" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="B75" s="19" t="s">
         <v>74</v>
@@ -11069,21 +11070,21 @@
         <v>27</v>
       </c>
       <c r="D75" s="28" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="E75" s="19" t="s">
         <v>274</v>
       </c>
       <c r="F75" s="19" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="G75" s="22" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
     </row>
     <row r="76" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="42" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="B76" s="39"/>
       <c r="C76" s="39"/>
@@ -11094,7 +11095,7 @@
     </row>
     <row r="77" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A77" s="18" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="B77" s="19" t="s">
         <v>13</v>
@@ -11103,21 +11104,21 @@
         <v>151</v>
       </c>
       <c r="D77" s="29" t="s">
+        <v>475</v>
+      </c>
+      <c r="E77" s="19" t="s">
         <v>476</v>
       </c>
-      <c r="E77" s="19" t="s">
+      <c r="F77" s="19" t="s">
+        <v>474</v>
+      </c>
+      <c r="G77" s="22" t="s">
         <v>477</v>
-      </c>
-      <c r="F77" s="19" t="s">
-        <v>475</v>
-      </c>
-      <c r="G77" s="22" t="s">
-        <v>478</v>
       </c>
     </row>
     <row r="78" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A78" s="18" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="B78" s="19" t="s">
         <v>74</v>
@@ -11126,21 +11127,21 @@
         <v>151</v>
       </c>
       <c r="D78" s="29" t="s">
+        <v>478</v>
+      </c>
+      <c r="E78" s="19" t="s">
         <v>479</v>
       </c>
-      <c r="E78" s="19" t="s">
-        <v>480</v>
-      </c>
       <c r="F78" s="19" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="G78" s="22" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
     </row>
     <row r="79" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A79" s="18" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="B79" s="19" t="s">
         <v>13</v>
@@ -11149,21 +11150,21 @@
         <v>193</v>
       </c>
       <c r="D79" s="29" t="s">
+        <v>480</v>
+      </c>
+      <c r="E79" s="19" t="s">
         <v>481</v>
       </c>
-      <c r="E79" s="19" t="s">
-        <v>482</v>
-      </c>
       <c r="F79" s="19" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="G79" s="22" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
     </row>
     <row r="80" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A80" s="18" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="B80" s="19" t="s">
         <v>74</v>
@@ -11172,21 +11173,21 @@
         <v>193</v>
       </c>
       <c r="D80" s="29" t="s">
+        <v>482</v>
+      </c>
+      <c r="E80" s="19" t="s">
         <v>483</v>
       </c>
-      <c r="E80" s="19" t="s">
-        <v>484</v>
-      </c>
       <c r="F80" s="19" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="G80" s="22" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
     </row>
     <row r="81" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A81" s="18" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="B81" s="19" t="s">
         <v>13</v>
@@ -11195,21 +11196,21 @@
         <v>112</v>
       </c>
       <c r="D81" s="29" t="s">
+        <v>484</v>
+      </c>
+      <c r="E81" s="19" t="s">
         <v>485</v>
       </c>
-      <c r="E81" s="19" t="s">
-        <v>486</v>
-      </c>
       <c r="F81" s="19" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="G81" s="22" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
     </row>
     <row r="82" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A82" s="18" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="B82" s="19" t="s">
         <v>74</v>
@@ -11218,21 +11219,21 @@
         <v>112</v>
       </c>
       <c r="D82" s="29" t="s">
+        <v>486</v>
+      </c>
+      <c r="E82" s="19" t="s">
         <v>487</v>
       </c>
-      <c r="E82" s="19" t="s">
-        <v>488</v>
-      </c>
       <c r="F82" s="19" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="G82" s="22" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
     </row>
     <row r="83" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A83" s="18" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="B83" s="19" t="s">
         <v>13</v>
@@ -11241,21 +11242,21 @@
         <v>137</v>
       </c>
       <c r="D83" s="29" t="s">
+        <v>488</v>
+      </c>
+      <c r="E83" s="19" t="s">
         <v>489</v>
       </c>
-      <c r="E83" s="19" t="s">
-        <v>490</v>
-      </c>
       <c r="F83" s="19" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="G83" s="22" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
     </row>
     <row r="84" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A84" s="18" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="B84" s="19" t="s">
         <v>74</v>
@@ -11264,21 +11265,21 @@
         <v>137</v>
       </c>
       <c r="D84" s="29" t="s">
+        <v>490</v>
+      </c>
+      <c r="E84" s="19" t="s">
         <v>491</v>
       </c>
-      <c r="E84" s="19" t="s">
-        <v>492</v>
-      </c>
       <c r="F84" s="19" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="G84" s="22" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
     </row>
     <row r="85" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A85" s="18" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="B85" s="19" t="s">
         <v>13</v>
@@ -11287,21 +11288,21 @@
         <v>215</v>
       </c>
       <c r="D85" s="29" t="s">
+        <v>492</v>
+      </c>
+      <c r="E85" s="19" t="s">
         <v>493</v>
       </c>
-      <c r="E85" s="19" t="s">
-        <v>494</v>
-      </c>
       <c r="F85" s="19" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="G85" s="22" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
     </row>
     <row r="86" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A86" s="18" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="B86" s="19" t="s">
         <v>74</v>
@@ -11310,21 +11311,21 @@
         <v>215</v>
       </c>
       <c r="D86" s="29" t="s">
+        <v>494</v>
+      </c>
+      <c r="E86" s="19" t="s">
         <v>495</v>
       </c>
-      <c r="E86" s="19" t="s">
-        <v>496</v>
-      </c>
       <c r="F86" s="19" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="G86" s="22" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
     </row>
     <row r="87" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A87" s="18" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="B87" s="19" t="s">
         <v>13</v>
@@ -11333,44 +11334,44 @@
         <v>218</v>
       </c>
       <c r="D87" s="29" t="s">
+        <v>496</v>
+      </c>
+      <c r="E87" s="19" t="s">
         <v>497</v>
       </c>
-      <c r="E87" s="19" t="s">
-        <v>498</v>
-      </c>
       <c r="F87" s="19" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="G87" s="22" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
     </row>
     <row r="88" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A88" s="18" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="B88" s="19" t="s">
         <v>13</v>
       </c>
       <c r="C88" s="20" t="s">
+        <v>498</v>
+      </c>
+      <c r="D88" s="29" t="s">
         <v>499</v>
       </c>
-      <c r="D88" s="29" t="s">
+      <c r="E88" s="19" t="s">
         <v>500</v>
       </c>
-      <c r="E88" s="19" t="s">
-        <v>501</v>
-      </c>
       <c r="F88" s="19" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="G88" s="22" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
     </row>
     <row r="89" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="42" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="B89" s="39"/>
       <c r="C89" s="39"/>
@@ -11381,7 +11382,7 @@
     </row>
     <row r="90" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A90" s="18" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="B90" s="19" t="s">
         <v>166</v>
@@ -11390,21 +11391,21 @@
         <v>205</v>
       </c>
       <c r="D90" s="30" t="s">
+        <v>503</v>
+      </c>
+      <c r="E90" s="19" t="s">
         <v>504</v>
-      </c>
-      <c r="E90" s="19" t="s">
-        <v>505</v>
       </c>
       <c r="F90" s="19" t="s">
         <v>378</v>
       </c>
       <c r="G90" s="22" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
     </row>
     <row r="91" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A91" s="18" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="B91" s="19" t="s">
         <v>166</v>
@@ -11413,21 +11414,21 @@
         <v>218</v>
       </c>
       <c r="D91" s="30" t="s">
+        <v>506</v>
+      </c>
+      <c r="E91" s="19" t="s">
         <v>507</v>
-      </c>
-      <c r="E91" s="19" t="s">
-        <v>508</v>
       </c>
       <c r="F91" s="19" t="s">
         <v>378</v>
       </c>
       <c r="G91" s="22" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
     </row>
     <row r="92" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A92" s="18" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="B92" s="19" t="s">
         <v>166</v>
@@ -11436,21 +11437,21 @@
         <v>114</v>
       </c>
       <c r="D92" s="30" t="s">
+        <v>508</v>
+      </c>
+      <c r="E92" s="19" t="s">
         <v>509</v>
-      </c>
-      <c r="E92" s="19" t="s">
-        <v>510</v>
       </c>
       <c r="F92" s="19" t="s">
         <v>378</v>
       </c>
       <c r="G92" s="22" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
     </row>
     <row r="93" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A93" s="18" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="B93" s="19" t="s">
         <v>166</v>
@@ -11459,21 +11460,21 @@
         <v>193</v>
       </c>
       <c r="D93" s="30" t="s">
+        <v>510</v>
+      </c>
+      <c r="E93" s="19" t="s">
         <v>511</v>
-      </c>
-      <c r="E93" s="19" t="s">
-        <v>512</v>
       </c>
       <c r="F93" s="19" t="s">
         <v>378</v>
       </c>
       <c r="G93" s="22" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
     </row>
     <row r="94" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A94" s="18" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="B94" s="19" t="s">
         <v>268</v>
@@ -11482,21 +11483,21 @@
         <v>193</v>
       </c>
       <c r="D94" s="30" t="s">
+        <v>512</v>
+      </c>
+      <c r="E94" s="19" t="s">
         <v>513</v>
-      </c>
-      <c r="E94" s="19" t="s">
-        <v>514</v>
       </c>
       <c r="F94" s="19" t="s">
         <v>378</v>
       </c>
       <c r="G94" s="22" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
     </row>
     <row r="95" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A95" s="18" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="B95" s="19" t="s">
         <v>13</v>
@@ -11505,21 +11506,21 @@
         <v>155</v>
       </c>
       <c r="D95" s="30" t="s">
+        <v>514</v>
+      </c>
+      <c r="E95" s="19" t="s">
         <v>515</v>
-      </c>
-      <c r="E95" s="19" t="s">
-        <v>516</v>
       </c>
       <c r="F95" s="19" t="s">
         <v>378</v>
       </c>
       <c r="G95" s="22" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
     </row>
     <row r="96" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A96" s="18" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="B96" s="19" t="s">
         <v>13</v>
@@ -11528,16 +11529,16 @@
         <v>157</v>
       </c>
       <c r="D96" s="30" t="s">
+        <v>516</v>
+      </c>
+      <c r="E96" s="19" t="s">
         <v>517</v>
-      </c>
-      <c r="E96" s="19" t="s">
-        <v>518</v>
       </c>
       <c r="F96" s="19" t="s">
         <v>378</v>
       </c>
       <c r="G96" s="22" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
     </row>
   </sheetData>
@@ -11571,7 +11572,7 @@
   <sheetData>
     <row r="1" spans="1:9" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A1" s="47" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="B1" s="39"/>
       <c r="C1" s="39"/>
@@ -11583,7 +11584,7 @@
     </row>
     <row r="2" spans="1:9" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A2" s="41" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="B2" s="39"/>
       <c r="C2" s="39"/>
@@ -11601,30 +11602,30 @@
         <v>3</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="D3" s="1" t="s">
+        <v>520</v>
+      </c>
+      <c r="E3" s="1" t="s">
         <v>521</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="F3" s="1" t="s">
         <v>522</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="G3" s="1" t="s">
         <v>523</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="H3" s="1" t="s">
         <v>524</v>
       </c>
-      <c r="H3" s="1" t="s">
+      <c r="I3" s="1" t="s">
         <v>525</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>526</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="38" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="B4" s="39"/>
       <c r="C4" s="39"/>
@@ -11647,13 +11648,13 @@
       <c r="E5" s="32"/>
       <c r="F5" s="33"/>
       <c r="G5" s="34" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H5" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I5" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -11668,13 +11669,13 @@
       <c r="E6" s="32"/>
       <c r="F6" s="33"/>
       <c r="G6" s="34" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H6" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I6" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -11689,13 +11690,13 @@
       <c r="E7" s="32"/>
       <c r="F7" s="33"/>
       <c r="G7" s="34" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H7" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I7" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -11710,13 +11711,13 @@
       <c r="E8" s="32"/>
       <c r="F8" s="33"/>
       <c r="G8" s="34" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H8" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I8" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -11731,13 +11732,13 @@
       <c r="E9" s="32"/>
       <c r="F9" s="33"/>
       <c r="G9" s="34" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H9" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I9" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -11752,13 +11753,13 @@
       <c r="E10" s="32"/>
       <c r="F10" s="33"/>
       <c r="G10" s="34" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H10" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I10" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -11773,13 +11774,13 @@
       <c r="E11" s="32"/>
       <c r="F11" s="33"/>
       <c r="G11" s="34" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H11" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I11" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -11794,13 +11795,13 @@
       <c r="E12" s="32"/>
       <c r="F12" s="33"/>
       <c r="G12" s="34" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H12" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I12" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -11815,13 +11816,13 @@
       <c r="E13" s="32"/>
       <c r="F13" s="33"/>
       <c r="G13" s="34" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H13" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I13" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -11829,20 +11830,20 @@
         <v>13</v>
       </c>
       <c r="B14" s="20" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="C14" s="19"/>
       <c r="D14" s="31"/>
       <c r="E14" s="32"/>
       <c r="F14" s="33"/>
       <c r="G14" s="34" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H14" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I14" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -11857,13 +11858,13 @@
       <c r="E15" s="32"/>
       <c r="F15" s="33"/>
       <c r="G15" s="34" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H15" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I15" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="16" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -11878,13 +11879,13 @@
       <c r="E16" s="32"/>
       <c r="F16" s="33"/>
       <c r="G16" s="34" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H16" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I16" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="17" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -11899,13 +11900,13 @@
       <c r="E17" s="32"/>
       <c r="F17" s="33"/>
       <c r="G17" s="34" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H17" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I17" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="18" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -11920,13 +11921,13 @@
       <c r="E18" s="32"/>
       <c r="F18" s="33"/>
       <c r="G18" s="34" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H18" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I18" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="19" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -11934,20 +11935,20 @@
         <v>13</v>
       </c>
       <c r="B19" s="20" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="C19" s="19"/>
       <c r="D19" s="31"/>
       <c r="E19" s="32"/>
       <c r="F19" s="33"/>
       <c r="G19" s="34" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H19" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I19" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="20" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -11962,13 +11963,13 @@
       <c r="E20" s="32"/>
       <c r="F20" s="33"/>
       <c r="G20" s="34" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H20" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I20" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="21" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -11983,13 +11984,13 @@
       <c r="E21" s="32"/>
       <c r="F21" s="33"/>
       <c r="G21" s="34" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H21" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I21" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="22" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -12004,13 +12005,13 @@
       <c r="E22" s="32"/>
       <c r="F22" s="33"/>
       <c r="G22" s="34" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H22" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I22" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="23" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -12025,13 +12026,13 @@
       <c r="E23" s="32"/>
       <c r="F23" s="33"/>
       <c r="G23" s="34" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H23" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I23" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="24" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -12046,13 +12047,13 @@
       <c r="E24" s="32"/>
       <c r="F24" s="33"/>
       <c r="G24" s="34" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H24" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I24" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="25" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -12060,20 +12061,20 @@
         <v>13</v>
       </c>
       <c r="B25" s="20" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="C25" s="19"/>
       <c r="D25" s="31"/>
       <c r="E25" s="32"/>
       <c r="F25" s="33"/>
       <c r="G25" s="34" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H25" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I25" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="26" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -12088,13 +12089,13 @@
       <c r="E26" s="32"/>
       <c r="F26" s="33"/>
       <c r="G26" s="34" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H26" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I26" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="27" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -12109,13 +12110,13 @@
       <c r="E27" s="32"/>
       <c r="F27" s="33"/>
       <c r="G27" s="34" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H27" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I27" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="28" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -12130,13 +12131,13 @@
       <c r="E28" s="32"/>
       <c r="F28" s="33"/>
       <c r="G28" s="34" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H28" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I28" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="29" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -12151,13 +12152,13 @@
       <c r="E29" s="32"/>
       <c r="F29" s="33"/>
       <c r="G29" s="34" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H29" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I29" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="30" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -12172,13 +12173,13 @@
       <c r="E30" s="32"/>
       <c r="F30" s="33"/>
       <c r="G30" s="34" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H30" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I30" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="31" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -12190,16 +12191,16 @@
       </c>
       <c r="C31" s="19"/>
       <c r="D31" s="23" t="s">
+        <v>529</v>
+      </c>
+      <c r="E31" s="25" t="s">
         <v>530</v>
-      </c>
-      <c r="E31" s="25" t="s">
-        <v>531</v>
       </c>
       <c r="F31" s="33"/>
       <c r="G31" s="37"/>
       <c r="H31" s="37"/>
       <c r="I31" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="32" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -12212,15 +12213,15 @@
       <c r="C32" s="19"/>
       <c r="D32" s="31"/>
       <c r="E32" s="25" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="F32" s="33"/>
       <c r="G32" s="34" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H32" s="37"/>
       <c r="I32" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="33" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -12233,15 +12234,15 @@
       <c r="C33" s="19"/>
       <c r="D33" s="31"/>
       <c r="E33" s="25" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="F33" s="33"/>
       <c r="G33" s="34" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H33" s="37"/>
       <c r="I33" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="34" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -12254,15 +12255,15 @@
       <c r="C34" s="19"/>
       <c r="D34" s="31"/>
       <c r="E34" s="25" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="F34" s="33"/>
       <c r="G34" s="34" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H34" s="37"/>
       <c r="I34" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="35" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -12270,20 +12271,20 @@
         <v>13</v>
       </c>
       <c r="B35" s="20" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="C35" s="19"/>
       <c r="D35" s="31"/>
       <c r="E35" s="32"/>
       <c r="F35" s="33"/>
       <c r="G35" s="34" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H35" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I35" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="36" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -12291,20 +12292,20 @@
         <v>13</v>
       </c>
       <c r="B36" s="20" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="C36" s="19"/>
       <c r="D36" s="31"/>
       <c r="E36" s="32"/>
       <c r="F36" s="33"/>
       <c r="G36" s="34" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H36" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I36" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="37" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -12312,20 +12313,20 @@
         <v>13</v>
       </c>
       <c r="B37" s="20" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="C37" s="19"/>
       <c r="D37" s="31"/>
       <c r="E37" s="32"/>
       <c r="F37" s="33"/>
       <c r="G37" s="34" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H37" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I37" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="38" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -12333,20 +12334,20 @@
         <v>13</v>
       </c>
       <c r="B38" s="20" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="C38" s="19"/>
       <c r="D38" s="31"/>
       <c r="E38" s="32"/>
       <c r="F38" s="33"/>
       <c r="G38" s="34" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H38" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I38" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="39" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -12354,20 +12355,20 @@
         <v>13</v>
       </c>
       <c r="B39" s="20" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="C39" s="19"/>
       <c r="D39" s="31"/>
       <c r="E39" s="32"/>
       <c r="F39" s="33"/>
       <c r="G39" s="34" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H39" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I39" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="40" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -12380,15 +12381,15 @@
       <c r="C40" s="19"/>
       <c r="D40" s="31"/>
       <c r="E40" s="25" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="F40" s="33"/>
       <c r="G40" s="34" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H40" s="37"/>
       <c r="I40" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="41" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -12402,13 +12403,13 @@
       <c r="D41" s="31"/>
       <c r="E41" s="32"/>
       <c r="F41" s="26" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="G41" s="34" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H41" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I41" s="37"/>
     </row>
@@ -12421,16 +12422,16 @@
       </c>
       <c r="C42" s="19"/>
       <c r="D42" s="23" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="E42" s="32"/>
       <c r="F42" s="33"/>
       <c r="G42" s="37"/>
       <c r="H42" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I42" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="43" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -12442,16 +12443,16 @@
       </c>
       <c r="C43" s="19"/>
       <c r="D43" s="23" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="E43" s="32"/>
       <c r="F43" s="33"/>
       <c r="G43" s="37"/>
       <c r="H43" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I43" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="44" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -12459,20 +12460,20 @@
         <v>13</v>
       </c>
       <c r="B44" s="20" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="C44" s="19"/>
       <c r="D44" s="31"/>
       <c r="E44" s="32"/>
       <c r="F44" s="33"/>
       <c r="G44" s="34" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H44" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I44" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="45" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -12480,25 +12481,25 @@
         <v>13</v>
       </c>
       <c r="B45" s="20" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="C45" s="19"/>
       <c r="D45" s="31"/>
       <c r="E45" s="32"/>
       <c r="F45" s="33"/>
       <c r="G45" s="34" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H45" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I45" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="46" spans="1:9" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="38" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="B46" s="39"/>
       <c r="C46" s="39"/>
@@ -12521,13 +12522,13 @@
       <c r="E47" s="32"/>
       <c r="F47" s="33"/>
       <c r="G47" s="34" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H47" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I47" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="48" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -12542,13 +12543,13 @@
       <c r="E48" s="32"/>
       <c r="F48" s="33"/>
       <c r="G48" s="34" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H48" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I48" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="49" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -12563,13 +12564,13 @@
       <c r="E49" s="32"/>
       <c r="F49" s="33"/>
       <c r="G49" s="34" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H49" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I49" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="50" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -12584,13 +12585,13 @@
       <c r="E50" s="32"/>
       <c r="F50" s="33"/>
       <c r="G50" s="34" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H50" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I50" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="51" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -12605,13 +12606,13 @@
       <c r="E51" s="32"/>
       <c r="F51" s="33"/>
       <c r="G51" s="34" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H51" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I51" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="52" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -12626,13 +12627,13 @@
       <c r="E52" s="32"/>
       <c r="F52" s="33"/>
       <c r="G52" s="34" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H52" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I52" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="53" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -12647,13 +12648,13 @@
       <c r="E53" s="32"/>
       <c r="F53" s="33"/>
       <c r="G53" s="34" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H53" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I53" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="54" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -12668,13 +12669,13 @@
       <c r="E54" s="32"/>
       <c r="F54" s="33"/>
       <c r="G54" s="34" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H54" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I54" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="55" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -12689,13 +12690,13 @@
       <c r="E55" s="32"/>
       <c r="F55" s="33"/>
       <c r="G55" s="34" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H55" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I55" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="56" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -12703,20 +12704,20 @@
         <v>74</v>
       </c>
       <c r="B56" s="20" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="C56" s="19"/>
       <c r="D56" s="31"/>
       <c r="E56" s="32"/>
       <c r="F56" s="33"/>
       <c r="G56" s="34" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H56" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I56" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="57" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -12731,13 +12732,13 @@
       <c r="E57" s="32"/>
       <c r="F57" s="33"/>
       <c r="G57" s="34" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H57" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I57" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="58" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -12752,13 +12753,13 @@
       <c r="E58" s="32"/>
       <c r="F58" s="33"/>
       <c r="G58" s="34" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H58" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I58" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="59" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -12773,13 +12774,13 @@
       <c r="E59" s="32"/>
       <c r="F59" s="33"/>
       <c r="G59" s="34" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H59" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I59" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="60" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -12794,13 +12795,13 @@
       <c r="E60" s="32"/>
       <c r="F60" s="33"/>
       <c r="G60" s="34" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H60" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I60" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="61" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -12808,20 +12809,20 @@
         <v>74</v>
       </c>
       <c r="B61" s="20" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="C61" s="19"/>
       <c r="D61" s="31"/>
       <c r="E61" s="32"/>
       <c r="F61" s="33"/>
       <c r="G61" s="34" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H61" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I61" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="62" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -12836,13 +12837,13 @@
       <c r="E62" s="32"/>
       <c r="F62" s="33"/>
       <c r="G62" s="34" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H62" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I62" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="63" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -12857,13 +12858,13 @@
       <c r="E63" s="32"/>
       <c r="F63" s="33"/>
       <c r="G63" s="34" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H63" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I63" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="64" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -12878,13 +12879,13 @@
       <c r="E64" s="32"/>
       <c r="F64" s="33"/>
       <c r="G64" s="34" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H64" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I64" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="65" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -12899,13 +12900,13 @@
       <c r="E65" s="32"/>
       <c r="F65" s="33"/>
       <c r="G65" s="34" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H65" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I65" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="66" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -12920,13 +12921,13 @@
       <c r="E66" s="32"/>
       <c r="F66" s="33"/>
       <c r="G66" s="34" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H66" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I66" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="67" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -12934,20 +12935,20 @@
         <v>74</v>
       </c>
       <c r="B67" s="20" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="C67" s="19"/>
       <c r="D67" s="31"/>
       <c r="E67" s="32"/>
       <c r="F67" s="33"/>
       <c r="G67" s="34" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H67" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I67" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="68" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -12962,13 +12963,13 @@
       <c r="E68" s="32"/>
       <c r="F68" s="33"/>
       <c r="G68" s="34" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H68" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I68" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="69" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -12983,13 +12984,13 @@
       <c r="E69" s="32"/>
       <c r="F69" s="33"/>
       <c r="G69" s="34" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H69" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I69" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="70" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -13004,13 +13005,13 @@
       <c r="E70" s="32"/>
       <c r="F70" s="33"/>
       <c r="G70" s="34" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H70" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I70" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="71" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -13025,13 +13026,13 @@
       <c r="E71" s="32"/>
       <c r="F71" s="33"/>
       <c r="G71" s="34" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H71" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I71" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="72" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -13046,13 +13047,13 @@
       <c r="E72" s="32"/>
       <c r="F72" s="33"/>
       <c r="G72" s="34" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H72" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I72" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="73" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -13065,15 +13066,15 @@
       <c r="C73" s="19"/>
       <c r="D73" s="31"/>
       <c r="E73" s="25" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="F73" s="33"/>
       <c r="G73" s="34" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H73" s="37"/>
       <c r="I73" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="74" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -13086,15 +13087,15 @@
       <c r="C74" s="19"/>
       <c r="D74" s="31"/>
       <c r="E74" s="25" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="F74" s="33"/>
       <c r="G74" s="34" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H74" s="37"/>
       <c r="I74" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="75" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -13107,15 +13108,15 @@
       <c r="C75" s="19"/>
       <c r="D75" s="31"/>
       <c r="E75" s="25" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="F75" s="33"/>
       <c r="G75" s="34" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H75" s="37"/>
       <c r="I75" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="76" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -13128,15 +13129,15 @@
       <c r="C76" s="19"/>
       <c r="D76" s="31"/>
       <c r="E76" s="25" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="F76" s="33"/>
       <c r="G76" s="34" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H76" s="37"/>
       <c r="I76" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="77" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -13149,15 +13150,15 @@
       <c r="C77" s="19"/>
       <c r="D77" s="31"/>
       <c r="E77" s="25" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="F77" s="33"/>
       <c r="G77" s="34" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H77" s="37"/>
       <c r="I77" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="78" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -13165,20 +13166,20 @@
         <v>74</v>
       </c>
       <c r="B78" s="20" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="C78" s="19"/>
       <c r="D78" s="31"/>
       <c r="E78" s="32"/>
       <c r="F78" s="33"/>
       <c r="G78" s="34" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H78" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I78" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="79" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -13186,20 +13187,20 @@
         <v>74</v>
       </c>
       <c r="B79" s="20" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="C79" s="19"/>
       <c r="D79" s="31"/>
       <c r="E79" s="32"/>
       <c r="F79" s="33"/>
       <c r="G79" s="34" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H79" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I79" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="80" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -13207,20 +13208,20 @@
         <v>74</v>
       </c>
       <c r="B80" s="20" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="C80" s="19"/>
       <c r="D80" s="31"/>
       <c r="E80" s="32"/>
       <c r="F80" s="33"/>
       <c r="G80" s="34" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H80" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I80" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="81" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -13228,20 +13229,20 @@
         <v>74</v>
       </c>
       <c r="B81" s="20" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="C81" s="19"/>
       <c r="D81" s="31"/>
       <c r="E81" s="32"/>
       <c r="F81" s="33"/>
       <c r="G81" s="34" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H81" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I81" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="82" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -13249,20 +13250,20 @@
         <v>74</v>
       </c>
       <c r="B82" s="20" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="C82" s="19"/>
       <c r="D82" s="31"/>
       <c r="E82" s="32"/>
       <c r="F82" s="33"/>
       <c r="G82" s="34" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H82" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I82" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="83" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -13277,13 +13278,13 @@
       <c r="E83" s="32"/>
       <c r="F83" s="33"/>
       <c r="G83" s="34" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H83" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I83" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="84" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -13298,13 +13299,13 @@
       <c r="E84" s="32"/>
       <c r="F84" s="33"/>
       <c r="G84" s="34" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H84" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I84" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="85" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -13317,15 +13318,15 @@
       <c r="C85" s="19"/>
       <c r="D85" s="31"/>
       <c r="E85" s="25" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="F85" s="33"/>
       <c r="G85" s="34" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H85" s="37"/>
       <c r="I85" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="86" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -13340,13 +13341,13 @@
       <c r="E86" s="32"/>
       <c r="F86" s="33"/>
       <c r="G86" s="34" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H86" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I86" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="87" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -13358,16 +13359,16 @@
       </c>
       <c r="C87" s="19"/>
       <c r="D87" s="23" t="s">
+        <v>544</v>
+      </c>
+      <c r="E87" s="25" t="s">
         <v>545</v>
-      </c>
-      <c r="E87" s="25" t="s">
-        <v>546</v>
       </c>
       <c r="F87" s="33"/>
       <c r="G87" s="37"/>
       <c r="H87" s="37"/>
       <c r="I87" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="88" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -13379,16 +13380,16 @@
       </c>
       <c r="C88" s="19"/>
       <c r="D88" s="23" t="s">
+        <v>546</v>
+      </c>
+      <c r="E88" s="25" t="s">
         <v>547</v>
-      </c>
-      <c r="E88" s="25" t="s">
-        <v>548</v>
       </c>
       <c r="F88" s="33"/>
       <c r="G88" s="37"/>
       <c r="H88" s="37"/>
       <c r="I88" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="89" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -13400,16 +13401,16 @@
       </c>
       <c r="C89" s="19"/>
       <c r="D89" s="23" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="E89" s="32"/>
       <c r="F89" s="33"/>
       <c r="G89" s="37"/>
       <c r="H89" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I89" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="90" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -13421,16 +13422,16 @@
       </c>
       <c r="C90" s="19"/>
       <c r="D90" s="23" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="E90" s="32"/>
       <c r="F90" s="33"/>
       <c r="G90" s="37"/>
       <c r="H90" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I90" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="91" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -13438,20 +13439,20 @@
         <v>74</v>
       </c>
       <c r="B91" s="20" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="C91" s="19"/>
       <c r="D91" s="31"/>
       <c r="E91" s="32"/>
       <c r="F91" s="33"/>
       <c r="G91" s="34" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H91" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I91" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="92" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -13459,25 +13460,25 @@
         <v>74</v>
       </c>
       <c r="B92" s="20" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="C92" s="19"/>
       <c r="D92" s="31"/>
       <c r="E92" s="32"/>
       <c r="F92" s="33"/>
       <c r="G92" s="34" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H92" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I92" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="93" spans="1:9" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A93" s="38" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="B93" s="39"/>
       <c r="C93" s="39"/>
@@ -13497,16 +13498,16 @@
       </c>
       <c r="C94" s="19"/>
       <c r="D94" s="23" t="s">
+        <v>551</v>
+      </c>
+      <c r="E94" s="25" t="s">
         <v>552</v>
-      </c>
-      <c r="E94" s="25" t="s">
-        <v>553</v>
       </c>
       <c r="F94" s="33"/>
       <c r="G94" s="37"/>
       <c r="H94" s="37"/>
       <c r="I94" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="95" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -13518,16 +13519,16 @@
       </c>
       <c r="C95" s="19"/>
       <c r="D95" s="23" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="E95" s="32"/>
       <c r="F95" s="33"/>
       <c r="G95" s="37"/>
       <c r="H95" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I95" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="96" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -13539,16 +13540,16 @@
       </c>
       <c r="C96" s="19"/>
       <c r="D96" s="23" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="E96" s="32"/>
       <c r="F96" s="33"/>
       <c r="G96" s="37"/>
       <c r="H96" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I96" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="97" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -13560,16 +13561,16 @@
       </c>
       <c r="C97" s="19"/>
       <c r="D97" s="23" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="E97" s="32"/>
       <c r="F97" s="33"/>
       <c r="G97" s="37"/>
       <c r="H97" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I97" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="98" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -13581,16 +13582,16 @@
       </c>
       <c r="C98" s="19"/>
       <c r="D98" s="23" t="s">
+        <v>553</v>
+      </c>
+      <c r="E98" s="25" t="s">
         <v>554</v>
-      </c>
-      <c r="E98" s="25" t="s">
-        <v>555</v>
       </c>
       <c r="F98" s="33"/>
       <c r="G98" s="37"/>
       <c r="H98" s="37"/>
       <c r="I98" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="99" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -13602,16 +13603,16 @@
       </c>
       <c r="C99" s="19"/>
       <c r="D99" s="23" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="E99" s="32"/>
       <c r="F99" s="33"/>
       <c r="G99" s="37"/>
       <c r="H99" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I99" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="100" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -13619,20 +13620,20 @@
         <v>99</v>
       </c>
       <c r="B100" s="20" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="C100" s="19"/>
       <c r="D100" s="31"/>
       <c r="E100" s="32"/>
       <c r="F100" s="33"/>
       <c r="G100" s="34" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H100" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I100" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="101" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -13650,10 +13651,10 @@
       <c r="F101" s="33"/>
       <c r="G101" s="37"/>
       <c r="H101" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I101" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="102" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -13668,13 +13669,13 @@
       <c r="E102" s="32"/>
       <c r="F102" s="33"/>
       <c r="G102" s="34" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H102" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I102" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="103" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -13689,13 +13690,13 @@
       <c r="E103" s="32"/>
       <c r="F103" s="33"/>
       <c r="G103" s="34" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H103" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I103" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="104" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -13707,16 +13708,16 @@
       </c>
       <c r="C104" s="19"/>
       <c r="D104" s="23" t="s">
+        <v>556</v>
+      </c>
+      <c r="E104" s="25" t="s">
         <v>557</v>
-      </c>
-      <c r="E104" s="25" t="s">
-        <v>558</v>
       </c>
       <c r="F104" s="33"/>
       <c r="G104" s="37"/>
       <c r="H104" s="37"/>
       <c r="I104" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="105" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -13724,20 +13725,20 @@
         <v>99</v>
       </c>
       <c r="B105" s="20" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="C105" s="19"/>
       <c r="D105" s="31"/>
       <c r="E105" s="32"/>
       <c r="F105" s="33"/>
       <c r="G105" s="34" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H105" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I105" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="106" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -13749,16 +13750,16 @@
       </c>
       <c r="C106" s="19"/>
       <c r="D106" s="23" t="s">
+        <v>558</v>
+      </c>
+      <c r="E106" s="25" t="s">
         <v>559</v>
-      </c>
-      <c r="E106" s="25" t="s">
-        <v>560</v>
       </c>
       <c r="F106" s="33"/>
       <c r="G106" s="37"/>
       <c r="H106" s="37"/>
       <c r="I106" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="107" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -13773,13 +13774,13 @@
       <c r="E107" s="32"/>
       <c r="F107" s="33"/>
       <c r="G107" s="34" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H107" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I107" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="108" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -13794,13 +13795,13 @@
       <c r="E108" s="32"/>
       <c r="F108" s="33"/>
       <c r="G108" s="34" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H108" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I108" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="109" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -13812,16 +13813,16 @@
       </c>
       <c r="C109" s="19"/>
       <c r="D109" s="23" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="E109" s="32"/>
       <c r="F109" s="33"/>
       <c r="G109" s="37"/>
       <c r="H109" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I109" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="110" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -13836,13 +13837,13 @@
       <c r="E110" s="32"/>
       <c r="F110" s="33"/>
       <c r="G110" s="34" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H110" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I110" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="111" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -13850,20 +13851,20 @@
         <v>99</v>
       </c>
       <c r="B111" s="20" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="C111" s="19"/>
       <c r="D111" s="31"/>
       <c r="E111" s="32"/>
       <c r="F111" s="33"/>
       <c r="G111" s="34" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H111" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I111" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="112" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -13875,16 +13876,16 @@
       </c>
       <c r="C112" s="19"/>
       <c r="D112" s="23" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="E112" s="32"/>
       <c r="F112" s="33"/>
       <c r="G112" s="37"/>
       <c r="H112" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I112" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="113" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -13899,13 +13900,13 @@
       <c r="E113" s="32"/>
       <c r="F113" s="33"/>
       <c r="G113" s="34" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H113" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I113" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="114" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -13917,16 +13918,16 @@
       </c>
       <c r="C114" s="19"/>
       <c r="D114" s="23" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="E114" s="32"/>
       <c r="F114" s="33"/>
       <c r="G114" s="37"/>
       <c r="H114" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I114" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="115" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -13938,16 +13939,16 @@
       </c>
       <c r="C115" s="19"/>
       <c r="D115" s="23" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="E115" s="32"/>
       <c r="F115" s="33"/>
       <c r="G115" s="37"/>
       <c r="H115" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I115" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="116" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -13959,16 +13960,16 @@
       </c>
       <c r="C116" s="19"/>
       <c r="D116" s="23" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="E116" s="32"/>
       <c r="F116" s="33"/>
       <c r="G116" s="37"/>
       <c r="H116" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I116" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="117" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -13983,13 +13984,13 @@
       <c r="E117" s="32"/>
       <c r="F117" s="33"/>
       <c r="G117" s="34" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H117" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I117" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="118" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -14004,13 +14005,13 @@
       <c r="E118" s="32"/>
       <c r="F118" s="33"/>
       <c r="G118" s="34" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H118" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I118" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="119" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -14025,13 +14026,13 @@
       <c r="E119" s="32"/>
       <c r="F119" s="33"/>
       <c r="G119" s="34" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H119" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I119" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="120" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -14046,13 +14047,13 @@
       <c r="E120" s="32"/>
       <c r="F120" s="33"/>
       <c r="G120" s="34" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H120" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I120" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="121" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -14067,13 +14068,13 @@
       <c r="E121" s="32"/>
       <c r="F121" s="33"/>
       <c r="G121" s="34" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H121" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I121" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="122" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -14081,20 +14082,20 @@
         <v>99</v>
       </c>
       <c r="B122" s="20" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="C122" s="19"/>
       <c r="D122" s="31"/>
       <c r="E122" s="32"/>
       <c r="F122" s="33"/>
       <c r="G122" s="34" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H122" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I122" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="123" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -14102,20 +14103,20 @@
         <v>99</v>
       </c>
       <c r="B123" s="20" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="C123" s="19"/>
       <c r="D123" s="31"/>
       <c r="E123" s="32"/>
       <c r="F123" s="33"/>
       <c r="G123" s="34" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H123" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I123" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="124" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -14123,20 +14124,20 @@
         <v>99</v>
       </c>
       <c r="B124" s="20" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="C124" s="19"/>
       <c r="D124" s="31"/>
       <c r="E124" s="32"/>
       <c r="F124" s="33"/>
       <c r="G124" s="34" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H124" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I124" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="125" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -14144,20 +14145,20 @@
         <v>99</v>
       </c>
       <c r="B125" s="20" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="C125" s="19"/>
       <c r="D125" s="31"/>
       <c r="E125" s="32"/>
       <c r="F125" s="33"/>
       <c r="G125" s="34" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H125" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I125" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="126" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -14165,20 +14166,20 @@
         <v>99</v>
       </c>
       <c r="B126" s="20" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="C126" s="19"/>
       <c r="D126" s="31"/>
       <c r="E126" s="32"/>
       <c r="F126" s="33"/>
       <c r="G126" s="34" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H126" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I126" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="127" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -14193,13 +14194,13 @@
       <c r="E127" s="32"/>
       <c r="F127" s="33"/>
       <c r="G127" s="34" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H127" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I127" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="128" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -14214,13 +14215,13 @@
       <c r="E128" s="32"/>
       <c r="F128" s="33"/>
       <c r="G128" s="34" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H128" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I128" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="129" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -14232,16 +14233,16 @@
       </c>
       <c r="C129" s="19"/>
       <c r="D129" s="23" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="E129" s="25" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="F129" s="33"/>
       <c r="G129" s="37"/>
       <c r="H129" s="37"/>
       <c r="I129" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="130" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -14256,13 +14257,13 @@
       <c r="E130" s="32"/>
       <c r="F130" s="33"/>
       <c r="G130" s="34" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H130" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I130" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="131" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -14277,13 +14278,13 @@
       <c r="E131" s="32"/>
       <c r="F131" s="33"/>
       <c r="G131" s="34" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H131" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I131" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="132" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -14298,13 +14299,13 @@
       <c r="E132" s="32"/>
       <c r="F132" s="33"/>
       <c r="G132" s="34" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H132" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I132" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="133" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -14319,13 +14320,13 @@
       <c r="E133" s="32"/>
       <c r="F133" s="33"/>
       <c r="G133" s="34" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H133" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I133" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="134" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -14340,13 +14341,13 @@
       <c r="E134" s="32"/>
       <c r="F134" s="33"/>
       <c r="G134" s="34" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H134" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I134" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="135" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -14354,20 +14355,20 @@
         <v>99</v>
       </c>
       <c r="B135" s="20" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="C135" s="19"/>
       <c r="D135" s="31"/>
       <c r="E135" s="32"/>
       <c r="F135" s="33"/>
       <c r="G135" s="34" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H135" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I135" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="136" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -14375,25 +14376,25 @@
         <v>99</v>
       </c>
       <c r="B136" s="20" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="C136" s="19"/>
       <c r="D136" s="31"/>
       <c r="E136" s="32"/>
       <c r="F136" s="33"/>
       <c r="G136" s="34" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H136" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I136" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="137" spans="1:9" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A137" s="38" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="B137" s="39"/>
       <c r="C137" s="39"/>
@@ -14416,13 +14417,13 @@
       <c r="E138" s="32"/>
       <c r="F138" s="33"/>
       <c r="G138" s="34" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H138" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I138" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="139" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -14434,16 +14435,16 @@
       </c>
       <c r="C139" s="19"/>
       <c r="D139" s="23" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="E139" s="32"/>
       <c r="F139" s="33"/>
       <c r="G139" s="37"/>
       <c r="H139" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I139" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="140" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -14455,16 +14456,16 @@
       </c>
       <c r="C140" s="19"/>
       <c r="D140" s="23" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="E140" s="32"/>
       <c r="F140" s="33"/>
       <c r="G140" s="37"/>
       <c r="H140" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I140" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="141" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -14479,13 +14480,13 @@
       <c r="E141" s="32"/>
       <c r="F141" s="33"/>
       <c r="G141" s="34" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H141" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I141" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="142" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -14493,20 +14494,20 @@
         <v>166</v>
       </c>
       <c r="B142" s="20" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="C142" s="19"/>
       <c r="D142" s="31"/>
       <c r="E142" s="32"/>
       <c r="F142" s="33"/>
       <c r="G142" s="34" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H142" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I142" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="143" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -14521,13 +14522,13 @@
       <c r="E143" s="32"/>
       <c r="F143" s="33"/>
       <c r="G143" s="34" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H143" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I143" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="144" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -14535,20 +14536,20 @@
         <v>166</v>
       </c>
       <c r="B144" s="20" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="C144" s="19"/>
       <c r="D144" s="31"/>
       <c r="E144" s="32"/>
       <c r="F144" s="33"/>
       <c r="G144" s="34" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H144" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I144" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="145" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -14556,20 +14557,20 @@
         <v>166</v>
       </c>
       <c r="B145" s="20" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="C145" s="19"/>
       <c r="D145" s="31"/>
       <c r="E145" s="32"/>
       <c r="F145" s="33"/>
       <c r="G145" s="34" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H145" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I145" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="146" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -14584,13 +14585,13 @@
       <c r="E146" s="32"/>
       <c r="F146" s="33"/>
       <c r="G146" s="34" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H146" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I146" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="147" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -14605,13 +14606,13 @@
       <c r="E147" s="32"/>
       <c r="F147" s="33"/>
       <c r="G147" s="34" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H147" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I147" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="148" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -14626,13 +14627,13 @@
       <c r="E148" s="32"/>
       <c r="F148" s="33"/>
       <c r="G148" s="34" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H148" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I148" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="149" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -14647,13 +14648,13 @@
       <c r="E149" s="32"/>
       <c r="F149" s="33"/>
       <c r="G149" s="34" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H149" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I149" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="150" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -14668,13 +14669,13 @@
       <c r="E150" s="32"/>
       <c r="F150" s="33"/>
       <c r="G150" s="34" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H150" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I150" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="151" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -14689,13 +14690,13 @@
       <c r="E151" s="32"/>
       <c r="F151" s="33"/>
       <c r="G151" s="34" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H151" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I151" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="152" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -14710,13 +14711,13 @@
       <c r="E152" s="32"/>
       <c r="F152" s="33"/>
       <c r="G152" s="34" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H152" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I152" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="153" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -14731,13 +14732,13 @@
       <c r="E153" s="32"/>
       <c r="F153" s="33"/>
       <c r="G153" s="34" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H153" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I153" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="154" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -14752,13 +14753,13 @@
       <c r="E154" s="32"/>
       <c r="F154" s="33"/>
       <c r="G154" s="34" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H154" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I154" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="155" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -14766,20 +14767,20 @@
         <v>166</v>
       </c>
       <c r="B155" s="20" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="C155" s="19"/>
       <c r="D155" s="31"/>
       <c r="E155" s="32"/>
       <c r="F155" s="33"/>
       <c r="G155" s="34" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H155" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I155" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="156" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -14787,20 +14788,20 @@
         <v>166</v>
       </c>
       <c r="B156" s="20" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="C156" s="19"/>
       <c r="D156" s="31"/>
       <c r="E156" s="32"/>
       <c r="F156" s="33"/>
       <c r="G156" s="34" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H156" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I156" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="157" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -14808,20 +14809,20 @@
         <v>166</v>
       </c>
       <c r="B157" s="20" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="C157" s="19"/>
       <c r="D157" s="31"/>
       <c r="E157" s="32"/>
       <c r="F157" s="33"/>
       <c r="G157" s="34" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H157" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I157" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="158" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -14829,20 +14830,20 @@
         <v>166</v>
       </c>
       <c r="B158" s="20" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="C158" s="19"/>
       <c r="D158" s="31"/>
       <c r="E158" s="32"/>
       <c r="F158" s="33"/>
       <c r="G158" s="34" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H158" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I158" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="159" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -14850,20 +14851,20 @@
         <v>166</v>
       </c>
       <c r="B159" s="20" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="C159" s="19"/>
       <c r="D159" s="31"/>
       <c r="E159" s="32"/>
       <c r="F159" s="33"/>
       <c r="G159" s="34" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H159" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I159" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="160" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -14878,13 +14879,13 @@
       <c r="E160" s="32"/>
       <c r="F160" s="33"/>
       <c r="G160" s="34" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H160" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I160" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="161" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -14899,13 +14900,13 @@
       <c r="E161" s="32"/>
       <c r="F161" s="33"/>
       <c r="G161" s="34" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H161" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I161" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="162" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -14920,13 +14921,13 @@
       <c r="E162" s="32"/>
       <c r="F162" s="33"/>
       <c r="G162" s="34" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H162" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I162" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="163" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -14938,15 +14939,15 @@
       </c>
       <c r="C163" s="19"/>
       <c r="D163" s="23" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="E163" s="32"/>
       <c r="F163" s="26" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="G163" s="37"/>
       <c r="H163" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I163" s="37"/>
     </row>
@@ -14959,16 +14960,16 @@
       </c>
       <c r="C164" s="19"/>
       <c r="D164" s="23" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="E164" s="32"/>
       <c r="F164" s="33"/>
       <c r="G164" s="37"/>
       <c r="H164" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I164" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="165" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -14980,16 +14981,16 @@
       </c>
       <c r="C165" s="19"/>
       <c r="D165" s="23" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="E165" s="32"/>
       <c r="F165" s="33"/>
       <c r="G165" s="37"/>
       <c r="H165" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I165" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="166" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -15001,16 +15002,16 @@
       </c>
       <c r="C166" s="19"/>
       <c r="D166" s="23" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="E166" s="32"/>
       <c r="F166" s="33"/>
       <c r="G166" s="37"/>
       <c r="H166" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I166" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="167" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -15022,16 +15023,16 @@
       </c>
       <c r="C167" s="19"/>
       <c r="D167" s="23" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="E167" s="32"/>
       <c r="F167" s="33"/>
       <c r="G167" s="37"/>
       <c r="H167" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I167" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="168" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -15039,20 +15040,20 @@
         <v>166</v>
       </c>
       <c r="B168" s="20" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="C168" s="19"/>
       <c r="D168" s="31"/>
       <c r="E168" s="32"/>
       <c r="F168" s="33"/>
       <c r="G168" s="34" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H168" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I168" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="169" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -15060,25 +15061,25 @@
         <v>166</v>
       </c>
       <c r="B169" s="20" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="C169" s="19"/>
       <c r="D169" s="31"/>
       <c r="E169" s="32"/>
       <c r="F169" s="33"/>
       <c r="G169" s="34" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H169" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I169" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="170" spans="1:9" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A170" s="38" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="B170" s="39"/>
       <c r="C170" s="39"/>
@@ -15098,16 +15099,16 @@
       </c>
       <c r="C171" s="19"/>
       <c r="D171" s="23" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="E171" s="32"/>
       <c r="F171" s="33"/>
       <c r="G171" s="37"/>
       <c r="H171" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I171" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="172" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -15119,16 +15120,16 @@
       </c>
       <c r="C172" s="19"/>
       <c r="D172" s="23" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="E172" s="32"/>
       <c r="F172" s="33"/>
       <c r="G172" s="37"/>
       <c r="H172" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I172" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="173" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -15143,13 +15144,13 @@
       <c r="E173" s="32"/>
       <c r="F173" s="33"/>
       <c r="G173" s="34" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H173" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I173" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="174" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -15164,13 +15165,13 @@
       <c r="E174" s="32"/>
       <c r="F174" s="33"/>
       <c r="G174" s="34" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H174" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I174" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="175" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -15182,16 +15183,16 @@
       </c>
       <c r="C175" s="19"/>
       <c r="D175" s="23" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="E175" s="32"/>
       <c r="F175" s="33"/>
       <c r="G175" s="37"/>
       <c r="H175" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I175" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="176" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -15203,16 +15204,16 @@
       </c>
       <c r="C176" s="19"/>
       <c r="D176" s="23" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="E176" s="32"/>
       <c r="F176" s="33"/>
       <c r="G176" s="37"/>
       <c r="H176" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I176" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="177" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -15227,13 +15228,13 @@
       <c r="E177" s="32"/>
       <c r="F177" s="33"/>
       <c r="G177" s="34" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H177" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I177" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="178" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -15248,13 +15249,13 @@
       <c r="E178" s="32"/>
       <c r="F178" s="33"/>
       <c r="G178" s="34" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H178" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I178" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="179" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -15266,16 +15267,16 @@
       </c>
       <c r="C179" s="19"/>
       <c r="D179" s="23" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="E179" s="32"/>
       <c r="F179" s="33"/>
       <c r="G179" s="37"/>
       <c r="H179" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I179" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="180" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -15283,20 +15284,20 @@
         <v>242</v>
       </c>
       <c r="B180" s="20" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="C180" s="19"/>
       <c r="D180" s="31"/>
       <c r="E180" s="32"/>
       <c r="F180" s="33"/>
       <c r="G180" s="34" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H180" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I180" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="181" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -15311,13 +15312,13 @@
       <c r="E181" s="32"/>
       <c r="F181" s="33"/>
       <c r="G181" s="34" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H181" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I181" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="182" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -15332,13 +15333,13 @@
       <c r="E182" s="32"/>
       <c r="F182" s="33"/>
       <c r="G182" s="34" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H182" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I182" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="183" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -15353,13 +15354,13 @@
       <c r="E183" s="32"/>
       <c r="F183" s="33"/>
       <c r="G183" s="34" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H183" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I183" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="184" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -15371,16 +15372,16 @@
       </c>
       <c r="C184" s="19"/>
       <c r="D184" s="23" t="s">
+        <v>546</v>
+      </c>
+      <c r="E184" s="25" t="s">
         <v>547</v>
-      </c>
-      <c r="E184" s="25" t="s">
-        <v>548</v>
       </c>
       <c r="F184" s="33"/>
       <c r="G184" s="37"/>
       <c r="H184" s="37"/>
       <c r="I184" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="185" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -15388,20 +15389,20 @@
         <v>242</v>
       </c>
       <c r="B185" s="20" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="C185" s="19"/>
       <c r="D185" s="31"/>
       <c r="E185" s="32"/>
       <c r="F185" s="33"/>
       <c r="G185" s="34" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H185" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I185" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="186" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -15413,16 +15414,16 @@
       </c>
       <c r="C186" s="19"/>
       <c r="D186" s="23" t="s">
+        <v>544</v>
+      </c>
+      <c r="E186" s="25" t="s">
         <v>545</v>
-      </c>
-      <c r="E186" s="25" t="s">
-        <v>546</v>
       </c>
       <c r="F186" s="33"/>
       <c r="G186" s="37"/>
       <c r="H186" s="37"/>
       <c r="I186" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="187" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -15437,13 +15438,13 @@
       <c r="E187" s="32"/>
       <c r="F187" s="33"/>
       <c r="G187" s="34" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H187" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I187" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="188" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -15458,13 +15459,13 @@
       <c r="E188" s="32"/>
       <c r="F188" s="33"/>
       <c r="G188" s="34" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H188" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I188" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="189" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -15479,13 +15480,13 @@
       <c r="E189" s="32"/>
       <c r="F189" s="33"/>
       <c r="G189" s="34" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H189" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I189" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="190" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -15493,20 +15494,20 @@
         <v>242</v>
       </c>
       <c r="B190" s="20" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="C190" s="19"/>
       <c r="D190" s="31"/>
       <c r="E190" s="32"/>
       <c r="F190" s="33"/>
       <c r="G190" s="34" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H190" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I190" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="191" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -15521,13 +15522,13 @@
       <c r="E191" s="32"/>
       <c r="F191" s="33"/>
       <c r="G191" s="34" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H191" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I191" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="192" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -15542,13 +15543,13 @@
       <c r="E192" s="32"/>
       <c r="F192" s="33"/>
       <c r="G192" s="34" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H192" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I192" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="193" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -15563,13 +15564,13 @@
       <c r="E193" s="32"/>
       <c r="F193" s="33"/>
       <c r="G193" s="34" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H193" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I193" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="194" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -15584,13 +15585,13 @@
       <c r="E194" s="32"/>
       <c r="F194" s="33"/>
       <c r="G194" s="34" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H194" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I194" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="195" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -15605,13 +15606,13 @@
       <c r="E195" s="32"/>
       <c r="F195" s="33"/>
       <c r="G195" s="34" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H195" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I195" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="196" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -15626,13 +15627,13 @@
       <c r="E196" s="32"/>
       <c r="F196" s="33"/>
       <c r="G196" s="34" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H196" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I196" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="197" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -15647,13 +15648,13 @@
       <c r="E197" s="32"/>
       <c r="F197" s="33"/>
       <c r="G197" s="34" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H197" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I197" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="198" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -15668,13 +15669,13 @@
       <c r="E198" s="32"/>
       <c r="F198" s="33"/>
       <c r="G198" s="34" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H198" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I198" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="199" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -15689,13 +15690,13 @@
       <c r="E199" s="32"/>
       <c r="F199" s="33"/>
       <c r="G199" s="34" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H199" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I199" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="200" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -15710,13 +15711,13 @@
       <c r="E200" s="32"/>
       <c r="F200" s="33"/>
       <c r="G200" s="34" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H200" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I200" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="201" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -15724,20 +15725,20 @@
         <v>242</v>
       </c>
       <c r="B201" s="20" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="C201" s="19"/>
       <c r="D201" s="31"/>
       <c r="E201" s="32"/>
       <c r="F201" s="33"/>
       <c r="G201" s="34" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H201" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I201" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="202" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -15745,20 +15746,20 @@
         <v>242</v>
       </c>
       <c r="B202" s="20" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="C202" s="19"/>
       <c r="D202" s="31"/>
       <c r="E202" s="32"/>
       <c r="F202" s="33"/>
       <c r="G202" s="34" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H202" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I202" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="203" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -15766,20 +15767,20 @@
         <v>242</v>
       </c>
       <c r="B203" s="20" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="C203" s="19"/>
       <c r="D203" s="31"/>
       <c r="E203" s="32"/>
       <c r="F203" s="33"/>
       <c r="G203" s="34" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H203" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I203" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="204" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -15787,20 +15788,20 @@
         <v>242</v>
       </c>
       <c r="B204" s="20" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="C204" s="19"/>
       <c r="D204" s="31"/>
       <c r="E204" s="32"/>
       <c r="F204" s="33"/>
       <c r="G204" s="34" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H204" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I204" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="205" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -15808,20 +15809,20 @@
         <v>242</v>
       </c>
       <c r="B205" s="20" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="C205" s="19"/>
       <c r="D205" s="31"/>
       <c r="E205" s="32"/>
       <c r="F205" s="33"/>
       <c r="G205" s="34" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H205" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I205" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="206" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -15836,13 +15837,13 @@
       <c r="E206" s="32"/>
       <c r="F206" s="33"/>
       <c r="G206" s="34" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H206" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I206" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="207" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -15857,13 +15858,13 @@
       <c r="E207" s="32"/>
       <c r="F207" s="33"/>
       <c r="G207" s="34" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H207" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I207" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="208" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -15878,13 +15879,13 @@
       <c r="E208" s="32"/>
       <c r="F208" s="33"/>
       <c r="G208" s="34" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H208" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I208" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="209" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -15899,13 +15900,13 @@
       <c r="E209" s="32"/>
       <c r="F209" s="33"/>
       <c r="G209" s="34" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H209" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I209" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="210" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -15920,13 +15921,13 @@
       <c r="E210" s="32"/>
       <c r="F210" s="33"/>
       <c r="G210" s="34" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H210" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I210" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="211" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -15941,13 +15942,13 @@
       <c r="E211" s="32"/>
       <c r="F211" s="33"/>
       <c r="G211" s="34" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H211" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I211" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="212" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -15962,13 +15963,13 @@
       <c r="E212" s="32"/>
       <c r="F212" s="33"/>
       <c r="G212" s="34" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H212" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I212" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="213" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -15983,13 +15984,13 @@
       <c r="E213" s="32"/>
       <c r="F213" s="33"/>
       <c r="G213" s="34" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H213" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I213" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="214" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -15997,20 +15998,20 @@
         <v>242</v>
       </c>
       <c r="B214" s="20" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="C214" s="19"/>
       <c r="D214" s="31"/>
       <c r="E214" s="32"/>
       <c r="F214" s="33"/>
       <c r="G214" s="34" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H214" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I214" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="215" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -16018,25 +16019,25 @@
         <v>242</v>
       </c>
       <c r="B215" s="20" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="C215" s="19"/>
       <c r="D215" s="31"/>
       <c r="E215" s="32"/>
       <c r="F215" s="33"/>
       <c r="G215" s="34" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H215" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I215" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="216" spans="1:9" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A216" s="38" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="B216" s="39"/>
       <c r="C216" s="39"/>
@@ -16059,13 +16060,13 @@
       <c r="E217" s="32"/>
       <c r="F217" s="33"/>
       <c r="G217" s="34" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H217" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I217" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="218" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -16077,16 +16078,16 @@
       </c>
       <c r="C218" s="19"/>
       <c r="D218" s="23" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="E218" s="32"/>
       <c r="F218" s="33"/>
       <c r="G218" s="37"/>
       <c r="H218" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I218" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="219" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -16101,13 +16102,13 @@
       <c r="E219" s="32"/>
       <c r="F219" s="33"/>
       <c r="G219" s="34" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H219" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I219" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="220" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -16122,13 +16123,13 @@
       <c r="E220" s="32"/>
       <c r="F220" s="33"/>
       <c r="G220" s="34" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H220" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I220" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="221" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -16143,13 +16144,13 @@
       <c r="E221" s="32"/>
       <c r="F221" s="33"/>
       <c r="G221" s="34" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H221" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I221" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="222" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -16161,16 +16162,16 @@
       </c>
       <c r="C222" s="19"/>
       <c r="D222" s="23" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="E222" s="32"/>
       <c r="F222" s="33"/>
       <c r="G222" s="37"/>
       <c r="H222" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I222" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="223" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -16185,13 +16186,13 @@
       <c r="E223" s="32"/>
       <c r="F223" s="33"/>
       <c r="G223" s="34" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H223" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I223" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="224" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -16206,13 +16207,13 @@
       <c r="E224" s="32"/>
       <c r="F224" s="33"/>
       <c r="G224" s="34" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H224" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I224" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="225" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -16227,13 +16228,13 @@
       <c r="E225" s="32"/>
       <c r="F225" s="33"/>
       <c r="G225" s="34" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H225" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I225" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="226" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -16241,20 +16242,20 @@
         <v>268</v>
       </c>
       <c r="B226" s="20" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="C226" s="19"/>
       <c r="D226" s="31"/>
       <c r="E226" s="32"/>
       <c r="F226" s="33"/>
       <c r="G226" s="34" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H226" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I226" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="227" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -16269,13 +16270,13 @@
       <c r="E227" s="32"/>
       <c r="F227" s="33"/>
       <c r="G227" s="34" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H227" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I227" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="228" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -16290,13 +16291,13 @@
       <c r="E228" s="32"/>
       <c r="F228" s="33"/>
       <c r="G228" s="34" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H228" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I228" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="229" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -16304,20 +16305,20 @@
         <v>268</v>
       </c>
       <c r="B229" s="20" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="C229" s="19"/>
       <c r="D229" s="31"/>
       <c r="E229" s="32"/>
       <c r="F229" s="33"/>
       <c r="G229" s="34" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H229" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I229" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="230" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -16332,13 +16333,13 @@
       <c r="E230" s="32"/>
       <c r="F230" s="33"/>
       <c r="G230" s="34" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H230" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I230" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="231" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -16353,13 +16354,13 @@
       <c r="E231" s="32"/>
       <c r="F231" s="33"/>
       <c r="G231" s="34" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H231" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I231" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="232" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -16374,13 +16375,13 @@
       <c r="E232" s="32"/>
       <c r="F232" s="33"/>
       <c r="G232" s="34" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H232" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I232" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="233" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -16395,13 +16396,13 @@
       <c r="E233" s="32"/>
       <c r="F233" s="33"/>
       <c r="G233" s="34" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H233" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I233" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="234" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -16409,20 +16410,20 @@
         <v>268</v>
       </c>
       <c r="B234" s="20" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="C234" s="19"/>
       <c r="D234" s="31"/>
       <c r="E234" s="32"/>
       <c r="F234" s="33"/>
       <c r="G234" s="34" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H234" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I234" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="235" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -16437,13 +16438,13 @@
       <c r="E235" s="32"/>
       <c r="F235" s="33"/>
       <c r="G235" s="34" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H235" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I235" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="236" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -16458,13 +16459,13 @@
       <c r="E236" s="32"/>
       <c r="F236" s="33"/>
       <c r="G236" s="34" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H236" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I236" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="237" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -16479,13 +16480,13 @@
       <c r="E237" s="32"/>
       <c r="F237" s="33"/>
       <c r="G237" s="34" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H237" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I237" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="238" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -16500,13 +16501,13 @@
       <c r="E238" s="32"/>
       <c r="F238" s="33"/>
       <c r="G238" s="34" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H238" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I238" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="239" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -16521,13 +16522,13 @@
       <c r="E239" s="32"/>
       <c r="F239" s="33"/>
       <c r="G239" s="34" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H239" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I239" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="240" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -16542,13 +16543,13 @@
       <c r="E240" s="32"/>
       <c r="F240" s="33"/>
       <c r="G240" s="34" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H240" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I240" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="241" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -16563,13 +16564,13 @@
       <c r="E241" s="32"/>
       <c r="F241" s="33"/>
       <c r="G241" s="34" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H241" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I241" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="242" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -16584,13 +16585,13 @@
       <c r="E242" s="32"/>
       <c r="F242" s="33"/>
       <c r="G242" s="34" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H242" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I242" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="243" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -16605,13 +16606,13 @@
       <c r="E243" s="32"/>
       <c r="F243" s="33"/>
       <c r="G243" s="34" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H243" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I243" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="244" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -16626,13 +16627,13 @@
       <c r="E244" s="32"/>
       <c r="F244" s="33"/>
       <c r="G244" s="34" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H244" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I244" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="245" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -16640,20 +16641,20 @@
         <v>268</v>
       </c>
       <c r="B245" s="20" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="C245" s="19"/>
       <c r="D245" s="31"/>
       <c r="E245" s="32"/>
       <c r="F245" s="33"/>
       <c r="G245" s="34" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H245" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I245" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="246" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -16661,20 +16662,20 @@
         <v>268</v>
       </c>
       <c r="B246" s="20" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="C246" s="19"/>
       <c r="D246" s="31"/>
       <c r="E246" s="32"/>
       <c r="F246" s="33"/>
       <c r="G246" s="34" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H246" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I246" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="247" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -16682,20 +16683,20 @@
         <v>268</v>
       </c>
       <c r="B247" s="20" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="C247" s="19"/>
       <c r="D247" s="31"/>
       <c r="E247" s="32"/>
       <c r="F247" s="33"/>
       <c r="G247" s="34" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H247" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I247" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="248" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -16703,20 +16704,20 @@
         <v>268</v>
       </c>
       <c r="B248" s="20" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="C248" s="19"/>
       <c r="D248" s="31"/>
       <c r="E248" s="32"/>
       <c r="F248" s="33"/>
       <c r="G248" s="34" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H248" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I248" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="249" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -16724,20 +16725,20 @@
         <v>268</v>
       </c>
       <c r="B249" s="20" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="C249" s="19"/>
       <c r="D249" s="31"/>
       <c r="E249" s="32"/>
       <c r="F249" s="33"/>
       <c r="G249" s="34" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H249" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I249" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="250" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -16752,13 +16753,13 @@
       <c r="E250" s="32"/>
       <c r="F250" s="33"/>
       <c r="G250" s="34" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H250" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I250" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="251" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -16773,13 +16774,13 @@
       <c r="E251" s="32"/>
       <c r="F251" s="33"/>
       <c r="G251" s="34" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H251" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I251" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="252" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -16794,13 +16795,13 @@
       <c r="E252" s="32"/>
       <c r="F252" s="33"/>
       <c r="G252" s="34" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H252" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I252" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="253" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -16812,15 +16813,15 @@
       </c>
       <c r="C253" s="19"/>
       <c r="D253" s="23" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="E253" s="32"/>
       <c r="F253" s="26" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="G253" s="37"/>
       <c r="H253" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I253" s="37"/>
     </row>
@@ -16833,16 +16834,16 @@
       </c>
       <c r="C254" s="19"/>
       <c r="D254" s="23" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="E254" s="32"/>
       <c r="F254" s="33"/>
       <c r="G254" s="37"/>
       <c r="H254" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I254" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="255" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -16854,16 +16855,16 @@
       </c>
       <c r="C255" s="19"/>
       <c r="D255" s="23" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="E255" s="32"/>
       <c r="F255" s="33"/>
       <c r="G255" s="37"/>
       <c r="H255" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I255" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="256" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -16875,16 +16876,16 @@
       </c>
       <c r="C256" s="19"/>
       <c r="D256" s="23" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="E256" s="32"/>
       <c r="F256" s="33"/>
       <c r="G256" s="37"/>
       <c r="H256" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I256" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="257" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -16896,16 +16897,16 @@
       </c>
       <c r="C257" s="19"/>
       <c r="D257" s="23" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="E257" s="32"/>
       <c r="F257" s="33"/>
       <c r="G257" s="37"/>
       <c r="H257" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I257" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="258" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -16913,20 +16914,20 @@
         <v>268</v>
       </c>
       <c r="B258" s="20" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="C258" s="19"/>
       <c r="D258" s="31"/>
       <c r="E258" s="32"/>
       <c r="F258" s="33"/>
       <c r="G258" s="34" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H258" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I258" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="259" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -16934,25 +16935,25 @@
         <v>268</v>
       </c>
       <c r="B259" s="20" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="C259" s="19"/>
       <c r="D259" s="31"/>
       <c r="E259" s="32"/>
       <c r="F259" s="33"/>
       <c r="G259" s="34" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H259" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I259" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="260" spans="1:9" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A260" s="38" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="B260" s="39"/>
       <c r="C260" s="39"/>
@@ -16975,13 +16976,13 @@
       <c r="E261" s="32"/>
       <c r="F261" s="33"/>
       <c r="G261" s="34" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H261" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I261" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="262" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -16996,13 +16997,13 @@
       <c r="E262" s="32"/>
       <c r="F262" s="33"/>
       <c r="G262" s="34" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H262" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I262" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="263" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -17017,13 +17018,13 @@
       <c r="E263" s="32"/>
       <c r="F263" s="33"/>
       <c r="G263" s="34" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H263" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I263" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="264" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -17038,13 +17039,13 @@
       <c r="E264" s="32"/>
       <c r="F264" s="33"/>
       <c r="G264" s="34" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H264" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I264" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="265" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -17059,13 +17060,13 @@
       <c r="E265" s="32"/>
       <c r="F265" s="33"/>
       <c r="G265" s="34" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H265" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I265" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="266" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -17080,13 +17081,13 @@
       <c r="E266" s="32"/>
       <c r="F266" s="33"/>
       <c r="G266" s="34" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H266" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I266" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="267" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -17101,13 +17102,13 @@
       <c r="E267" s="32"/>
       <c r="F267" s="33"/>
       <c r="G267" s="34" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H267" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I267" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="268" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -17122,13 +17123,13 @@
       <c r="E268" s="32"/>
       <c r="F268" s="33"/>
       <c r="G268" s="34" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H268" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I268" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="269" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -17136,20 +17137,20 @@
         <v>293</v>
       </c>
       <c r="B269" s="20" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="C269" s="19"/>
       <c r="D269" s="31"/>
       <c r="E269" s="32"/>
       <c r="F269" s="33"/>
       <c r="G269" s="34" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H269" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I269" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="270" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -17164,13 +17165,13 @@
       <c r="E270" s="32"/>
       <c r="F270" s="33"/>
       <c r="G270" s="34" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H270" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I270" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="271" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -17185,13 +17186,13 @@
       <c r="E271" s="32"/>
       <c r="F271" s="33"/>
       <c r="G271" s="34" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H271" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I271" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="272" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -17206,13 +17207,13 @@
       <c r="E272" s="32"/>
       <c r="F272" s="33"/>
       <c r="G272" s="34" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H272" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I272" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="273" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -17224,16 +17225,16 @@
       </c>
       <c r="C273" s="19"/>
       <c r="D273" s="23" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="E273" s="32"/>
       <c r="F273" s="33"/>
       <c r="G273" s="37"/>
       <c r="H273" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I273" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="274" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -17241,20 +17242,20 @@
         <v>293</v>
       </c>
       <c r="B274" s="20" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="C274" s="19"/>
       <c r="D274" s="31"/>
       <c r="E274" s="32"/>
       <c r="F274" s="33"/>
       <c r="G274" s="34" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H274" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I274" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="275" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -17266,16 +17267,16 @@
       </c>
       <c r="C275" s="19"/>
       <c r="D275" s="23" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="E275" s="32"/>
       <c r="F275" s="33"/>
       <c r="G275" s="37"/>
       <c r="H275" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I275" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="276" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -17290,13 +17291,13 @@
       <c r="E276" s="32"/>
       <c r="F276" s="33"/>
       <c r="G276" s="34" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H276" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I276" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="277" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -17311,13 +17312,13 @@
       <c r="E277" s="32"/>
       <c r="F277" s="33"/>
       <c r="G277" s="34" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H277" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I277" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="278" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -17332,13 +17333,13 @@
       <c r="E278" s="32"/>
       <c r="F278" s="33"/>
       <c r="G278" s="34" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H278" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I278" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="279" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -17353,13 +17354,13 @@
       <c r="E279" s="32"/>
       <c r="F279" s="33"/>
       <c r="G279" s="34" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H279" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I279" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="280" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -17367,20 +17368,20 @@
         <v>293</v>
       </c>
       <c r="B280" s="20" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="C280" s="19"/>
       <c r="D280" s="31"/>
       <c r="E280" s="32"/>
       <c r="F280" s="33"/>
       <c r="G280" s="34" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H280" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I280" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="281" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -17395,13 +17396,13 @@
       <c r="E281" s="32"/>
       <c r="F281" s="33"/>
       <c r="G281" s="34" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H281" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I281" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="282" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -17416,13 +17417,13 @@
       <c r="E282" s="32"/>
       <c r="F282" s="33"/>
       <c r="G282" s="34" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H282" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I282" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="283" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -17437,13 +17438,13 @@
       <c r="E283" s="32"/>
       <c r="F283" s="33"/>
       <c r="G283" s="34" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H283" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I283" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="284" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -17458,13 +17459,13 @@
       <c r="E284" s="32"/>
       <c r="F284" s="33"/>
       <c r="G284" s="34" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H284" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I284" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="285" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -17479,13 +17480,13 @@
       <c r="E285" s="32"/>
       <c r="F285" s="33"/>
       <c r="G285" s="34" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H285" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I285" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="286" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -17500,13 +17501,13 @@
       <c r="E286" s="32"/>
       <c r="F286" s="33"/>
       <c r="G286" s="34" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H286" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I286" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="287" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -17521,13 +17522,13 @@
       <c r="E287" s="32"/>
       <c r="F287" s="33"/>
       <c r="G287" s="34" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H287" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I287" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="288" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -17542,13 +17543,13 @@
       <c r="E288" s="32"/>
       <c r="F288" s="33"/>
       <c r="G288" s="34" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H288" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I288" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="289" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -17563,13 +17564,13 @@
       <c r="E289" s="32"/>
       <c r="F289" s="33"/>
       <c r="G289" s="34" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H289" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I289" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="290" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -17584,13 +17585,13 @@
       <c r="E290" s="32"/>
       <c r="F290" s="33"/>
       <c r="G290" s="34" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H290" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I290" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="291" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -17598,20 +17599,20 @@
         <v>293</v>
       </c>
       <c r="B291" s="20" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="C291" s="19"/>
       <c r="D291" s="31"/>
       <c r="E291" s="32"/>
       <c r="F291" s="33"/>
       <c r="G291" s="34" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H291" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I291" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="292" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -17619,20 +17620,20 @@
         <v>293</v>
       </c>
       <c r="B292" s="20" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="C292" s="19"/>
       <c r="D292" s="31"/>
       <c r="E292" s="32"/>
       <c r="F292" s="33"/>
       <c r="G292" s="34" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H292" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I292" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="293" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -17640,20 +17641,20 @@
         <v>293</v>
       </c>
       <c r="B293" s="20" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="C293" s="19"/>
       <c r="D293" s="31"/>
       <c r="E293" s="32"/>
       <c r="F293" s="33"/>
       <c r="G293" s="34" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H293" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I293" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="294" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -17661,20 +17662,20 @@
         <v>293</v>
       </c>
       <c r="B294" s="20" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="C294" s="19"/>
       <c r="D294" s="31"/>
       <c r="E294" s="32"/>
       <c r="F294" s="33"/>
       <c r="G294" s="34" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H294" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I294" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="295" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -17682,20 +17683,20 @@
         <v>293</v>
       </c>
       <c r="B295" s="20" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="C295" s="19"/>
       <c r="D295" s="31"/>
       <c r="E295" s="32"/>
       <c r="F295" s="33"/>
       <c r="G295" s="34" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H295" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I295" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="296" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -17710,13 +17711,13 @@
       <c r="E296" s="32"/>
       <c r="F296" s="33"/>
       <c r="G296" s="34" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H296" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I296" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="297" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -17731,13 +17732,13 @@
       <c r="E297" s="32"/>
       <c r="F297" s="33"/>
       <c r="G297" s="34" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H297" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I297" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="298" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -17752,13 +17753,13 @@
       <c r="E298" s="32"/>
       <c r="F298" s="33"/>
       <c r="G298" s="34" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H298" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I298" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="299" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -17773,13 +17774,13 @@
       <c r="E299" s="32"/>
       <c r="F299" s="33"/>
       <c r="G299" s="34" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H299" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I299" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="300" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -17791,16 +17792,16 @@
       </c>
       <c r="C300" s="19"/>
       <c r="D300" s="23" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="E300" s="32"/>
       <c r="F300" s="33"/>
       <c r="G300" s="37"/>
       <c r="H300" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I300" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="301" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -17812,16 +17813,16 @@
       </c>
       <c r="C301" s="19"/>
       <c r="D301" s="23" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="E301" s="32"/>
       <c r="F301" s="33"/>
       <c r="G301" s="37"/>
       <c r="H301" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I301" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="302" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -17836,13 +17837,13 @@
       <c r="E302" s="32"/>
       <c r="F302" s="33"/>
       <c r="G302" s="34" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H302" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I302" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="303" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -17857,13 +17858,13 @@
       <c r="E303" s="32"/>
       <c r="F303" s="33"/>
       <c r="G303" s="34" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H303" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I303" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="304" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -17871,20 +17872,20 @@
         <v>293</v>
       </c>
       <c r="B304" s="20" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="C304" s="19"/>
       <c r="D304" s="31"/>
       <c r="E304" s="32"/>
       <c r="F304" s="33"/>
       <c r="G304" s="34" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H304" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I304" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="305" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -17892,25 +17893,25 @@
         <v>293</v>
       </c>
       <c r="B305" s="20" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="C305" s="19"/>
       <c r="D305" s="31"/>
       <c r="E305" s="32"/>
       <c r="F305" s="33"/>
       <c r="G305" s="34" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H305" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I305" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="306" spans="1:9" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A306" s="38" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="B306" s="39"/>
       <c r="C306" s="39"/>
@@ -17933,13 +17934,13 @@
       <c r="E307" s="32"/>
       <c r="F307" s="33"/>
       <c r="G307" s="34" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H307" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I307" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="308" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -17954,13 +17955,13 @@
       <c r="E308" s="32"/>
       <c r="F308" s="33"/>
       <c r="G308" s="34" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H308" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I308" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="309" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -17975,13 +17976,13 @@
       <c r="E309" s="32"/>
       <c r="F309" s="33"/>
       <c r="G309" s="34" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H309" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I309" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="310" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -17996,13 +17997,13 @@
       <c r="E310" s="32"/>
       <c r="F310" s="33"/>
       <c r="G310" s="34" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H310" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I310" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="311" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -18017,13 +18018,13 @@
       <c r="E311" s="32"/>
       <c r="F311" s="33"/>
       <c r="G311" s="34" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H311" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I311" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="312" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -18038,13 +18039,13 @@
       <c r="E312" s="32"/>
       <c r="F312" s="33"/>
       <c r="G312" s="34" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H312" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I312" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="313" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -18059,13 +18060,13 @@
       <c r="E313" s="32"/>
       <c r="F313" s="33"/>
       <c r="G313" s="34" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H313" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I313" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="314" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -18080,13 +18081,13 @@
       <c r="E314" s="32"/>
       <c r="F314" s="33"/>
       <c r="G314" s="34" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H314" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I314" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="315" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -18098,16 +18099,16 @@
       </c>
       <c r="C315" s="19"/>
       <c r="D315" s="23" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="E315" s="32"/>
       <c r="F315" s="33"/>
       <c r="G315" s="37"/>
       <c r="H315" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I315" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="316" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -18115,20 +18116,20 @@
         <v>303</v>
       </c>
       <c r="B316" s="20" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="C316" s="19"/>
       <c r="D316" s="31"/>
       <c r="E316" s="32"/>
       <c r="F316" s="33"/>
       <c r="G316" s="34" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H316" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I316" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="317" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -18143,13 +18144,13 @@
       <c r="E317" s="32"/>
       <c r="F317" s="33"/>
       <c r="G317" s="34" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H317" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I317" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="318" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -18164,13 +18165,13 @@
       <c r="E318" s="32"/>
       <c r="F318" s="33"/>
       <c r="G318" s="34" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H318" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I318" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="319" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -18185,13 +18186,13 @@
       <c r="E319" s="32"/>
       <c r="F319" s="33"/>
       <c r="G319" s="34" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H319" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I319" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="320" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -18203,16 +18204,16 @@
       </c>
       <c r="C320" s="19"/>
       <c r="D320" s="23" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="E320" s="32"/>
       <c r="F320" s="33"/>
       <c r="G320" s="37"/>
       <c r="H320" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I320" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="321" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -18220,20 +18221,20 @@
         <v>303</v>
       </c>
       <c r="B321" s="20" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="C321" s="19"/>
       <c r="D321" s="31"/>
       <c r="E321" s="32"/>
       <c r="F321" s="33"/>
       <c r="G321" s="34" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H321" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I321" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="322" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -18245,16 +18246,16 @@
       </c>
       <c r="C322" s="19"/>
       <c r="D322" s="23" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="E322" s="32"/>
       <c r="F322" s="33"/>
       <c r="G322" s="37"/>
       <c r="H322" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I322" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="323" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -18269,13 +18270,13 @@
       <c r="E323" s="32"/>
       <c r="F323" s="33"/>
       <c r="G323" s="34" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H323" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I323" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="324" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -18290,13 +18291,13 @@
       <c r="E324" s="32"/>
       <c r="F324" s="33"/>
       <c r="G324" s="34" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H324" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I324" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="325" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -18311,13 +18312,13 @@
       <c r="E325" s="32"/>
       <c r="F325" s="33"/>
       <c r="G325" s="34" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H325" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I325" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="326" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -18332,13 +18333,13 @@
       <c r="E326" s="32"/>
       <c r="F326" s="33"/>
       <c r="G326" s="34" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H326" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I326" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="327" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -18346,20 +18347,20 @@
         <v>303</v>
       </c>
       <c r="B327" s="20" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="C327" s="19"/>
       <c r="D327" s="31"/>
       <c r="E327" s="32"/>
       <c r="F327" s="33"/>
       <c r="G327" s="34" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H327" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I327" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="328" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -18374,13 +18375,13 @@
       <c r="E328" s="32"/>
       <c r="F328" s="33"/>
       <c r="G328" s="34" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H328" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I328" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="329" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -18395,13 +18396,13 @@
       <c r="E329" s="32"/>
       <c r="F329" s="33"/>
       <c r="G329" s="34" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H329" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I329" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="330" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -18416,13 +18417,13 @@
       <c r="E330" s="32"/>
       <c r="F330" s="33"/>
       <c r="G330" s="34" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H330" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I330" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="331" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -18437,13 +18438,13 @@
       <c r="E331" s="32"/>
       <c r="F331" s="33"/>
       <c r="G331" s="34" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H331" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I331" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="332" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -18458,13 +18459,13 @@
       <c r="E332" s="32"/>
       <c r="F332" s="33"/>
       <c r="G332" s="34" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H332" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I332" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="333" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -18479,13 +18480,13 @@
       <c r="E333" s="32"/>
       <c r="F333" s="33"/>
       <c r="G333" s="34" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H333" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I333" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="334" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -18500,13 +18501,13 @@
       <c r="E334" s="32"/>
       <c r="F334" s="33"/>
       <c r="G334" s="34" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H334" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I334" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="335" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -18521,13 +18522,13 @@
       <c r="E335" s="32"/>
       <c r="F335" s="33"/>
       <c r="G335" s="34" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H335" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I335" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="336" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -18542,13 +18543,13 @@
       <c r="E336" s="32"/>
       <c r="F336" s="33"/>
       <c r="G336" s="34" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H336" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I336" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="337" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -18563,13 +18564,13 @@
       <c r="E337" s="32"/>
       <c r="F337" s="33"/>
       <c r="G337" s="34" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H337" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I337" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="338" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -18577,20 +18578,20 @@
         <v>303</v>
       </c>
       <c r="B338" s="20" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="C338" s="19"/>
       <c r="D338" s="31"/>
       <c r="E338" s="32"/>
       <c r="F338" s="33"/>
       <c r="G338" s="34" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H338" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I338" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="339" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -18598,20 +18599,20 @@
         <v>303</v>
       </c>
       <c r="B339" s="20" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="C339" s="19"/>
       <c r="D339" s="31"/>
       <c r="E339" s="32"/>
       <c r="F339" s="33"/>
       <c r="G339" s="34" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H339" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I339" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="340" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -18619,20 +18620,20 @@
         <v>303</v>
       </c>
       <c r="B340" s="20" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="C340" s="19"/>
       <c r="D340" s="31"/>
       <c r="E340" s="32"/>
       <c r="F340" s="33"/>
       <c r="G340" s="34" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H340" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I340" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="341" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -18640,20 +18641,20 @@
         <v>303</v>
       </c>
       <c r="B341" s="20" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="C341" s="19"/>
       <c r="D341" s="31"/>
       <c r="E341" s="32"/>
       <c r="F341" s="33"/>
       <c r="G341" s="34" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H341" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I341" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="342" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -18661,20 +18662,20 @@
         <v>303</v>
       </c>
       <c r="B342" s="20" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="C342" s="19"/>
       <c r="D342" s="31"/>
       <c r="E342" s="32"/>
       <c r="F342" s="33"/>
       <c r="G342" s="34" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H342" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I342" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="343" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -18689,13 +18690,13 @@
       <c r="E343" s="32"/>
       <c r="F343" s="33"/>
       <c r="G343" s="34" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H343" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I343" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="344" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -18710,13 +18711,13 @@
       <c r="E344" s="32"/>
       <c r="F344" s="33"/>
       <c r="G344" s="34" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H344" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I344" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="345" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -18731,13 +18732,13 @@
       <c r="E345" s="32"/>
       <c r="F345" s="33"/>
       <c r="G345" s="34" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H345" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I345" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="346" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -18752,13 +18753,13 @@
       <c r="E346" s="32"/>
       <c r="F346" s="33"/>
       <c r="G346" s="34" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H346" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I346" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="347" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -18773,13 +18774,13 @@
       <c r="E347" s="32"/>
       <c r="F347" s="33"/>
       <c r="G347" s="34" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H347" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I347" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="348" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -18794,13 +18795,13 @@
       <c r="E348" s="32"/>
       <c r="F348" s="33"/>
       <c r="G348" s="34" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H348" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I348" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="349" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -18815,13 +18816,13 @@
       <c r="E349" s="32"/>
       <c r="F349" s="33"/>
       <c r="G349" s="34" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H349" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I349" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="350" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -18836,13 +18837,13 @@
       <c r="E350" s="32"/>
       <c r="F350" s="33"/>
       <c r="G350" s="34" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H350" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I350" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="351" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -18850,20 +18851,20 @@
         <v>303</v>
       </c>
       <c r="B351" s="20" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="C351" s="19"/>
       <c r="D351" s="31"/>
       <c r="E351" s="32"/>
       <c r="F351" s="33"/>
       <c r="G351" s="34" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H351" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I351" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="352" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -18871,20 +18872,20 @@
         <v>303</v>
       </c>
       <c r="B352" s="20" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="C352" s="19"/>
       <c r="D352" s="31"/>
       <c r="E352" s="32"/>
       <c r="F352" s="33"/>
       <c r="G352" s="34" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H352" s="35" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="I352" s="36" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
   </sheetData>

--- a/ThinktankWebCC_KeyBindings.xlsx
+++ b/ThinktankWebCC_KeyBindings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gogow\Documents\ThinktankWebCC\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A3BCED6-D821-4A28-A92D-95E38A45FA42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CBE1B04-C2DB-4DEC-80FF-252828813C55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1274,6 +1274,9 @@
     <t>Global &amp; ExMode キーバインディング詳細</t>
   </si>
   <si>
+    <t>▶ Global: パネル切替</t>
+  </si>
+  <si>
     <t>Global: パネル切替</t>
   </si>
   <si>
@@ -1791,10 +1794,6 @@
   </si>
   <si>
     <t>SelPos:firstline</t>
-  </si>
-  <si>
-    <t>▶ Global: パネル切替</t>
-    <phoneticPr fontId="13"/>
   </si>
 </sst>
 </file>
@@ -7682,17 +7681,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="A95:G95"/>
+    <mergeCell ref="A86:G86"/>
+    <mergeCell ref="A60:G60"/>
+    <mergeCell ref="A49:G49"/>
+    <mergeCell ref="A75:G75"/>
     <mergeCell ref="A13:G13"/>
     <mergeCell ref="A36:G36"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A80:G80"/>
     <mergeCell ref="A3:G3"/>
     <mergeCell ref="A77:G77"/>
-    <mergeCell ref="A95:G95"/>
-    <mergeCell ref="A86:G86"/>
-    <mergeCell ref="A60:G60"/>
-    <mergeCell ref="A49:G49"/>
-    <mergeCell ref="A75:G75"/>
   </mergeCells>
   <phoneticPr fontId="13"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -9477,7 +9476,7 @@
     </row>
     <row r="3" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="42" t="s">
-        <v>586</v>
+        <v>413</v>
       </c>
       <c r="B3" s="39"/>
       <c r="C3" s="39"/>
@@ -9488,7 +9487,7 @@
     </row>
     <row r="4" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="18" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="B4" s="19" t="s">
         <v>166</v>
@@ -9503,15 +9502,15 @@
         <v>231</v>
       </c>
       <c r="F4" s="19" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="G4" s="22" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="18" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="B5" s="19" t="s">
         <v>268</v>
@@ -9526,15 +9525,15 @@
         <v>291</v>
       </c>
       <c r="F5" s="19" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="G5" s="22" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="18" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="B6" s="19" t="s">
         <v>166</v>
@@ -9549,15 +9548,15 @@
         <v>192</v>
       </c>
       <c r="F6" s="19" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="G6" s="22" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="18" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="B7" s="19" t="s">
         <v>166</v>
@@ -9572,15 +9571,15 @@
         <v>189</v>
       </c>
       <c r="F7" s="19" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="G7" s="22" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="18" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="B8" s="19" t="s">
         <v>166</v>
@@ -9595,15 +9594,15 @@
         <v>214</v>
       </c>
       <c r="F8" s="19" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="G8" s="22" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="18" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="B9" s="19" t="s">
         <v>166</v>
@@ -9618,15 +9617,15 @@
         <v>179</v>
       </c>
       <c r="F9" s="19" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="G9" s="22" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="18" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="B10" s="19" t="s">
         <v>166</v>
@@ -9641,15 +9640,15 @@
         <v>222</v>
       </c>
       <c r="F10" s="19" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="G10" s="22" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="18" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="B11" s="19" t="s">
         <v>166</v>
@@ -9664,15 +9663,15 @@
         <v>225</v>
       </c>
       <c r="F11" s="19" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="G11" s="22" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="18" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="B12" s="19" t="s">
         <v>166</v>
@@ -9687,15 +9686,15 @@
         <v>228</v>
       </c>
       <c r="F12" s="19" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="G12" s="22" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="42" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="B13" s="39"/>
       <c r="C13" s="39"/>
@@ -9706,7 +9705,7 @@
     </row>
     <row r="14" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A14" s="18" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="B14" s="19" t="s">
         <v>166</v>
@@ -9721,15 +9720,15 @@
         <v>207</v>
       </c>
       <c r="F14" s="19" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="G14" s="22" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A15" s="18" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="B15" s="19" t="s">
         <v>166</v>
@@ -9744,15 +9743,15 @@
         <v>220</v>
       </c>
       <c r="F15" s="19" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="G15" s="22" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A16" s="18" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="B16" s="19" t="s">
         <v>166</v>
@@ -9767,15 +9766,15 @@
         <v>181</v>
       </c>
       <c r="F16" s="19" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="G16" s="22" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A17" s="18" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="B17" s="19" t="s">
         <v>166</v>
@@ -9790,15 +9789,15 @@
         <v>195</v>
       </c>
       <c r="F17" s="19" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="G17" s="22" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A18" s="18" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="B18" s="19" t="s">
         <v>268</v>
@@ -9813,15 +9812,15 @@
         <v>282</v>
       </c>
       <c r="F18" s="19" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="G18" s="22" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="19" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A19" s="18" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="B19" s="19" t="s">
         <v>311</v>
@@ -9836,15 +9835,15 @@
         <v>314</v>
       </c>
       <c r="F19" s="19" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="G19" s="22" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="20" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A20" s="18" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="B20" s="19" t="s">
         <v>311</v>
@@ -9859,15 +9858,15 @@
         <v>320</v>
       </c>
       <c r="F20" s="19" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="G20" s="22" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="21" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A21" s="18" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="B21" s="19" t="s">
         <v>311</v>
@@ -9882,15 +9881,15 @@
         <v>318</v>
       </c>
       <c r="F21" s="19" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="G21" s="22" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="22" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A22" s="18" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="B22" s="19" t="s">
         <v>311</v>
@@ -9905,15 +9904,15 @@
         <v>322</v>
       </c>
       <c r="F22" s="19" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="G22" s="22" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="23" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A23" s="18" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="B23" s="19" t="s">
         <v>311</v>
@@ -9928,15 +9927,15 @@
         <v>316</v>
       </c>
       <c r="F23" s="19" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="G23" s="22" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="24" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A24" s="18" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="B24" s="19" t="s">
         <v>311</v>
@@ -9951,15 +9950,15 @@
         <v>324</v>
       </c>
       <c r="F24" s="19" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="G24" s="22" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="25" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A25" s="18" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="B25" s="19" t="s">
         <v>311</v>
@@ -9974,15 +9973,15 @@
         <v>326</v>
       </c>
       <c r="F25" s="19" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="G25" s="22" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="26" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A26" s="18" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="B26" s="19" t="s">
         <v>311</v>
@@ -9997,15 +9996,15 @@
         <v>328</v>
       </c>
       <c r="F26" s="19" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="G26" s="22" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="27" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="42" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="B27" s="39"/>
       <c r="C27" s="39"/>
@@ -10016,7 +10015,7 @@
     </row>
     <row r="28" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A28" s="18" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="B28" s="19" t="s">
         <v>311</v>
@@ -10031,15 +10030,15 @@
         <v>314</v>
       </c>
       <c r="F28" s="19" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="G28" s="22" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="29" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A29" s="18" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="B29" s="19" t="s">
         <v>311</v>
@@ -10054,15 +10053,15 @@
         <v>320</v>
       </c>
       <c r="F29" s="19" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="G29" s="22" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="30" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A30" s="18" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="B30" s="19" t="s">
         <v>311</v>
@@ -10077,15 +10076,15 @@
         <v>318</v>
       </c>
       <c r="F30" s="19" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="G30" s="22" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="31" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A31" s="18" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="B31" s="19" t="s">
         <v>311</v>
@@ -10100,15 +10099,15 @@
         <v>322</v>
       </c>
       <c r="F31" s="19" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="G31" s="22" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="32" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A32" s="18" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="B32" s="19" t="s">
         <v>311</v>
@@ -10123,15 +10122,15 @@
         <v>316</v>
       </c>
       <c r="F32" s="19" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="G32" s="22" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="33" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A33" s="18" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="B33" s="19" t="s">
         <v>311</v>
@@ -10146,15 +10145,15 @@
         <v>324</v>
       </c>
       <c r="F33" s="19" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="G33" s="22" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="34" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A34" s="18" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="B34" s="19" t="s">
         <v>311</v>
@@ -10169,15 +10168,15 @@
         <v>326</v>
       </c>
       <c r="F34" s="19" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="G34" s="22" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="35" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A35" s="18" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="B35" s="19" t="s">
         <v>311</v>
@@ -10192,15 +10191,15 @@
         <v>328</v>
       </c>
       <c r="F35" s="19" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="G35" s="22" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="36" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="42" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="B36" s="39"/>
       <c r="C36" s="39"/>
@@ -10211,7 +10210,7 @@
     </row>
     <row r="37" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A37" s="18" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="B37" s="19" t="s">
         <v>99</v>
@@ -10226,7 +10225,7 @@
         <v>124</v>
       </c>
       <c r="F37" s="19" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="G37" s="22" t="s">
         <v>339</v>
@@ -10234,7 +10233,7 @@
     </row>
     <row r="38" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A38" s="18" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="B38" s="19" t="s">
         <v>166</v>
@@ -10249,7 +10248,7 @@
         <v>212</v>
       </c>
       <c r="F38" s="19" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="G38" s="22" t="s">
         <v>339</v>
@@ -10257,7 +10256,7 @@
     </row>
     <row r="39" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A39" s="18" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="B39" s="19" t="s">
         <v>166</v>
@@ -10272,7 +10271,7 @@
         <v>177</v>
       </c>
       <c r="F39" s="19" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="G39" s="22" t="s">
         <v>339</v>
@@ -10280,7 +10279,7 @@
     </row>
     <row r="40" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A40" s="18" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="B40" s="19" t="s">
         <v>99</v>
@@ -10295,7 +10294,7 @@
         <v>133</v>
       </c>
       <c r="F40" s="19" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="G40" s="22" t="s">
         <v>339</v>
@@ -10303,7 +10302,7 @@
     </row>
     <row r="41" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A41" s="18" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="B41" s="19" t="s">
         <v>166</v>
@@ -10318,7 +10317,7 @@
         <v>338</v>
       </c>
       <c r="F41" s="19" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="G41" s="22" t="s">
         <v>339</v>
@@ -10326,7 +10325,7 @@
     </row>
     <row r="42" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A42" s="18" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="B42" s="19" t="s">
         <v>13</v>
@@ -10341,15 +10340,15 @@
         <v>50</v>
       </c>
       <c r="F42" s="19" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="G42" s="22" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="43" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A43" s="18" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="B43" s="19" t="s">
         <v>242</v>
@@ -10364,15 +10363,15 @@
         <v>50</v>
       </c>
       <c r="F43" s="19" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="G43" s="22" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="44" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A44" s="18" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="B44" s="19" t="s">
         <v>13</v>
@@ -10387,15 +10386,15 @@
         <v>55</v>
       </c>
       <c r="F44" s="19" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="G44" s="22" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="45" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A45" s="18" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="B45" s="19" t="s">
         <v>13</v>
@@ -10410,15 +10409,15 @@
         <v>53</v>
       </c>
       <c r="F45" s="19" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="G45" s="22" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="46" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A46" s="18" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="B46" s="19" t="s">
         <v>242</v>
@@ -10433,15 +10432,15 @@
         <v>156</v>
       </c>
       <c r="F46" s="19" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="G46" s="22" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="47" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A47" s="18" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="B47" s="19" t="s">
         <v>242</v>
@@ -10456,15 +10455,15 @@
         <v>158</v>
       </c>
       <c r="F47" s="19" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="G47" s="22" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="48" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A48" s="18" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="B48" s="19" t="s">
         <v>99</v>
@@ -10479,15 +10478,15 @@
         <v>156</v>
       </c>
       <c r="F48" s="19" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="G48" s="22" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="49" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A49" s="18" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="B49" s="19" t="s">
         <v>99</v>
@@ -10502,15 +10501,15 @@
         <v>158</v>
       </c>
       <c r="F49" s="19" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="G49" s="22" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="50" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A50" s="18" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="B50" s="19" t="s">
         <v>293</v>
@@ -10525,15 +10524,15 @@
         <v>297</v>
       </c>
       <c r="F50" s="19" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="G50" s="22" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="51" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A51" s="18" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="B51" s="19" t="s">
         <v>99</v>
@@ -10548,15 +10547,15 @@
         <v>129</v>
       </c>
       <c r="F51" s="19" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="G51" s="22" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="52" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A52" s="18" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="B52" s="19" t="s">
         <v>166</v>
@@ -10571,15 +10570,15 @@
         <v>217</v>
       </c>
       <c r="F52" s="19" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="G52" s="22" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="53" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="42" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B53" s="39"/>
       <c r="C53" s="39"/>
@@ -10590,7 +10589,7 @@
     </row>
     <row r="54" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A54" s="18" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="B54" s="19" t="s">
         <v>13</v>
@@ -10599,7 +10598,7 @@
         <v>155</v>
       </c>
       <c r="D54" s="24" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="E54" s="19" t="s">
         <v>156</v>
@@ -10608,12 +10607,12 @@
         <v>360</v>
       </c>
       <c r="G54" s="22" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
     </row>
     <row r="55" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A55" s="18" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="B55" s="19" t="s">
         <v>13</v>
@@ -10622,7 +10621,7 @@
         <v>157</v>
       </c>
       <c r="D55" s="24" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="E55" s="19" t="s">
         <v>158</v>
@@ -10631,12 +10630,12 @@
         <v>360</v>
       </c>
       <c r="G55" s="22" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
     </row>
     <row r="56" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A56" s="18" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="B56" s="19" t="s">
         <v>13</v>
@@ -10645,21 +10644,21 @@
         <v>153</v>
       </c>
       <c r="D56" s="24" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="E56" s="19" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="F56" s="19" t="s">
         <v>360</v>
       </c>
       <c r="G56" s="22" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
     </row>
     <row r="57" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A57" s="18" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="B57" s="19" t="s">
         <v>13</v>
@@ -10668,21 +10667,21 @@
         <v>144</v>
       </c>
       <c r="D57" s="24" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="E57" s="19" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="F57" s="19" t="s">
         <v>360</v>
       </c>
       <c r="G57" s="22" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
     </row>
     <row r="58" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A58" s="18" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="B58" s="19" t="s">
         <v>13</v>
@@ -10691,21 +10690,21 @@
         <v>208</v>
       </c>
       <c r="D58" s="24" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="E58" s="19" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="F58" s="19" t="s">
         <v>360</v>
       </c>
       <c r="G58" s="22" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
     </row>
     <row r="59" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A59" s="18" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="B59" s="19" t="s">
         <v>13</v>
@@ -10714,67 +10713,67 @@
         <v>147</v>
       </c>
       <c r="D59" s="24" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="E59" s="19" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="F59" s="19" t="s">
         <v>360</v>
       </c>
       <c r="G59" s="22" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
     </row>
     <row r="60" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A60" s="18" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="B60" s="19" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="C60" s="20" t="s">
         <v>208</v>
       </c>
       <c r="D60" s="24" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="E60" s="19" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="F60" s="19" t="s">
         <v>360</v>
       </c>
       <c r="G60" s="22" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
     </row>
     <row r="61" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A61" s="18" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="B61" s="19" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="C61" s="20" t="s">
         <v>208</v>
       </c>
       <c r="D61" s="24" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="E61" s="19" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="F61" s="19" t="s">
         <v>360</v>
       </c>
       <c r="G61" s="22" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
     </row>
     <row r="62" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="42" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="B62" s="39"/>
       <c r="C62" s="39"/>
@@ -10785,7 +10784,7 @@
     </row>
     <row r="63" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A63" s="18" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="B63" s="19" t="s">
         <v>13</v>
@@ -10794,21 +10793,21 @@
         <v>30</v>
       </c>
       <c r="D63" s="28" t="s">
+        <v>444</v>
+      </c>
+      <c r="E63" s="19" t="s">
+        <v>445</v>
+      </c>
+      <c r="F63" s="19" t="s">
         <v>443</v>
       </c>
-      <c r="E63" s="19" t="s">
-        <v>444</v>
-      </c>
-      <c r="F63" s="19" t="s">
-        <v>442</v>
-      </c>
       <c r="G63" s="22" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="64" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A64" s="18" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="B64" s="19" t="s">
         <v>13</v>
@@ -10817,44 +10816,44 @@
         <v>27</v>
       </c>
       <c r="D64" s="28" t="s">
+        <v>447</v>
+      </c>
+      <c r="E64" s="19" t="s">
+        <v>448</v>
+      </c>
+      <c r="F64" s="19" t="s">
+        <v>443</v>
+      </c>
+      <c r="G64" s="22" t="s">
         <v>446</v>
-      </c>
-      <c r="E64" s="19" t="s">
-        <v>447</v>
-      </c>
-      <c r="F64" s="19" t="s">
-        <v>442</v>
-      </c>
-      <c r="G64" s="22" t="s">
-        <v>445</v>
       </c>
     </row>
     <row r="65" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A65" s="18" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="B65" s="19" t="s">
         <v>13</v>
       </c>
       <c r="C65" s="20" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="D65" s="28" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="E65" s="19" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="F65" s="19" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="G65" s="22" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="66" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A66" s="18" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="B66" s="19" t="s">
         <v>13</v>
@@ -10863,136 +10862,136 @@
         <v>110</v>
       </c>
       <c r="D66" s="28" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="E66" s="19" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="F66" s="19" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="G66" s="22" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="67" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A67" s="18" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="B67" s="19" t="s">
         <v>13</v>
       </c>
       <c r="C67" s="20" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="D67" s="28" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="E67" s="19" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="F67" s="19" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="G67" s="22" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="68" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A68" s="18" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="B68" s="19" t="s">
         <v>13</v>
       </c>
       <c r="C68" s="20" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="D68" s="28" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="E68" s="19" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="F68" s="19" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="G68" s="22" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="69" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A69" s="18" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="B69" s="19" t="s">
         <v>13</v>
       </c>
       <c r="C69" s="20" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="D69" s="28" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="E69" s="19" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="F69" s="19" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="G69" s="22" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="70" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A70" s="18" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="B70" s="19" t="s">
         <v>13</v>
       </c>
       <c r="C70" s="20" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="D70" s="28" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="E70" s="19" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="F70" s="19" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="G70" s="22" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="71" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A71" s="18" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="B71" s="19" t="s">
         <v>13</v>
       </c>
       <c r="C71" s="20" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="D71" s="28" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="E71" s="19" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="F71" s="19" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="G71" s="22" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="72" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A72" s="18" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="B72" s="19" t="s">
         <v>13</v>
@@ -11001,21 +11000,21 @@
         <v>142</v>
       </c>
       <c r="D72" s="28" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="E72" s="19" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="F72" s="19" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="G72" s="22" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="73" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A73" s="18" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="B73" s="19" t="s">
         <v>13</v>
@@ -11024,21 +11023,21 @@
         <v>140</v>
       </c>
       <c r="D73" s="28" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="E73" s="19" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="F73" s="19" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="G73" s="22" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="74" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A74" s="18" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="B74" s="19" t="s">
         <v>74</v>
@@ -11047,21 +11046,21 @@
         <v>30</v>
       </c>
       <c r="D74" s="28" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="E74" s="19" t="s">
         <v>276</v>
       </c>
       <c r="F74" s="19" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="G74" s="22" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="75" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A75" s="18" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="B75" s="19" t="s">
         <v>74</v>
@@ -11070,21 +11069,21 @@
         <v>27</v>
       </c>
       <c r="D75" s="28" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="E75" s="19" t="s">
         <v>274</v>
       </c>
       <c r="F75" s="19" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="G75" s="22" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="76" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="42" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="B76" s="39"/>
       <c r="C76" s="39"/>
@@ -11095,7 +11094,7 @@
     </row>
     <row r="77" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A77" s="18" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B77" s="19" t="s">
         <v>13</v>
@@ -11104,21 +11103,21 @@
         <v>151</v>
       </c>
       <c r="D77" s="29" t="s">
+        <v>476</v>
+      </c>
+      <c r="E77" s="19" t="s">
+        <v>477</v>
+      </c>
+      <c r="F77" s="19" t="s">
         <v>475</v>
       </c>
-      <c r="E77" s="19" t="s">
-        <v>476</v>
-      </c>
-      <c r="F77" s="19" t="s">
-        <v>474</v>
-      </c>
       <c r="G77" s="22" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
     </row>
     <row r="78" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A78" s="18" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B78" s="19" t="s">
         <v>74</v>
@@ -11127,21 +11126,21 @@
         <v>151</v>
       </c>
       <c r="D78" s="29" t="s">
+        <v>479</v>
+      </c>
+      <c r="E78" s="19" t="s">
+        <v>480</v>
+      </c>
+      <c r="F78" s="19" t="s">
+        <v>475</v>
+      </c>
+      <c r="G78" s="22" t="s">
         <v>478</v>
-      </c>
-      <c r="E78" s="19" t="s">
-        <v>479</v>
-      </c>
-      <c r="F78" s="19" t="s">
-        <v>474</v>
-      </c>
-      <c r="G78" s="22" t="s">
-        <v>477</v>
       </c>
     </row>
     <row r="79" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A79" s="18" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B79" s="19" t="s">
         <v>13</v>
@@ -11150,21 +11149,21 @@
         <v>193</v>
       </c>
       <c r="D79" s="29" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="E79" s="19" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="F79" s="19" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="G79" s="22" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
     </row>
     <row r="80" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A80" s="18" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B80" s="19" t="s">
         <v>74</v>
@@ -11173,21 +11172,21 @@
         <v>193</v>
       </c>
       <c r="D80" s="29" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="E80" s="19" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="F80" s="19" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="G80" s="22" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
     </row>
     <row r="81" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A81" s="18" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B81" s="19" t="s">
         <v>13</v>
@@ -11196,21 +11195,21 @@
         <v>112</v>
       </c>
       <c r="D81" s="29" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="E81" s="19" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="F81" s="19" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="G81" s="22" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
     </row>
     <row r="82" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A82" s="18" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B82" s="19" t="s">
         <v>74</v>
@@ -11219,21 +11218,21 @@
         <v>112</v>
       </c>
       <c r="D82" s="29" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="E82" s="19" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="F82" s="19" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="G82" s="22" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
     </row>
     <row r="83" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A83" s="18" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B83" s="19" t="s">
         <v>13</v>
@@ -11242,21 +11241,21 @@
         <v>137</v>
       </c>
       <c r="D83" s="29" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="E83" s="19" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="F83" s="19" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="G83" s="22" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
     </row>
     <row r="84" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A84" s="18" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B84" s="19" t="s">
         <v>74</v>
@@ -11265,21 +11264,21 @@
         <v>137</v>
       </c>
       <c r="D84" s="29" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="E84" s="19" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="F84" s="19" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="G84" s="22" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
     </row>
     <row r="85" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A85" s="18" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B85" s="19" t="s">
         <v>13</v>
@@ -11288,21 +11287,21 @@
         <v>215</v>
       </c>
       <c r="D85" s="29" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="E85" s="19" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="F85" s="19" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="G85" s="22" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
     </row>
     <row r="86" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A86" s="18" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B86" s="19" t="s">
         <v>74</v>
@@ -11311,21 +11310,21 @@
         <v>215</v>
       </c>
       <c r="D86" s="29" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="E86" s="19" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="F86" s="19" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="G86" s="22" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
     </row>
     <row r="87" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A87" s="18" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B87" s="19" t="s">
         <v>13</v>
@@ -11334,44 +11333,44 @@
         <v>218</v>
       </c>
       <c r="D87" s="29" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="E87" s="19" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="F87" s="19" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="G87" s="22" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
     </row>
     <row r="88" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A88" s="18" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B88" s="19" t="s">
         <v>13</v>
       </c>
       <c r="C88" s="20" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="D88" s="29" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="E88" s="19" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="F88" s="19" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="G88" s="22" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
     </row>
     <row r="89" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="42" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="B89" s="39"/>
       <c r="C89" s="39"/>
@@ -11382,7 +11381,7 @@
     </row>
     <row r="90" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A90" s="18" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="B90" s="19" t="s">
         <v>166</v>
@@ -11391,21 +11390,21 @@
         <v>205</v>
       </c>
       <c r="D90" s="30" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="E90" s="19" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="F90" s="19" t="s">
         <v>378</v>
       </c>
       <c r="G90" s="22" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
     </row>
     <row r="91" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A91" s="18" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="B91" s="19" t="s">
         <v>166</v>
@@ -11414,21 +11413,21 @@
         <v>218</v>
       </c>
       <c r="D91" s="30" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="E91" s="19" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="F91" s="19" t="s">
         <v>378</v>
       </c>
       <c r="G91" s="22" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
     </row>
     <row r="92" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A92" s="18" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="B92" s="19" t="s">
         <v>166</v>
@@ -11437,21 +11436,21 @@
         <v>114</v>
       </c>
       <c r="D92" s="30" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="E92" s="19" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="F92" s="19" t="s">
         <v>378</v>
       </c>
       <c r="G92" s="22" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
     </row>
     <row r="93" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A93" s="18" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="B93" s="19" t="s">
         <v>166</v>
@@ -11460,21 +11459,21 @@
         <v>193</v>
       </c>
       <c r="D93" s="30" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="E93" s="19" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="F93" s="19" t="s">
         <v>378</v>
       </c>
       <c r="G93" s="22" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
     </row>
     <row r="94" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A94" s="18" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="B94" s="19" t="s">
         <v>268</v>
@@ -11483,21 +11482,21 @@
         <v>193</v>
       </c>
       <c r="D94" s="30" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="E94" s="19" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="F94" s="19" t="s">
         <v>378</v>
       </c>
       <c r="G94" s="22" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
     </row>
     <row r="95" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A95" s="18" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="B95" s="19" t="s">
         <v>13</v>
@@ -11506,21 +11505,21 @@
         <v>155</v>
       </c>
       <c r="D95" s="30" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="E95" s="19" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="F95" s="19" t="s">
         <v>378</v>
       </c>
       <c r="G95" s="22" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
     </row>
     <row r="96" spans="1:7" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A96" s="18" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="B96" s="19" t="s">
         <v>13</v>
@@ -11529,16 +11528,16 @@
         <v>157</v>
       </c>
       <c r="D96" s="30" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="E96" s="19" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="F96" s="19" t="s">
         <v>378</v>
       </c>
       <c r="G96" s="22" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
     </row>
   </sheetData>
@@ -11572,7 +11571,7 @@
   <sheetData>
     <row r="1" spans="1:9" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A1" s="47" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="B1" s="39"/>
       <c r="C1" s="39"/>
@@ -11584,7 +11583,7 @@
     </row>
     <row r="2" spans="1:9" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A2" s="41" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="B2" s="39"/>
       <c r="C2" s="39"/>
@@ -11602,30 +11601,30 @@
         <v>3</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="38" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="B4" s="39"/>
       <c r="C4" s="39"/>
@@ -11648,13 +11647,13 @@
       <c r="E5" s="32"/>
       <c r="F5" s="33"/>
       <c r="G5" s="34" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H5" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I5" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -11669,13 +11668,13 @@
       <c r="E6" s="32"/>
       <c r="F6" s="33"/>
       <c r="G6" s="34" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H6" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I6" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -11690,13 +11689,13 @@
       <c r="E7" s="32"/>
       <c r="F7" s="33"/>
       <c r="G7" s="34" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H7" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I7" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -11711,13 +11710,13 @@
       <c r="E8" s="32"/>
       <c r="F8" s="33"/>
       <c r="G8" s="34" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H8" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I8" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -11732,13 +11731,13 @@
       <c r="E9" s="32"/>
       <c r="F9" s="33"/>
       <c r="G9" s="34" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H9" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I9" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -11753,13 +11752,13 @@
       <c r="E10" s="32"/>
       <c r="F10" s="33"/>
       <c r="G10" s="34" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H10" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I10" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -11774,13 +11773,13 @@
       <c r="E11" s="32"/>
       <c r="F11" s="33"/>
       <c r="G11" s="34" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H11" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I11" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -11795,13 +11794,13 @@
       <c r="E12" s="32"/>
       <c r="F12" s="33"/>
       <c r="G12" s="34" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H12" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I12" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -11816,13 +11815,13 @@
       <c r="E13" s="32"/>
       <c r="F13" s="33"/>
       <c r="G13" s="34" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H13" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I13" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -11830,20 +11829,20 @@
         <v>13</v>
       </c>
       <c r="B14" s="20" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="C14" s="19"/>
       <c r="D14" s="31"/>
       <c r="E14" s="32"/>
       <c r="F14" s="33"/>
       <c r="G14" s="34" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H14" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I14" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -11858,13 +11857,13 @@
       <c r="E15" s="32"/>
       <c r="F15" s="33"/>
       <c r="G15" s="34" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H15" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I15" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="16" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -11879,13 +11878,13 @@
       <c r="E16" s="32"/>
       <c r="F16" s="33"/>
       <c r="G16" s="34" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H16" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I16" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="17" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -11900,13 +11899,13 @@
       <c r="E17" s="32"/>
       <c r="F17" s="33"/>
       <c r="G17" s="34" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H17" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I17" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="18" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -11921,13 +11920,13 @@
       <c r="E18" s="32"/>
       <c r="F18" s="33"/>
       <c r="G18" s="34" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H18" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I18" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="19" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -11935,20 +11934,20 @@
         <v>13</v>
       </c>
       <c r="B19" s="20" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="C19" s="19"/>
       <c r="D19" s="31"/>
       <c r="E19" s="32"/>
       <c r="F19" s="33"/>
       <c r="G19" s="34" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H19" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I19" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="20" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -11963,13 +11962,13 @@
       <c r="E20" s="32"/>
       <c r="F20" s="33"/>
       <c r="G20" s="34" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H20" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I20" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="21" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -11984,13 +11983,13 @@
       <c r="E21" s="32"/>
       <c r="F21" s="33"/>
       <c r="G21" s="34" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H21" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I21" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="22" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -12005,13 +12004,13 @@
       <c r="E22" s="32"/>
       <c r="F22" s="33"/>
       <c r="G22" s="34" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H22" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I22" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="23" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -12026,13 +12025,13 @@
       <c r="E23" s="32"/>
       <c r="F23" s="33"/>
       <c r="G23" s="34" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H23" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I23" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="24" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -12047,13 +12046,13 @@
       <c r="E24" s="32"/>
       <c r="F24" s="33"/>
       <c r="G24" s="34" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H24" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I24" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="25" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -12061,20 +12060,20 @@
         <v>13</v>
       </c>
       <c r="B25" s="20" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="C25" s="19"/>
       <c r="D25" s="31"/>
       <c r="E25" s="32"/>
       <c r="F25" s="33"/>
       <c r="G25" s="34" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H25" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I25" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="26" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -12089,13 +12088,13 @@
       <c r="E26" s="32"/>
       <c r="F26" s="33"/>
       <c r="G26" s="34" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H26" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I26" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="27" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -12110,13 +12109,13 @@
       <c r="E27" s="32"/>
       <c r="F27" s="33"/>
       <c r="G27" s="34" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H27" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I27" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="28" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -12131,13 +12130,13 @@
       <c r="E28" s="32"/>
       <c r="F28" s="33"/>
       <c r="G28" s="34" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H28" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I28" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="29" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -12152,13 +12151,13 @@
       <c r="E29" s="32"/>
       <c r="F29" s="33"/>
       <c r="G29" s="34" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H29" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I29" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="30" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -12173,13 +12172,13 @@
       <c r="E30" s="32"/>
       <c r="F30" s="33"/>
       <c r="G30" s="34" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H30" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I30" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="31" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -12191,16 +12190,16 @@
       </c>
       <c r="C31" s="19"/>
       <c r="D31" s="23" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="E31" s="25" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="F31" s="33"/>
       <c r="G31" s="37"/>
       <c r="H31" s="37"/>
       <c r="I31" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="32" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -12213,15 +12212,15 @@
       <c r="C32" s="19"/>
       <c r="D32" s="31"/>
       <c r="E32" s="25" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="F32" s="33"/>
       <c r="G32" s="34" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H32" s="37"/>
       <c r="I32" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="33" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -12234,15 +12233,15 @@
       <c r="C33" s="19"/>
       <c r="D33" s="31"/>
       <c r="E33" s="25" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="F33" s="33"/>
       <c r="G33" s="34" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H33" s="37"/>
       <c r="I33" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="34" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -12255,15 +12254,15 @@
       <c r="C34" s="19"/>
       <c r="D34" s="31"/>
       <c r="E34" s="25" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="F34" s="33"/>
       <c r="G34" s="34" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H34" s="37"/>
       <c r="I34" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="35" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -12271,20 +12270,20 @@
         <v>13</v>
       </c>
       <c r="B35" s="20" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="C35" s="19"/>
       <c r="D35" s="31"/>
       <c r="E35" s="32"/>
       <c r="F35" s="33"/>
       <c r="G35" s="34" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H35" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I35" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="36" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -12292,20 +12291,20 @@
         <v>13</v>
       </c>
       <c r="B36" s="20" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="C36" s="19"/>
       <c r="D36" s="31"/>
       <c r="E36" s="32"/>
       <c r="F36" s="33"/>
       <c r="G36" s="34" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H36" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I36" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="37" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -12313,20 +12312,20 @@
         <v>13</v>
       </c>
       <c r="B37" s="20" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="C37" s="19"/>
       <c r="D37" s="31"/>
       <c r="E37" s="32"/>
       <c r="F37" s="33"/>
       <c r="G37" s="34" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H37" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I37" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="38" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -12334,20 +12333,20 @@
         <v>13</v>
       </c>
       <c r="B38" s="20" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="C38" s="19"/>
       <c r="D38" s="31"/>
       <c r="E38" s="32"/>
       <c r="F38" s="33"/>
       <c r="G38" s="34" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H38" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I38" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="39" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -12355,20 +12354,20 @@
         <v>13</v>
       </c>
       <c r="B39" s="20" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="C39" s="19"/>
       <c r="D39" s="31"/>
       <c r="E39" s="32"/>
       <c r="F39" s="33"/>
       <c r="G39" s="34" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H39" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I39" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="40" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -12381,15 +12380,15 @@
       <c r="C40" s="19"/>
       <c r="D40" s="31"/>
       <c r="E40" s="25" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="F40" s="33"/>
       <c r="G40" s="34" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H40" s="37"/>
       <c r="I40" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="41" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -12403,13 +12402,13 @@
       <c r="D41" s="31"/>
       <c r="E41" s="32"/>
       <c r="F41" s="26" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="G41" s="34" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H41" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I41" s="37"/>
     </row>
@@ -12422,16 +12421,16 @@
       </c>
       <c r="C42" s="19"/>
       <c r="D42" s="23" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="E42" s="32"/>
       <c r="F42" s="33"/>
       <c r="G42" s="37"/>
       <c r="H42" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I42" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="43" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -12443,16 +12442,16 @@
       </c>
       <c r="C43" s="19"/>
       <c r="D43" s="23" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="E43" s="32"/>
       <c r="F43" s="33"/>
       <c r="G43" s="37"/>
       <c r="H43" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I43" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="44" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -12460,20 +12459,20 @@
         <v>13</v>
       </c>
       <c r="B44" s="20" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="C44" s="19"/>
       <c r="D44" s="31"/>
       <c r="E44" s="32"/>
       <c r="F44" s="33"/>
       <c r="G44" s="34" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H44" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I44" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="45" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -12481,25 +12480,25 @@
         <v>13</v>
       </c>
       <c r="B45" s="20" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="C45" s="19"/>
       <c r="D45" s="31"/>
       <c r="E45" s="32"/>
       <c r="F45" s="33"/>
       <c r="G45" s="34" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H45" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I45" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="46" spans="1:9" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="38" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="B46" s="39"/>
       <c r="C46" s="39"/>
@@ -12522,13 +12521,13 @@
       <c r="E47" s="32"/>
       <c r="F47" s="33"/>
       <c r="G47" s="34" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H47" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I47" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="48" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -12543,13 +12542,13 @@
       <c r="E48" s="32"/>
       <c r="F48" s="33"/>
       <c r="G48" s="34" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H48" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I48" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="49" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -12564,13 +12563,13 @@
       <c r="E49" s="32"/>
       <c r="F49" s="33"/>
       <c r="G49" s="34" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H49" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I49" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="50" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -12585,13 +12584,13 @@
       <c r="E50" s="32"/>
       <c r="F50" s="33"/>
       <c r="G50" s="34" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H50" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I50" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="51" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -12606,13 +12605,13 @@
       <c r="E51" s="32"/>
       <c r="F51" s="33"/>
       <c r="G51" s="34" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H51" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I51" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="52" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -12627,13 +12626,13 @@
       <c r="E52" s="32"/>
       <c r="F52" s="33"/>
       <c r="G52" s="34" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H52" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I52" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="53" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -12648,13 +12647,13 @@
       <c r="E53" s="32"/>
       <c r="F53" s="33"/>
       <c r="G53" s="34" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H53" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I53" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="54" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -12669,13 +12668,13 @@
       <c r="E54" s="32"/>
       <c r="F54" s="33"/>
       <c r="G54" s="34" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H54" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I54" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="55" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -12690,13 +12689,13 @@
       <c r="E55" s="32"/>
       <c r="F55" s="33"/>
       <c r="G55" s="34" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H55" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I55" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="56" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -12704,20 +12703,20 @@
         <v>74</v>
       </c>
       <c r="B56" s="20" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="C56" s="19"/>
       <c r="D56" s="31"/>
       <c r="E56" s="32"/>
       <c r="F56" s="33"/>
       <c r="G56" s="34" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H56" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I56" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="57" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -12732,13 +12731,13 @@
       <c r="E57" s="32"/>
       <c r="F57" s="33"/>
       <c r="G57" s="34" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H57" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I57" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="58" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -12753,13 +12752,13 @@
       <c r="E58" s="32"/>
       <c r="F58" s="33"/>
       <c r="G58" s="34" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H58" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I58" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="59" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -12774,13 +12773,13 @@
       <c r="E59" s="32"/>
       <c r="F59" s="33"/>
       <c r="G59" s="34" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H59" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I59" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="60" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -12795,13 +12794,13 @@
       <c r="E60" s="32"/>
       <c r="F60" s="33"/>
       <c r="G60" s="34" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H60" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I60" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="61" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -12809,20 +12808,20 @@
         <v>74</v>
       </c>
       <c r="B61" s="20" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="C61" s="19"/>
       <c r="D61" s="31"/>
       <c r="E61" s="32"/>
       <c r="F61" s="33"/>
       <c r="G61" s="34" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H61" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I61" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="62" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -12837,13 +12836,13 @@
       <c r="E62" s="32"/>
       <c r="F62" s="33"/>
       <c r="G62" s="34" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H62" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I62" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="63" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -12858,13 +12857,13 @@
       <c r="E63" s="32"/>
       <c r="F63" s="33"/>
       <c r="G63" s="34" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H63" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I63" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="64" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -12879,13 +12878,13 @@
       <c r="E64" s="32"/>
       <c r="F64" s="33"/>
       <c r="G64" s="34" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H64" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I64" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="65" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -12900,13 +12899,13 @@
       <c r="E65" s="32"/>
       <c r="F65" s="33"/>
       <c r="G65" s="34" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H65" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I65" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="66" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -12921,13 +12920,13 @@
       <c r="E66" s="32"/>
       <c r="F66" s="33"/>
       <c r="G66" s="34" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H66" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I66" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="67" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -12935,20 +12934,20 @@
         <v>74</v>
       </c>
       <c r="B67" s="20" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="C67" s="19"/>
       <c r="D67" s="31"/>
       <c r="E67" s="32"/>
       <c r="F67" s="33"/>
       <c r="G67" s="34" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H67" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I67" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="68" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -12963,13 +12962,13 @@
       <c r="E68" s="32"/>
       <c r="F68" s="33"/>
       <c r="G68" s="34" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H68" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I68" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="69" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -12984,13 +12983,13 @@
       <c r="E69" s="32"/>
       <c r="F69" s="33"/>
       <c r="G69" s="34" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H69" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I69" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="70" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -13005,13 +13004,13 @@
       <c r="E70" s="32"/>
       <c r="F70" s="33"/>
       <c r="G70" s="34" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H70" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I70" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="71" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -13026,13 +13025,13 @@
       <c r="E71" s="32"/>
       <c r="F71" s="33"/>
       <c r="G71" s="34" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H71" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I71" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="72" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -13047,13 +13046,13 @@
       <c r="E72" s="32"/>
       <c r="F72" s="33"/>
       <c r="G72" s="34" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H72" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I72" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="73" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -13066,15 +13065,15 @@
       <c r="C73" s="19"/>
       <c r="D73" s="31"/>
       <c r="E73" s="25" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="F73" s="33"/>
       <c r="G73" s="34" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H73" s="37"/>
       <c r="I73" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="74" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -13087,15 +13086,15 @@
       <c r="C74" s="19"/>
       <c r="D74" s="31"/>
       <c r="E74" s="25" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="F74" s="33"/>
       <c r="G74" s="34" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H74" s="37"/>
       <c r="I74" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="75" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -13108,15 +13107,15 @@
       <c r="C75" s="19"/>
       <c r="D75" s="31"/>
       <c r="E75" s="25" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="F75" s="33"/>
       <c r="G75" s="34" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H75" s="37"/>
       <c r="I75" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="76" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -13129,15 +13128,15 @@
       <c r="C76" s="19"/>
       <c r="D76" s="31"/>
       <c r="E76" s="25" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="F76" s="33"/>
       <c r="G76" s="34" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H76" s="37"/>
       <c r="I76" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="77" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -13150,15 +13149,15 @@
       <c r="C77" s="19"/>
       <c r="D77" s="31"/>
       <c r="E77" s="25" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="F77" s="33"/>
       <c r="G77" s="34" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H77" s="37"/>
       <c r="I77" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="78" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -13166,20 +13165,20 @@
         <v>74</v>
       </c>
       <c r="B78" s="20" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="C78" s="19"/>
       <c r="D78" s="31"/>
       <c r="E78" s="32"/>
       <c r="F78" s="33"/>
       <c r="G78" s="34" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H78" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I78" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="79" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -13187,20 +13186,20 @@
         <v>74</v>
       </c>
       <c r="B79" s="20" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="C79" s="19"/>
       <c r="D79" s="31"/>
       <c r="E79" s="32"/>
       <c r="F79" s="33"/>
       <c r="G79" s="34" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H79" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I79" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="80" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -13208,20 +13207,20 @@
         <v>74</v>
       </c>
       <c r="B80" s="20" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="C80" s="19"/>
       <c r="D80" s="31"/>
       <c r="E80" s="32"/>
       <c r="F80" s="33"/>
       <c r="G80" s="34" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H80" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I80" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="81" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -13229,20 +13228,20 @@
         <v>74</v>
       </c>
       <c r="B81" s="20" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="C81" s="19"/>
       <c r="D81" s="31"/>
       <c r="E81" s="32"/>
       <c r="F81" s="33"/>
       <c r="G81" s="34" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H81" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I81" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="82" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -13250,20 +13249,20 @@
         <v>74</v>
       </c>
       <c r="B82" s="20" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="C82" s="19"/>
       <c r="D82" s="31"/>
       <c r="E82" s="32"/>
       <c r="F82" s="33"/>
       <c r="G82" s="34" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H82" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I82" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="83" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -13278,13 +13277,13 @@
       <c r="E83" s="32"/>
       <c r="F83" s="33"/>
       <c r="G83" s="34" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H83" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I83" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="84" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -13299,13 +13298,13 @@
       <c r="E84" s="32"/>
       <c r="F84" s="33"/>
       <c r="G84" s="34" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H84" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I84" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="85" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -13318,15 +13317,15 @@
       <c r="C85" s="19"/>
       <c r="D85" s="31"/>
       <c r="E85" s="25" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="F85" s="33"/>
       <c r="G85" s="34" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H85" s="37"/>
       <c r="I85" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="86" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -13341,13 +13340,13 @@
       <c r="E86" s="32"/>
       <c r="F86" s="33"/>
       <c r="G86" s="34" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H86" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I86" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="87" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -13359,16 +13358,16 @@
       </c>
       <c r="C87" s="19"/>
       <c r="D87" s="23" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="E87" s="25" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="F87" s="33"/>
       <c r="G87" s="37"/>
       <c r="H87" s="37"/>
       <c r="I87" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="88" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -13380,16 +13379,16 @@
       </c>
       <c r="C88" s="19"/>
       <c r="D88" s="23" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="E88" s="25" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="F88" s="33"/>
       <c r="G88" s="37"/>
       <c r="H88" s="37"/>
       <c r="I88" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="89" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -13401,16 +13400,16 @@
       </c>
       <c r="C89" s="19"/>
       <c r="D89" s="23" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="E89" s="32"/>
       <c r="F89" s="33"/>
       <c r="G89" s="37"/>
       <c r="H89" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I89" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="90" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -13422,16 +13421,16 @@
       </c>
       <c r="C90" s="19"/>
       <c r="D90" s="23" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="E90" s="32"/>
       <c r="F90" s="33"/>
       <c r="G90" s="37"/>
       <c r="H90" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I90" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="91" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -13439,20 +13438,20 @@
         <v>74</v>
       </c>
       <c r="B91" s="20" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="C91" s="19"/>
       <c r="D91" s="31"/>
       <c r="E91" s="32"/>
       <c r="F91" s="33"/>
       <c r="G91" s="34" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H91" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I91" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="92" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -13460,25 +13459,25 @@
         <v>74</v>
       </c>
       <c r="B92" s="20" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="C92" s="19"/>
       <c r="D92" s="31"/>
       <c r="E92" s="32"/>
       <c r="F92" s="33"/>
       <c r="G92" s="34" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H92" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I92" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="93" spans="1:9" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A93" s="38" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="B93" s="39"/>
       <c r="C93" s="39"/>
@@ -13498,16 +13497,16 @@
       </c>
       <c r="C94" s="19"/>
       <c r="D94" s="23" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="E94" s="25" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="F94" s="33"/>
       <c r="G94" s="37"/>
       <c r="H94" s="37"/>
       <c r="I94" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="95" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -13519,16 +13518,16 @@
       </c>
       <c r="C95" s="19"/>
       <c r="D95" s="23" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="E95" s="32"/>
       <c r="F95" s="33"/>
       <c r="G95" s="37"/>
       <c r="H95" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I95" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="96" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -13540,16 +13539,16 @@
       </c>
       <c r="C96" s="19"/>
       <c r="D96" s="23" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="E96" s="32"/>
       <c r="F96" s="33"/>
       <c r="G96" s="37"/>
       <c r="H96" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I96" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="97" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -13561,16 +13560,16 @@
       </c>
       <c r="C97" s="19"/>
       <c r="D97" s="23" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="E97" s="32"/>
       <c r="F97" s="33"/>
       <c r="G97" s="37"/>
       <c r="H97" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I97" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="98" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -13582,16 +13581,16 @@
       </c>
       <c r="C98" s="19"/>
       <c r="D98" s="23" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="E98" s="25" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="F98" s="33"/>
       <c r="G98" s="37"/>
       <c r="H98" s="37"/>
       <c r="I98" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="99" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -13603,16 +13602,16 @@
       </c>
       <c r="C99" s="19"/>
       <c r="D99" s="23" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="E99" s="32"/>
       <c r="F99" s="33"/>
       <c r="G99" s="37"/>
       <c r="H99" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I99" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="100" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -13620,20 +13619,20 @@
         <v>99</v>
       </c>
       <c r="B100" s="20" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="C100" s="19"/>
       <c r="D100" s="31"/>
       <c r="E100" s="32"/>
       <c r="F100" s="33"/>
       <c r="G100" s="34" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H100" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I100" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="101" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -13651,10 +13650,10 @@
       <c r="F101" s="33"/>
       <c r="G101" s="37"/>
       <c r="H101" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I101" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="102" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -13669,13 +13668,13 @@
       <c r="E102" s="32"/>
       <c r="F102" s="33"/>
       <c r="G102" s="34" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H102" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I102" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="103" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -13690,13 +13689,13 @@
       <c r="E103" s="32"/>
       <c r="F103" s="33"/>
       <c r="G103" s="34" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H103" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I103" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="104" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -13708,16 +13707,16 @@
       </c>
       <c r="C104" s="19"/>
       <c r="D104" s="23" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="E104" s="25" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="F104" s="33"/>
       <c r="G104" s="37"/>
       <c r="H104" s="37"/>
       <c r="I104" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="105" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -13725,20 +13724,20 @@
         <v>99</v>
       </c>
       <c r="B105" s="20" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="C105" s="19"/>
       <c r="D105" s="31"/>
       <c r="E105" s="32"/>
       <c r="F105" s="33"/>
       <c r="G105" s="34" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H105" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I105" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="106" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -13750,16 +13749,16 @@
       </c>
       <c r="C106" s="19"/>
       <c r="D106" s="23" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="E106" s="25" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="F106" s="33"/>
       <c r="G106" s="37"/>
       <c r="H106" s="37"/>
       <c r="I106" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="107" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -13774,13 +13773,13 @@
       <c r="E107" s="32"/>
       <c r="F107" s="33"/>
       <c r="G107" s="34" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H107" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I107" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="108" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -13795,13 +13794,13 @@
       <c r="E108" s="32"/>
       <c r="F108" s="33"/>
       <c r="G108" s="34" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H108" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I108" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="109" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -13813,16 +13812,16 @@
       </c>
       <c r="C109" s="19"/>
       <c r="D109" s="23" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="E109" s="32"/>
       <c r="F109" s="33"/>
       <c r="G109" s="37"/>
       <c r="H109" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I109" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="110" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -13837,13 +13836,13 @@
       <c r="E110" s="32"/>
       <c r="F110" s="33"/>
       <c r="G110" s="34" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H110" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I110" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="111" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -13851,20 +13850,20 @@
         <v>99</v>
       </c>
       <c r="B111" s="20" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="C111" s="19"/>
       <c r="D111" s="31"/>
       <c r="E111" s="32"/>
       <c r="F111" s="33"/>
       <c r="G111" s="34" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H111" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I111" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="112" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -13876,16 +13875,16 @@
       </c>
       <c r="C112" s="19"/>
       <c r="D112" s="23" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="E112" s="32"/>
       <c r="F112" s="33"/>
       <c r="G112" s="37"/>
       <c r="H112" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I112" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="113" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -13900,13 +13899,13 @@
       <c r="E113" s="32"/>
       <c r="F113" s="33"/>
       <c r="G113" s="34" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H113" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I113" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="114" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -13918,16 +13917,16 @@
       </c>
       <c r="C114" s="19"/>
       <c r="D114" s="23" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="E114" s="32"/>
       <c r="F114" s="33"/>
       <c r="G114" s="37"/>
       <c r="H114" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I114" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="115" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -13939,16 +13938,16 @@
       </c>
       <c r="C115" s="19"/>
       <c r="D115" s="23" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="E115" s="32"/>
       <c r="F115" s="33"/>
       <c r="G115" s="37"/>
       <c r="H115" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I115" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="116" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -13960,16 +13959,16 @@
       </c>
       <c r="C116" s="19"/>
       <c r="D116" s="23" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="E116" s="32"/>
       <c r="F116" s="33"/>
       <c r="G116" s="37"/>
       <c r="H116" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I116" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="117" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -13984,13 +13983,13 @@
       <c r="E117" s="32"/>
       <c r="F117" s="33"/>
       <c r="G117" s="34" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H117" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I117" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="118" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -14005,13 +14004,13 @@
       <c r="E118" s="32"/>
       <c r="F118" s="33"/>
       <c r="G118" s="34" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H118" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I118" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="119" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -14026,13 +14025,13 @@
       <c r="E119" s="32"/>
       <c r="F119" s="33"/>
       <c r="G119" s="34" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H119" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I119" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="120" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -14047,13 +14046,13 @@
       <c r="E120" s="32"/>
       <c r="F120" s="33"/>
       <c r="G120" s="34" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H120" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I120" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="121" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -14068,13 +14067,13 @@
       <c r="E121" s="32"/>
       <c r="F121" s="33"/>
       <c r="G121" s="34" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H121" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I121" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="122" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -14082,20 +14081,20 @@
         <v>99</v>
       </c>
       <c r="B122" s="20" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="C122" s="19"/>
       <c r="D122" s="31"/>
       <c r="E122" s="32"/>
       <c r="F122" s="33"/>
       <c r="G122" s="34" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H122" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I122" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="123" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -14103,20 +14102,20 @@
         <v>99</v>
       </c>
       <c r="B123" s="20" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="C123" s="19"/>
       <c r="D123" s="31"/>
       <c r="E123" s="32"/>
       <c r="F123" s="33"/>
       <c r="G123" s="34" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H123" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I123" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="124" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -14124,20 +14123,20 @@
         <v>99</v>
       </c>
       <c r="B124" s="20" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="C124" s="19"/>
       <c r="D124" s="31"/>
       <c r="E124" s="32"/>
       <c r="F124" s="33"/>
       <c r="G124" s="34" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H124" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I124" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="125" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -14145,20 +14144,20 @@
         <v>99</v>
       </c>
       <c r="B125" s="20" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="C125" s="19"/>
       <c r="D125" s="31"/>
       <c r="E125" s="32"/>
       <c r="F125" s="33"/>
       <c r="G125" s="34" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H125" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I125" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="126" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -14166,20 +14165,20 @@
         <v>99</v>
       </c>
       <c r="B126" s="20" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="C126" s="19"/>
       <c r="D126" s="31"/>
       <c r="E126" s="32"/>
       <c r="F126" s="33"/>
       <c r="G126" s="34" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H126" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I126" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="127" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -14194,13 +14193,13 @@
       <c r="E127" s="32"/>
       <c r="F127" s="33"/>
       <c r="G127" s="34" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H127" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I127" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="128" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -14215,13 +14214,13 @@
       <c r="E128" s="32"/>
       <c r="F128" s="33"/>
       <c r="G128" s="34" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H128" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I128" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="129" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -14233,16 +14232,16 @@
       </c>
       <c r="C129" s="19"/>
       <c r="D129" s="23" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="E129" s="25" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="F129" s="33"/>
       <c r="G129" s="37"/>
       <c r="H129" s="37"/>
       <c r="I129" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="130" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -14257,13 +14256,13 @@
       <c r="E130" s="32"/>
       <c r="F130" s="33"/>
       <c r="G130" s="34" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H130" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I130" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="131" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -14278,13 +14277,13 @@
       <c r="E131" s="32"/>
       <c r="F131" s="33"/>
       <c r="G131" s="34" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H131" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I131" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="132" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -14299,13 +14298,13 @@
       <c r="E132" s="32"/>
       <c r="F132" s="33"/>
       <c r="G132" s="34" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H132" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I132" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="133" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -14320,13 +14319,13 @@
       <c r="E133" s="32"/>
       <c r="F133" s="33"/>
       <c r="G133" s="34" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H133" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I133" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="134" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -14341,13 +14340,13 @@
       <c r="E134" s="32"/>
       <c r="F134" s="33"/>
       <c r="G134" s="34" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H134" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I134" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="135" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -14355,20 +14354,20 @@
         <v>99</v>
       </c>
       <c r="B135" s="20" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="C135" s="19"/>
       <c r="D135" s="31"/>
       <c r="E135" s="32"/>
       <c r="F135" s="33"/>
       <c r="G135" s="34" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H135" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I135" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="136" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -14376,25 +14375,25 @@
         <v>99</v>
       </c>
       <c r="B136" s="20" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="C136" s="19"/>
       <c r="D136" s="31"/>
       <c r="E136" s="32"/>
       <c r="F136" s="33"/>
       <c r="G136" s="34" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H136" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I136" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="137" spans="1:9" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A137" s="38" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="B137" s="39"/>
       <c r="C137" s="39"/>
@@ -14417,13 +14416,13 @@
       <c r="E138" s="32"/>
       <c r="F138" s="33"/>
       <c r="G138" s="34" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H138" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I138" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="139" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -14435,16 +14434,16 @@
       </c>
       <c r="C139" s="19"/>
       <c r="D139" s="23" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="E139" s="32"/>
       <c r="F139" s="33"/>
       <c r="G139" s="37"/>
       <c r="H139" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I139" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="140" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -14456,16 +14455,16 @@
       </c>
       <c r="C140" s="19"/>
       <c r="D140" s="23" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="E140" s="32"/>
       <c r="F140" s="33"/>
       <c r="G140" s="37"/>
       <c r="H140" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I140" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="141" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -14480,13 +14479,13 @@
       <c r="E141" s="32"/>
       <c r="F141" s="33"/>
       <c r="G141" s="34" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H141" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I141" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="142" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -14494,20 +14493,20 @@
         <v>166</v>
       </c>
       <c r="B142" s="20" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="C142" s="19"/>
       <c r="D142" s="31"/>
       <c r="E142" s="32"/>
       <c r="F142" s="33"/>
       <c r="G142" s="34" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H142" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I142" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="143" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -14522,13 +14521,13 @@
       <c r="E143" s="32"/>
       <c r="F143" s="33"/>
       <c r="G143" s="34" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H143" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I143" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="144" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -14536,20 +14535,20 @@
         <v>166</v>
       </c>
       <c r="B144" s="20" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="C144" s="19"/>
       <c r="D144" s="31"/>
       <c r="E144" s="32"/>
       <c r="F144" s="33"/>
       <c r="G144" s="34" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H144" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I144" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="145" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -14557,20 +14556,20 @@
         <v>166</v>
       </c>
       <c r="B145" s="20" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="C145" s="19"/>
       <c r="D145" s="31"/>
       <c r="E145" s="32"/>
       <c r="F145" s="33"/>
       <c r="G145" s="34" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H145" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I145" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="146" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -14585,13 +14584,13 @@
       <c r="E146" s="32"/>
       <c r="F146" s="33"/>
       <c r="G146" s="34" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H146" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I146" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="147" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -14606,13 +14605,13 @@
       <c r="E147" s="32"/>
       <c r="F147" s="33"/>
       <c r="G147" s="34" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H147" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I147" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="148" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -14627,13 +14626,13 @@
       <c r="E148" s="32"/>
       <c r="F148" s="33"/>
       <c r="G148" s="34" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H148" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I148" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="149" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -14648,13 +14647,13 @@
       <c r="E149" s="32"/>
       <c r="F149" s="33"/>
       <c r="G149" s="34" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H149" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I149" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="150" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -14669,13 +14668,13 @@
       <c r="E150" s="32"/>
       <c r="F150" s="33"/>
       <c r="G150" s="34" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H150" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I150" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="151" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -14690,13 +14689,13 @@
       <c r="E151" s="32"/>
       <c r="F151" s="33"/>
       <c r="G151" s="34" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H151" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I151" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="152" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -14711,13 +14710,13 @@
       <c r="E152" s="32"/>
       <c r="F152" s="33"/>
       <c r="G152" s="34" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H152" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I152" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="153" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -14732,13 +14731,13 @@
       <c r="E153" s="32"/>
       <c r="F153" s="33"/>
       <c r="G153" s="34" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H153" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I153" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="154" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -14753,13 +14752,13 @@
       <c r="E154" s="32"/>
       <c r="F154" s="33"/>
       <c r="G154" s="34" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H154" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I154" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="155" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -14767,20 +14766,20 @@
         <v>166</v>
       </c>
       <c r="B155" s="20" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="C155" s="19"/>
       <c r="D155" s="31"/>
       <c r="E155" s="32"/>
       <c r="F155" s="33"/>
       <c r="G155" s="34" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H155" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I155" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="156" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -14788,20 +14787,20 @@
         <v>166</v>
       </c>
       <c r="B156" s="20" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="C156" s="19"/>
       <c r="D156" s="31"/>
       <c r="E156" s="32"/>
       <c r="F156" s="33"/>
       <c r="G156" s="34" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H156" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I156" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="157" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -14809,20 +14808,20 @@
         <v>166</v>
       </c>
       <c r="B157" s="20" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="C157" s="19"/>
       <c r="D157" s="31"/>
       <c r="E157" s="32"/>
       <c r="F157" s="33"/>
       <c r="G157" s="34" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H157" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I157" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="158" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -14830,20 +14829,20 @@
         <v>166</v>
       </c>
       <c r="B158" s="20" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="C158" s="19"/>
       <c r="D158" s="31"/>
       <c r="E158" s="32"/>
       <c r="F158" s="33"/>
       <c r="G158" s="34" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H158" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I158" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="159" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -14851,20 +14850,20 @@
         <v>166</v>
       </c>
       <c r="B159" s="20" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="C159" s="19"/>
       <c r="D159" s="31"/>
       <c r="E159" s="32"/>
       <c r="F159" s="33"/>
       <c r="G159" s="34" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H159" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I159" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="160" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -14879,13 +14878,13 @@
       <c r="E160" s="32"/>
       <c r="F160" s="33"/>
       <c r="G160" s="34" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H160" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I160" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="161" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -14900,13 +14899,13 @@
       <c r="E161" s="32"/>
       <c r="F161" s="33"/>
       <c r="G161" s="34" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H161" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I161" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="162" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -14921,13 +14920,13 @@
       <c r="E162" s="32"/>
       <c r="F162" s="33"/>
       <c r="G162" s="34" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H162" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I162" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="163" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -14939,15 +14938,15 @@
       </c>
       <c r="C163" s="19"/>
       <c r="D163" s="23" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="E163" s="32"/>
       <c r="F163" s="26" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="G163" s="37"/>
       <c r="H163" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I163" s="37"/>
     </row>
@@ -14960,16 +14959,16 @@
       </c>
       <c r="C164" s="19"/>
       <c r="D164" s="23" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="E164" s="32"/>
       <c r="F164" s="33"/>
       <c r="G164" s="37"/>
       <c r="H164" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I164" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="165" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -14981,16 +14980,16 @@
       </c>
       <c r="C165" s="19"/>
       <c r="D165" s="23" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="E165" s="32"/>
       <c r="F165" s="33"/>
       <c r="G165" s="37"/>
       <c r="H165" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I165" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="166" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -15002,16 +15001,16 @@
       </c>
       <c r="C166" s="19"/>
       <c r="D166" s="23" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="E166" s="32"/>
       <c r="F166" s="33"/>
       <c r="G166" s="37"/>
       <c r="H166" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I166" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="167" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -15023,16 +15022,16 @@
       </c>
       <c r="C167" s="19"/>
       <c r="D167" s="23" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="E167" s="32"/>
       <c r="F167" s="33"/>
       <c r="G167" s="37"/>
       <c r="H167" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I167" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="168" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -15040,20 +15039,20 @@
         <v>166</v>
       </c>
       <c r="B168" s="20" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="C168" s="19"/>
       <c r="D168" s="31"/>
       <c r="E168" s="32"/>
       <c r="F168" s="33"/>
       <c r="G168" s="34" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H168" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I168" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="169" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -15061,25 +15060,25 @@
         <v>166</v>
       </c>
       <c r="B169" s="20" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="C169" s="19"/>
       <c r="D169" s="31"/>
       <c r="E169" s="32"/>
       <c r="F169" s="33"/>
       <c r="G169" s="34" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H169" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I169" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="170" spans="1:9" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A170" s="38" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="B170" s="39"/>
       <c r="C170" s="39"/>
@@ -15099,16 +15098,16 @@
       </c>
       <c r="C171" s="19"/>
       <c r="D171" s="23" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="E171" s="32"/>
       <c r="F171" s="33"/>
       <c r="G171" s="37"/>
       <c r="H171" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I171" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="172" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -15120,16 +15119,16 @@
       </c>
       <c r="C172" s="19"/>
       <c r="D172" s="23" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="E172" s="32"/>
       <c r="F172" s="33"/>
       <c r="G172" s="37"/>
       <c r="H172" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I172" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="173" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -15144,13 +15143,13 @@
       <c r="E173" s="32"/>
       <c r="F173" s="33"/>
       <c r="G173" s="34" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H173" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I173" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="174" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -15165,13 +15164,13 @@
       <c r="E174" s="32"/>
       <c r="F174" s="33"/>
       <c r="G174" s="34" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H174" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I174" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="175" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -15183,16 +15182,16 @@
       </c>
       <c r="C175" s="19"/>
       <c r="D175" s="23" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="E175" s="32"/>
       <c r="F175" s="33"/>
       <c r="G175" s="37"/>
       <c r="H175" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I175" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="176" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -15204,16 +15203,16 @@
       </c>
       <c r="C176" s="19"/>
       <c r="D176" s="23" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="E176" s="32"/>
       <c r="F176" s="33"/>
       <c r="G176" s="37"/>
       <c r="H176" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I176" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="177" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -15228,13 +15227,13 @@
       <c r="E177" s="32"/>
       <c r="F177" s="33"/>
       <c r="G177" s="34" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H177" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I177" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="178" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -15249,13 +15248,13 @@
       <c r="E178" s="32"/>
       <c r="F178" s="33"/>
       <c r="G178" s="34" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H178" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I178" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="179" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -15267,16 +15266,16 @@
       </c>
       <c r="C179" s="19"/>
       <c r="D179" s="23" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="E179" s="32"/>
       <c r="F179" s="33"/>
       <c r="G179" s="37"/>
       <c r="H179" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I179" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="180" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -15284,20 +15283,20 @@
         <v>242</v>
       </c>
       <c r="B180" s="20" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="C180" s="19"/>
       <c r="D180" s="31"/>
       <c r="E180" s="32"/>
       <c r="F180" s="33"/>
       <c r="G180" s="34" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H180" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I180" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="181" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -15312,13 +15311,13 @@
       <c r="E181" s="32"/>
       <c r="F181" s="33"/>
       <c r="G181" s="34" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H181" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I181" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="182" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -15333,13 +15332,13 @@
       <c r="E182" s="32"/>
       <c r="F182" s="33"/>
       <c r="G182" s="34" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H182" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I182" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="183" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -15354,13 +15353,13 @@
       <c r="E183" s="32"/>
       <c r="F183" s="33"/>
       <c r="G183" s="34" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H183" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I183" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="184" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -15372,16 +15371,16 @@
       </c>
       <c r="C184" s="19"/>
       <c r="D184" s="23" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="E184" s="25" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="F184" s="33"/>
       <c r="G184" s="37"/>
       <c r="H184" s="37"/>
       <c r="I184" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="185" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -15389,20 +15388,20 @@
         <v>242</v>
       </c>
       <c r="B185" s="20" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="C185" s="19"/>
       <c r="D185" s="31"/>
       <c r="E185" s="32"/>
       <c r="F185" s="33"/>
       <c r="G185" s="34" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H185" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I185" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="186" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -15414,16 +15413,16 @@
       </c>
       <c r="C186" s="19"/>
       <c r="D186" s="23" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="E186" s="25" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="F186" s="33"/>
       <c r="G186" s="37"/>
       <c r="H186" s="37"/>
       <c r="I186" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="187" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -15438,13 +15437,13 @@
       <c r="E187" s="32"/>
       <c r="F187" s="33"/>
       <c r="G187" s="34" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H187" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I187" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="188" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -15459,13 +15458,13 @@
       <c r="E188" s="32"/>
       <c r="F188" s="33"/>
       <c r="G188" s="34" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H188" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I188" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="189" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -15480,13 +15479,13 @@
       <c r="E189" s="32"/>
       <c r="F189" s="33"/>
       <c r="G189" s="34" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H189" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I189" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="190" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -15494,20 +15493,20 @@
         <v>242</v>
       </c>
       <c r="B190" s="20" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="C190" s="19"/>
       <c r="D190" s="31"/>
       <c r="E190" s="32"/>
       <c r="F190" s="33"/>
       <c r="G190" s="34" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H190" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I190" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="191" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -15522,13 +15521,13 @@
       <c r="E191" s="32"/>
       <c r="F191" s="33"/>
       <c r="G191" s="34" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H191" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I191" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="192" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -15543,13 +15542,13 @@
       <c r="E192" s="32"/>
       <c r="F192" s="33"/>
       <c r="G192" s="34" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H192" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I192" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="193" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -15564,13 +15563,13 @@
       <c r="E193" s="32"/>
       <c r="F193" s="33"/>
       <c r="G193" s="34" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H193" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I193" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="194" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -15585,13 +15584,13 @@
       <c r="E194" s="32"/>
       <c r="F194" s="33"/>
       <c r="G194" s="34" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H194" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I194" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="195" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -15606,13 +15605,13 @@
       <c r="E195" s="32"/>
       <c r="F195" s="33"/>
       <c r="G195" s="34" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H195" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I195" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="196" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -15627,13 +15626,13 @@
       <c r="E196" s="32"/>
       <c r="F196" s="33"/>
       <c r="G196" s="34" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H196" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I196" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="197" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -15648,13 +15647,13 @@
       <c r="E197" s="32"/>
       <c r="F197" s="33"/>
       <c r="G197" s="34" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H197" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I197" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="198" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -15669,13 +15668,13 @@
       <c r="E198" s="32"/>
       <c r="F198" s="33"/>
       <c r="G198" s="34" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H198" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I198" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="199" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -15690,13 +15689,13 @@
       <c r="E199" s="32"/>
       <c r="F199" s="33"/>
       <c r="G199" s="34" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H199" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I199" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="200" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -15711,13 +15710,13 @@
       <c r="E200" s="32"/>
       <c r="F200" s="33"/>
       <c r="G200" s="34" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H200" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I200" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="201" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -15725,20 +15724,20 @@
         <v>242</v>
       </c>
       <c r="B201" s="20" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="C201" s="19"/>
       <c r="D201" s="31"/>
       <c r="E201" s="32"/>
       <c r="F201" s="33"/>
       <c r="G201" s="34" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H201" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I201" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="202" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -15746,20 +15745,20 @@
         <v>242</v>
       </c>
       <c r="B202" s="20" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="C202" s="19"/>
       <c r="D202" s="31"/>
       <c r="E202" s="32"/>
       <c r="F202" s="33"/>
       <c r="G202" s="34" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H202" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I202" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="203" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -15767,20 +15766,20 @@
         <v>242</v>
       </c>
       <c r="B203" s="20" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="C203" s="19"/>
       <c r="D203" s="31"/>
       <c r="E203" s="32"/>
       <c r="F203" s="33"/>
       <c r="G203" s="34" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H203" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I203" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="204" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -15788,20 +15787,20 @@
         <v>242</v>
       </c>
       <c r="B204" s="20" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="C204" s="19"/>
       <c r="D204" s="31"/>
       <c r="E204" s="32"/>
       <c r="F204" s="33"/>
       <c r="G204" s="34" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H204" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I204" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="205" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -15809,20 +15808,20 @@
         <v>242</v>
       </c>
       <c r="B205" s="20" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="C205" s="19"/>
       <c r="D205" s="31"/>
       <c r="E205" s="32"/>
       <c r="F205" s="33"/>
       <c r="G205" s="34" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H205" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I205" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="206" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -15837,13 +15836,13 @@
       <c r="E206" s="32"/>
       <c r="F206" s="33"/>
       <c r="G206" s="34" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H206" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I206" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="207" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -15858,13 +15857,13 @@
       <c r="E207" s="32"/>
       <c r="F207" s="33"/>
       <c r="G207" s="34" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H207" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I207" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="208" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -15879,13 +15878,13 @@
       <c r="E208" s="32"/>
       <c r="F208" s="33"/>
       <c r="G208" s="34" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H208" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I208" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="209" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -15900,13 +15899,13 @@
       <c r="E209" s="32"/>
       <c r="F209" s="33"/>
       <c r="G209" s="34" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H209" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I209" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="210" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -15921,13 +15920,13 @@
       <c r="E210" s="32"/>
       <c r="F210" s="33"/>
       <c r="G210" s="34" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H210" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I210" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="211" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -15942,13 +15941,13 @@
       <c r="E211" s="32"/>
       <c r="F211" s="33"/>
       <c r="G211" s="34" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H211" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I211" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="212" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -15963,13 +15962,13 @@
       <c r="E212" s="32"/>
       <c r="F212" s="33"/>
       <c r="G212" s="34" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H212" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I212" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="213" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -15984,13 +15983,13 @@
       <c r="E213" s="32"/>
       <c r="F213" s="33"/>
       <c r="G213" s="34" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H213" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I213" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="214" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -15998,20 +15997,20 @@
         <v>242</v>
       </c>
       <c r="B214" s="20" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="C214" s="19"/>
       <c r="D214" s="31"/>
       <c r="E214" s="32"/>
       <c r="F214" s="33"/>
       <c r="G214" s="34" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H214" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I214" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="215" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -16019,25 +16018,25 @@
         <v>242</v>
       </c>
       <c r="B215" s="20" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="C215" s="19"/>
       <c r="D215" s="31"/>
       <c r="E215" s="32"/>
       <c r="F215" s="33"/>
       <c r="G215" s="34" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H215" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I215" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="216" spans="1:9" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A216" s="38" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="B216" s="39"/>
       <c r="C216" s="39"/>
@@ -16060,13 +16059,13 @@
       <c r="E217" s="32"/>
       <c r="F217" s="33"/>
       <c r="G217" s="34" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H217" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I217" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="218" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -16078,16 +16077,16 @@
       </c>
       <c r="C218" s="19"/>
       <c r="D218" s="23" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="E218" s="32"/>
       <c r="F218" s="33"/>
       <c r="G218" s="37"/>
       <c r="H218" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I218" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="219" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -16102,13 +16101,13 @@
       <c r="E219" s="32"/>
       <c r="F219" s="33"/>
       <c r="G219" s="34" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H219" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I219" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="220" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -16123,13 +16122,13 @@
       <c r="E220" s="32"/>
       <c r="F220" s="33"/>
       <c r="G220" s="34" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H220" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I220" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="221" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -16144,13 +16143,13 @@
       <c r="E221" s="32"/>
       <c r="F221" s="33"/>
       <c r="G221" s="34" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H221" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I221" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="222" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -16162,16 +16161,16 @@
       </c>
       <c r="C222" s="19"/>
       <c r="D222" s="23" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="E222" s="32"/>
       <c r="F222" s="33"/>
       <c r="G222" s="37"/>
       <c r="H222" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I222" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="223" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -16186,13 +16185,13 @@
       <c r="E223" s="32"/>
       <c r="F223" s="33"/>
       <c r="G223" s="34" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H223" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I223" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="224" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -16207,13 +16206,13 @@
       <c r="E224" s="32"/>
       <c r="F224" s="33"/>
       <c r="G224" s="34" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H224" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I224" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="225" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -16228,13 +16227,13 @@
       <c r="E225" s="32"/>
       <c r="F225" s="33"/>
       <c r="G225" s="34" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H225" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I225" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="226" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -16242,20 +16241,20 @@
         <v>268</v>
       </c>
       <c r="B226" s="20" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="C226" s="19"/>
       <c r="D226" s="31"/>
       <c r="E226" s="32"/>
       <c r="F226" s="33"/>
       <c r="G226" s="34" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H226" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I226" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="227" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -16270,13 +16269,13 @@
       <c r="E227" s="32"/>
       <c r="F227" s="33"/>
       <c r="G227" s="34" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H227" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I227" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="228" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -16291,13 +16290,13 @@
       <c r="E228" s="32"/>
       <c r="F228" s="33"/>
       <c r="G228" s="34" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H228" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I228" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="229" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -16305,20 +16304,20 @@
         <v>268</v>
       </c>
       <c r="B229" s="20" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="C229" s="19"/>
       <c r="D229" s="31"/>
       <c r="E229" s="32"/>
       <c r="F229" s="33"/>
       <c r="G229" s="34" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H229" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I229" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="230" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -16333,13 +16332,13 @@
       <c r="E230" s="32"/>
       <c r="F230" s="33"/>
       <c r="G230" s="34" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H230" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I230" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="231" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -16354,13 +16353,13 @@
       <c r="E231" s="32"/>
       <c r="F231" s="33"/>
       <c r="G231" s="34" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H231" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I231" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="232" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -16375,13 +16374,13 @@
       <c r="E232" s="32"/>
       <c r="F232" s="33"/>
       <c r="G232" s="34" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H232" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I232" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="233" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -16396,13 +16395,13 @@
       <c r="E233" s="32"/>
       <c r="F233" s="33"/>
       <c r="G233" s="34" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H233" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I233" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="234" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -16410,20 +16409,20 @@
         <v>268</v>
       </c>
       <c r="B234" s="20" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="C234" s="19"/>
       <c r="D234" s="31"/>
       <c r="E234" s="32"/>
       <c r="F234" s="33"/>
       <c r="G234" s="34" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H234" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I234" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="235" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -16438,13 +16437,13 @@
       <c r="E235" s="32"/>
       <c r="F235" s="33"/>
       <c r="G235" s="34" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H235" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I235" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="236" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -16459,13 +16458,13 @@
       <c r="E236" s="32"/>
       <c r="F236" s="33"/>
       <c r="G236" s="34" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H236" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I236" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="237" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -16480,13 +16479,13 @@
       <c r="E237" s="32"/>
       <c r="F237" s="33"/>
       <c r="G237" s="34" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H237" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I237" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="238" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -16501,13 +16500,13 @@
       <c r="E238" s="32"/>
       <c r="F238" s="33"/>
       <c r="G238" s="34" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H238" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I238" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="239" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -16522,13 +16521,13 @@
       <c r="E239" s="32"/>
       <c r="F239" s="33"/>
       <c r="G239" s="34" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H239" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I239" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="240" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -16543,13 +16542,13 @@
       <c r="E240" s="32"/>
       <c r="F240" s="33"/>
       <c r="G240" s="34" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H240" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I240" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="241" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -16564,13 +16563,13 @@
       <c r="E241" s="32"/>
       <c r="F241" s="33"/>
       <c r="G241" s="34" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H241" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I241" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="242" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -16585,13 +16584,13 @@
       <c r="E242" s="32"/>
       <c r="F242" s="33"/>
       <c r="G242" s="34" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H242" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I242" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="243" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -16606,13 +16605,13 @@
       <c r="E243" s="32"/>
       <c r="F243" s="33"/>
       <c r="G243" s="34" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H243" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I243" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="244" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -16627,13 +16626,13 @@
       <c r="E244" s="32"/>
       <c r="F244" s="33"/>
       <c r="G244" s="34" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H244" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I244" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="245" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -16641,20 +16640,20 @@
         <v>268</v>
       </c>
       <c r="B245" s="20" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="C245" s="19"/>
       <c r="D245" s="31"/>
       <c r="E245" s="32"/>
       <c r="F245" s="33"/>
       <c r="G245" s="34" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H245" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I245" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="246" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -16662,20 +16661,20 @@
         <v>268</v>
       </c>
       <c r="B246" s="20" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="C246" s="19"/>
       <c r="D246" s="31"/>
       <c r="E246" s="32"/>
       <c r="F246" s="33"/>
       <c r="G246" s="34" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H246" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I246" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="247" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -16683,20 +16682,20 @@
         <v>268</v>
       </c>
       <c r="B247" s="20" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="C247" s="19"/>
       <c r="D247" s="31"/>
       <c r="E247" s="32"/>
       <c r="F247" s="33"/>
       <c r="G247" s="34" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H247" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I247" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="248" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -16704,20 +16703,20 @@
         <v>268</v>
       </c>
       <c r="B248" s="20" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="C248" s="19"/>
       <c r="D248" s="31"/>
       <c r="E248" s="32"/>
       <c r="F248" s="33"/>
       <c r="G248" s="34" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H248" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I248" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="249" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -16725,20 +16724,20 @@
         <v>268</v>
       </c>
       <c r="B249" s="20" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="C249" s="19"/>
       <c r="D249" s="31"/>
       <c r="E249" s="32"/>
       <c r="F249" s="33"/>
       <c r="G249" s="34" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H249" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I249" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="250" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -16753,13 +16752,13 @@
       <c r="E250" s="32"/>
       <c r="F250" s="33"/>
       <c r="G250" s="34" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H250" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I250" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="251" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -16774,13 +16773,13 @@
       <c r="E251" s="32"/>
       <c r="F251" s="33"/>
       <c r="G251" s="34" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H251" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I251" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="252" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -16795,13 +16794,13 @@
       <c r="E252" s="32"/>
       <c r="F252" s="33"/>
       <c r="G252" s="34" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H252" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I252" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="253" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -16813,15 +16812,15 @@
       </c>
       <c r="C253" s="19"/>
       <c r="D253" s="23" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="E253" s="32"/>
       <c r="F253" s="26" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="G253" s="37"/>
       <c r="H253" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I253" s="37"/>
     </row>
@@ -16834,16 +16833,16 @@
       </c>
       <c r="C254" s="19"/>
       <c r="D254" s="23" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="E254" s="32"/>
       <c r="F254" s="33"/>
       <c r="G254" s="37"/>
       <c r="H254" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I254" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="255" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -16855,16 +16854,16 @@
       </c>
       <c r="C255" s="19"/>
       <c r="D255" s="23" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="E255" s="32"/>
       <c r="F255" s="33"/>
       <c r="G255" s="37"/>
       <c r="H255" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I255" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="256" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -16876,16 +16875,16 @@
       </c>
       <c r="C256" s="19"/>
       <c r="D256" s="23" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="E256" s="32"/>
       <c r="F256" s="33"/>
       <c r="G256" s="37"/>
       <c r="H256" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I256" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="257" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -16897,16 +16896,16 @@
       </c>
       <c r="C257" s="19"/>
       <c r="D257" s="23" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="E257" s="32"/>
       <c r="F257" s="33"/>
       <c r="G257" s="37"/>
       <c r="H257" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I257" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="258" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -16914,20 +16913,20 @@
         <v>268</v>
       </c>
       <c r="B258" s="20" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="C258" s="19"/>
       <c r="D258" s="31"/>
       <c r="E258" s="32"/>
       <c r="F258" s="33"/>
       <c r="G258" s="34" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H258" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I258" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="259" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -16935,25 +16934,25 @@
         <v>268</v>
       </c>
       <c r="B259" s="20" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="C259" s="19"/>
       <c r="D259" s="31"/>
       <c r="E259" s="32"/>
       <c r="F259" s="33"/>
       <c r="G259" s="34" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H259" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I259" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="260" spans="1:9" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A260" s="38" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="B260" s="39"/>
       <c r="C260" s="39"/>
@@ -16976,13 +16975,13 @@
       <c r="E261" s="32"/>
       <c r="F261" s="33"/>
       <c r="G261" s="34" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H261" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I261" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="262" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -16997,13 +16996,13 @@
       <c r="E262" s="32"/>
       <c r="F262" s="33"/>
       <c r="G262" s="34" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H262" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I262" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="263" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -17018,13 +17017,13 @@
       <c r="E263" s="32"/>
       <c r="F263" s="33"/>
       <c r="G263" s="34" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H263" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I263" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="264" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -17039,13 +17038,13 @@
       <c r="E264" s="32"/>
       <c r="F264" s="33"/>
       <c r="G264" s="34" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H264" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I264" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="265" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -17060,13 +17059,13 @@
       <c r="E265" s="32"/>
       <c r="F265" s="33"/>
       <c r="G265" s="34" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H265" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I265" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="266" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -17081,13 +17080,13 @@
       <c r="E266" s="32"/>
       <c r="F266" s="33"/>
       <c r="G266" s="34" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H266" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I266" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="267" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -17102,13 +17101,13 @@
       <c r="E267" s="32"/>
       <c r="F267" s="33"/>
       <c r="G267" s="34" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H267" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I267" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="268" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -17123,13 +17122,13 @@
       <c r="E268" s="32"/>
       <c r="F268" s="33"/>
       <c r="G268" s="34" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H268" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I268" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="269" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -17137,20 +17136,20 @@
         <v>293</v>
       </c>
       <c r="B269" s="20" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="C269" s="19"/>
       <c r="D269" s="31"/>
       <c r="E269" s="32"/>
       <c r="F269" s="33"/>
       <c r="G269" s="34" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H269" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I269" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="270" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -17165,13 +17164,13 @@
       <c r="E270" s="32"/>
       <c r="F270" s="33"/>
       <c r="G270" s="34" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H270" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I270" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="271" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -17186,13 +17185,13 @@
       <c r="E271" s="32"/>
       <c r="F271" s="33"/>
       <c r="G271" s="34" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H271" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I271" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="272" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -17207,13 +17206,13 @@
       <c r="E272" s="32"/>
       <c r="F272" s="33"/>
       <c r="G272" s="34" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H272" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I272" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="273" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -17225,16 +17224,16 @@
       </c>
       <c r="C273" s="19"/>
       <c r="D273" s="23" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="E273" s="32"/>
       <c r="F273" s="33"/>
       <c r="G273" s="37"/>
       <c r="H273" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I273" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="274" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -17242,20 +17241,20 @@
         <v>293</v>
       </c>
       <c r="B274" s="20" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="C274" s="19"/>
       <c r="D274" s="31"/>
       <c r="E274" s="32"/>
       <c r="F274" s="33"/>
       <c r="G274" s="34" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H274" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I274" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="275" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -17267,16 +17266,16 @@
       </c>
       <c r="C275" s="19"/>
       <c r="D275" s="23" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="E275" s="32"/>
       <c r="F275" s="33"/>
       <c r="G275" s="37"/>
       <c r="H275" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I275" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="276" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -17291,13 +17290,13 @@
       <c r="E276" s="32"/>
       <c r="F276" s="33"/>
       <c r="G276" s="34" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H276" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I276" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="277" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -17312,13 +17311,13 @@
       <c r="E277" s="32"/>
       <c r="F277" s="33"/>
       <c r="G277" s="34" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H277" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I277" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="278" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -17333,13 +17332,13 @@
       <c r="E278" s="32"/>
       <c r="F278" s="33"/>
       <c r="G278" s="34" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H278" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I278" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="279" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -17354,13 +17353,13 @@
       <c r="E279" s="32"/>
       <c r="F279" s="33"/>
       <c r="G279" s="34" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H279" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I279" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="280" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -17368,20 +17367,20 @@
         <v>293</v>
       </c>
       <c r="B280" s="20" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="C280" s="19"/>
       <c r="D280" s="31"/>
       <c r="E280" s="32"/>
       <c r="F280" s="33"/>
       <c r="G280" s="34" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H280" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I280" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="281" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -17396,13 +17395,13 @@
       <c r="E281" s="32"/>
       <c r="F281" s="33"/>
       <c r="G281" s="34" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H281" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I281" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="282" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -17417,13 +17416,13 @@
       <c r="E282" s="32"/>
       <c r="F282" s="33"/>
       <c r="G282" s="34" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H282" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I282" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="283" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -17438,13 +17437,13 @@
       <c r="E283" s="32"/>
       <c r="F283" s="33"/>
       <c r="G283" s="34" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H283" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I283" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="284" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -17459,13 +17458,13 @@
       <c r="E284" s="32"/>
       <c r="F284" s="33"/>
       <c r="G284" s="34" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H284" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I284" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="285" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -17480,13 +17479,13 @@
       <c r="E285" s="32"/>
       <c r="F285" s="33"/>
       <c r="G285" s="34" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H285" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I285" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="286" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -17501,13 +17500,13 @@
       <c r="E286" s="32"/>
       <c r="F286" s="33"/>
       <c r="G286" s="34" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H286" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I286" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="287" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -17522,13 +17521,13 @@
       <c r="E287" s="32"/>
       <c r="F287" s="33"/>
       <c r="G287" s="34" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H287" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I287" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="288" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -17543,13 +17542,13 @@
       <c r="E288" s="32"/>
       <c r="F288" s="33"/>
       <c r="G288" s="34" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H288" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I288" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="289" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -17564,13 +17563,13 @@
       <c r="E289" s="32"/>
       <c r="F289" s="33"/>
       <c r="G289" s="34" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H289" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I289" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="290" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -17585,13 +17584,13 @@
       <c r="E290" s="32"/>
       <c r="F290" s="33"/>
       <c r="G290" s="34" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H290" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I290" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="291" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -17599,20 +17598,20 @@
         <v>293</v>
       </c>
       <c r="B291" s="20" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="C291" s="19"/>
       <c r="D291" s="31"/>
       <c r="E291" s="32"/>
       <c r="F291" s="33"/>
       <c r="G291" s="34" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H291" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I291" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="292" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -17620,20 +17619,20 @@
         <v>293</v>
       </c>
       <c r="B292" s="20" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="C292" s="19"/>
       <c r="D292" s="31"/>
       <c r="E292" s="32"/>
       <c r="F292" s="33"/>
       <c r="G292" s="34" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H292" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I292" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="293" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -17641,20 +17640,20 @@
         <v>293</v>
       </c>
       <c r="B293" s="20" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="C293" s="19"/>
       <c r="D293" s="31"/>
       <c r="E293" s="32"/>
       <c r="F293" s="33"/>
       <c r="G293" s="34" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H293" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I293" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="294" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -17662,20 +17661,20 @@
         <v>293</v>
       </c>
       <c r="B294" s="20" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="C294" s="19"/>
       <c r="D294" s="31"/>
       <c r="E294" s="32"/>
       <c r="F294" s="33"/>
       <c r="G294" s="34" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H294" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I294" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="295" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -17683,20 +17682,20 @@
         <v>293</v>
       </c>
       <c r="B295" s="20" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="C295" s="19"/>
       <c r="D295" s="31"/>
       <c r="E295" s="32"/>
       <c r="F295" s="33"/>
       <c r="G295" s="34" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H295" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I295" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="296" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -17711,13 +17710,13 @@
       <c r="E296" s="32"/>
       <c r="F296" s="33"/>
       <c r="G296" s="34" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H296" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I296" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="297" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -17732,13 +17731,13 @@
       <c r="E297" s="32"/>
       <c r="F297" s="33"/>
       <c r="G297" s="34" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H297" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I297" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="298" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -17753,13 +17752,13 @@
       <c r="E298" s="32"/>
       <c r="F298" s="33"/>
       <c r="G298" s="34" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H298" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I298" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="299" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -17774,13 +17773,13 @@
       <c r="E299" s="32"/>
       <c r="F299" s="33"/>
       <c r="G299" s="34" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H299" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I299" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="300" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -17792,16 +17791,16 @@
       </c>
       <c r="C300" s="19"/>
       <c r="D300" s="23" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="E300" s="32"/>
       <c r="F300" s="33"/>
       <c r="G300" s="37"/>
       <c r="H300" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I300" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="301" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -17813,16 +17812,16 @@
       </c>
       <c r="C301" s="19"/>
       <c r="D301" s="23" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="E301" s="32"/>
       <c r="F301" s="33"/>
       <c r="G301" s="37"/>
       <c r="H301" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I301" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="302" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -17837,13 +17836,13 @@
       <c r="E302" s="32"/>
       <c r="F302" s="33"/>
       <c r="G302" s="34" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H302" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I302" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="303" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -17858,13 +17857,13 @@
       <c r="E303" s="32"/>
       <c r="F303" s="33"/>
       <c r="G303" s="34" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H303" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I303" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="304" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -17872,20 +17871,20 @@
         <v>293</v>
       </c>
       <c r="B304" s="20" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="C304" s="19"/>
       <c r="D304" s="31"/>
       <c r="E304" s="32"/>
       <c r="F304" s="33"/>
       <c r="G304" s="34" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H304" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I304" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="305" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -17893,25 +17892,25 @@
         <v>293</v>
       </c>
       <c r="B305" s="20" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="C305" s="19"/>
       <c r="D305" s="31"/>
       <c r="E305" s="32"/>
       <c r="F305" s="33"/>
       <c r="G305" s="34" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H305" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I305" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="306" spans="1:9" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A306" s="38" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="B306" s="39"/>
       <c r="C306" s="39"/>
@@ -17934,13 +17933,13 @@
       <c r="E307" s="32"/>
       <c r="F307" s="33"/>
       <c r="G307" s="34" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H307" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I307" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="308" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -17955,13 +17954,13 @@
       <c r="E308" s="32"/>
       <c r="F308" s="33"/>
       <c r="G308" s="34" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H308" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I308" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="309" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -17976,13 +17975,13 @@
       <c r="E309" s="32"/>
       <c r="F309" s="33"/>
       <c r="G309" s="34" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H309" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I309" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="310" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -17997,13 +17996,13 @@
       <c r="E310" s="32"/>
       <c r="F310" s="33"/>
       <c r="G310" s="34" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H310" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I310" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="311" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -18018,13 +18017,13 @@
       <c r="E311" s="32"/>
       <c r="F311" s="33"/>
       <c r="G311" s="34" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H311" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I311" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="312" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -18039,13 +18038,13 @@
       <c r="E312" s="32"/>
       <c r="F312" s="33"/>
       <c r="G312" s="34" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H312" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I312" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="313" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -18060,13 +18059,13 @@
       <c r="E313" s="32"/>
       <c r="F313" s="33"/>
       <c r="G313" s="34" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H313" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I313" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="314" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -18081,13 +18080,13 @@
       <c r="E314" s="32"/>
       <c r="F314" s="33"/>
       <c r="G314" s="34" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H314" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I314" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="315" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -18099,16 +18098,16 @@
       </c>
       <c r="C315" s="19"/>
       <c r="D315" s="23" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="E315" s="32"/>
       <c r="F315" s="33"/>
       <c r="G315" s="37"/>
       <c r="H315" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I315" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="316" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -18116,20 +18115,20 @@
         <v>303</v>
       </c>
       <c r="B316" s="20" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="C316" s="19"/>
       <c r="D316" s="31"/>
       <c r="E316" s="32"/>
       <c r="F316" s="33"/>
       <c r="G316" s="34" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H316" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I316" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="317" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -18144,13 +18143,13 @@
       <c r="E317" s="32"/>
       <c r="F317" s="33"/>
       <c r="G317" s="34" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H317" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I317" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="318" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -18165,13 +18164,13 @@
       <c r="E318" s="32"/>
       <c r="F318" s="33"/>
       <c r="G318" s="34" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H318" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I318" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="319" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -18186,13 +18185,13 @@
       <c r="E319" s="32"/>
       <c r="F319" s="33"/>
       <c r="G319" s="34" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H319" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I319" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="320" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -18204,16 +18203,16 @@
       </c>
       <c r="C320" s="19"/>
       <c r="D320" s="23" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="E320" s="32"/>
       <c r="F320" s="33"/>
       <c r="G320" s="37"/>
       <c r="H320" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I320" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="321" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -18221,20 +18220,20 @@
         <v>303</v>
       </c>
       <c r="B321" s="20" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="C321" s="19"/>
       <c r="D321" s="31"/>
       <c r="E321" s="32"/>
       <c r="F321" s="33"/>
       <c r="G321" s="34" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H321" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I321" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="322" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -18246,16 +18245,16 @@
       </c>
       <c r="C322" s="19"/>
       <c r="D322" s="23" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="E322" s="32"/>
       <c r="F322" s="33"/>
       <c r="G322" s="37"/>
       <c r="H322" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I322" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="323" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -18270,13 +18269,13 @@
       <c r="E323" s="32"/>
       <c r="F323" s="33"/>
       <c r="G323" s="34" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H323" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I323" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="324" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -18291,13 +18290,13 @@
       <c r="E324" s="32"/>
       <c r="F324" s="33"/>
       <c r="G324" s="34" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H324" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I324" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="325" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -18312,13 +18311,13 @@
       <c r="E325" s="32"/>
       <c r="F325" s="33"/>
       <c r="G325" s="34" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H325" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I325" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="326" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -18333,13 +18332,13 @@
       <c r="E326" s="32"/>
       <c r="F326" s="33"/>
       <c r="G326" s="34" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H326" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I326" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="327" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -18347,20 +18346,20 @@
         <v>303</v>
       </c>
       <c r="B327" s="20" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="C327" s="19"/>
       <c r="D327" s="31"/>
       <c r="E327" s="32"/>
       <c r="F327" s="33"/>
       <c r="G327" s="34" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H327" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I327" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="328" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -18375,13 +18374,13 @@
       <c r="E328" s="32"/>
       <c r="F328" s="33"/>
       <c r="G328" s="34" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H328" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I328" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="329" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -18396,13 +18395,13 @@
       <c r="E329" s="32"/>
       <c r="F329" s="33"/>
       <c r="G329" s="34" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H329" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I329" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="330" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -18417,13 +18416,13 @@
       <c r="E330" s="32"/>
       <c r="F330" s="33"/>
       <c r="G330" s="34" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H330" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I330" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="331" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -18438,13 +18437,13 @@
       <c r="E331" s="32"/>
       <c r="F331" s="33"/>
       <c r="G331" s="34" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H331" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I331" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="332" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -18459,13 +18458,13 @@
       <c r="E332" s="32"/>
       <c r="F332" s="33"/>
       <c r="G332" s="34" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H332" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I332" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="333" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -18480,13 +18479,13 @@
       <c r="E333" s="32"/>
       <c r="F333" s="33"/>
       <c r="G333" s="34" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H333" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I333" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="334" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -18501,13 +18500,13 @@
       <c r="E334" s="32"/>
       <c r="F334" s="33"/>
       <c r="G334" s="34" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H334" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I334" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="335" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -18522,13 +18521,13 @@
       <c r="E335" s="32"/>
       <c r="F335" s="33"/>
       <c r="G335" s="34" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H335" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I335" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="336" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -18543,13 +18542,13 @@
       <c r="E336" s="32"/>
       <c r="F336" s="33"/>
       <c r="G336" s="34" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H336" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I336" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="337" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -18564,13 +18563,13 @@
       <c r="E337" s="32"/>
       <c r="F337" s="33"/>
       <c r="G337" s="34" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H337" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I337" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="338" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -18578,20 +18577,20 @@
         <v>303</v>
       </c>
       <c r="B338" s="20" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="C338" s="19"/>
       <c r="D338" s="31"/>
       <c r="E338" s="32"/>
       <c r="F338" s="33"/>
       <c r="G338" s="34" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H338" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I338" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="339" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -18599,20 +18598,20 @@
         <v>303</v>
       </c>
       <c r="B339" s="20" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="C339" s="19"/>
       <c r="D339" s="31"/>
       <c r="E339" s="32"/>
       <c r="F339" s="33"/>
       <c r="G339" s="34" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H339" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I339" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="340" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -18620,20 +18619,20 @@
         <v>303</v>
       </c>
       <c r="B340" s="20" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="C340" s="19"/>
       <c r="D340" s="31"/>
       <c r="E340" s="32"/>
       <c r="F340" s="33"/>
       <c r="G340" s="34" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H340" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I340" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="341" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -18641,20 +18640,20 @@
         <v>303</v>
       </c>
       <c r="B341" s="20" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="C341" s="19"/>
       <c r="D341" s="31"/>
       <c r="E341" s="32"/>
       <c r="F341" s="33"/>
       <c r="G341" s="34" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H341" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I341" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="342" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -18662,20 +18661,20 @@
         <v>303</v>
       </c>
       <c r="B342" s="20" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="C342" s="19"/>
       <c r="D342" s="31"/>
       <c r="E342" s="32"/>
       <c r="F342" s="33"/>
       <c r="G342" s="34" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H342" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I342" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="343" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -18690,13 +18689,13 @@
       <c r="E343" s="32"/>
       <c r="F343" s="33"/>
       <c r="G343" s="34" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H343" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I343" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="344" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -18711,13 +18710,13 @@
       <c r="E344" s="32"/>
       <c r="F344" s="33"/>
       <c r="G344" s="34" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H344" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I344" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="345" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -18732,13 +18731,13 @@
       <c r="E345" s="32"/>
       <c r="F345" s="33"/>
       <c r="G345" s="34" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H345" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I345" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="346" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -18753,13 +18752,13 @@
       <c r="E346" s="32"/>
       <c r="F346" s="33"/>
       <c r="G346" s="34" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H346" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I346" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="347" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -18774,13 +18773,13 @@
       <c r="E347" s="32"/>
       <c r="F347" s="33"/>
       <c r="G347" s="34" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H347" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I347" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="348" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -18795,13 +18794,13 @@
       <c r="E348" s="32"/>
       <c r="F348" s="33"/>
       <c r="G348" s="34" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H348" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I348" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="349" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -18816,13 +18815,13 @@
       <c r="E349" s="32"/>
       <c r="F349" s="33"/>
       <c r="G349" s="34" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H349" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I349" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="350" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -18837,13 +18836,13 @@
       <c r="E350" s="32"/>
       <c r="F350" s="33"/>
       <c r="G350" s="34" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H350" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I350" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="351" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -18851,20 +18850,20 @@
         <v>303</v>
       </c>
       <c r="B351" s="20" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="C351" s="19"/>
       <c r="D351" s="31"/>
       <c r="E351" s="32"/>
       <c r="F351" s="33"/>
       <c r="G351" s="34" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H351" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I351" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="352" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -18872,20 +18871,20 @@
         <v>303</v>
       </c>
       <c r="B352" s="20" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="C352" s="19"/>
       <c r="D352" s="31"/>
       <c r="E352" s="32"/>
       <c r="F352" s="33"/>
       <c r="G352" s="34" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H352" s="35" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I352" s="36" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
   </sheetData>
